--- a/Assets/AddressableResource/Data/Excels/QuestData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/QuestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F23745-C0F9-4DD4-BD6A-B2814D6782AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02EC6483-33D9-4441-976A-6E75FD2F6C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,10 +51,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>title</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>desc</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -87,26 +83,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>제목</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>내용. {0}을 {1}하라</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>target</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>count</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>matchcard 등</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>#1</t>
   </si>
   <si>
@@ -179,6 +163,14 @@
   </si>
   <si>
     <t>detailType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>questGame</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데일리 / 통상</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -609,22 +601,22 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="19.625" style="3" customWidth="1"/>
-    <col min="4" max="6" width="19.625" style="5" customWidth="1"/>
-    <col min="7" max="10" width="19.625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.625" style="9" customWidth="1"/>
-    <col min="12" max="12" width="19.625" style="5" customWidth="1"/>
-    <col min="13" max="15" width="12.75" style="2" customWidth="1"/>
-    <col min="16" max="16" width="17.125" style="2" customWidth="1"/>
-    <col min="17" max="17" width="10.625" style="2"/>
-    <col min="18" max="20" width="10.625" style="9"/>
-    <col min="21" max="16384" width="10.625" style="2"/>
+    <col min="1" max="4" width="19.625" style="3" customWidth="1"/>
+    <col min="5" max="7" width="19.625" style="5" customWidth="1"/>
+    <col min="8" max="9" width="19.625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="19.625" style="9" customWidth="1"/>
+    <col min="11" max="11" width="19.625" style="5" customWidth="1"/>
+    <col min="12" max="14" width="12.75" style="2" customWidth="1"/>
+    <col min="15" max="15" width="17.125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="10.625" style="2"/>
+    <col min="17" max="19" width="10.625" style="9"/>
+    <col min="20" max="16384" width="10.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,150 +624,143 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="G1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
+      <c r="B2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="8">
+        <v>10</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="6" t="s">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="8">
-        <v>10</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>18</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
-      <c r="D3" s="7"/>
+      <c r="D3" s="6"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
-      <c r="G3" s="6"/>
+      <c r="G3" s="7"/>
       <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="7"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="7"/>
+      <c r="M3" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="N3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="M4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="M5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="M6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="M7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="N4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="N5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="N6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="N7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/AddressableResource/Data/Excels/QuestData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/QuestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02EC6483-33D9-4441-976A-6E75FD2F6C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A30A16-764C-4A85-B672-07F9792378AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -720,7 +720,7 @@
         <v>25</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
@@ -730,7 +730,7 @@
         <v>19</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>

--- a/Assets/AddressableResource/Data/Excels/QuestData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/QuestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A30A16-764C-4A85-B672-07F9792378AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CAEE002-1CD5-49DE-8179-5F54EBA52A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="98">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -102,75 +102,256 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Match2Card</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FindAIWord</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>세부 타입(꿀밤 등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detailType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>questGame</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데일리 / 통상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Achievement</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>questType</t>
+  </si>
+  <si>
+    <t>questGame</t>
+  </si>
+  <si>
+    <t>detailType</t>
+  </si>
+  <si>
+    <t>grade</t>
+  </si>
+  <si>
+    <t>MatchCardGame</t>
+  </si>
+  <si>
+    <t>FindAIWordGame</t>
   </si>
   <si>
     <t>CubeGame</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>WingTto</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TowerGame</t>
   </si>
   <si>
     <t>Gacha</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tower</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>세부 타입(꿀밤 등)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>모든 카드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>특정등급 카드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Collection</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>// match card</t>
+  </si>
+  <si>
+    <t>PlayMatchCardGame</t>
+  </si>
+  <si>
+    <t>FinishCardGameUnderCount</t>
+  </si>
+  <si>
+    <t>// find AI word</t>
+  </si>
+  <si>
+    <t>PlayFindAIWordGame</t>
+  </si>
+  <si>
+    <t>FinishWordGameUnderCount</t>
+  </si>
+  <si>
+    <t>// cube</t>
+  </si>
+  <si>
+    <t>PlayCubeGame</t>
+  </si>
+  <si>
+    <t>ReachCubeScore</t>
+  </si>
+  <si>
+    <t>ReachTotalTouchCount</t>
+  </si>
+  <si>
+    <t>ReachCubeStateTouchCount</t>
+  </si>
+  <si>
+    <t>S_ReachScoreWithoutTooFastOrTooSlow</t>
+  </si>
+  <si>
+    <t>S_ReachScoreWithOnlyPerfect</t>
+  </si>
+  <si>
+    <t>// wingtto</t>
+  </si>
+  <si>
+    <t>PlayWingTto</t>
+  </si>
+  <si>
+    <t>ReachWingTtoDistance</t>
+  </si>
+  <si>
+    <t>CollectWingTtoItem</t>
+  </si>
+  <si>
+    <t>S_ReachScoreWithoutGimbab</t>
+  </si>
+  <si>
+    <t>S_ReachScoreWithCrash</t>
+  </si>
+  <si>
+    <t>// tower</t>
+  </si>
+  <si>
+    <t>ReachTowerFloor</t>
+  </si>
+  <si>
+    <t>ReachStatLevel</t>
+  </si>
+  <si>
+    <t>ReachWeaponLevel</t>
+  </si>
+  <si>
+    <t>S_WinWithAvoid</t>
+  </si>
+  <si>
+    <t>// collection</t>
+  </si>
+  <si>
+    <t>CollectCard</t>
+  </si>
+  <si>
+    <t>CollectWord</t>
+  </si>
+  <si>
+    <t>// gacha</t>
+  </si>
+  <si>
+    <t>PlayGacha</t>
+  </si>
+  <si>
+    <t>PlayMileageGacha</t>
+  </si>
+  <si>
+    <t>// common</t>
+  </si>
+  <si>
+    <t>CollectCoin</t>
+  </si>
+  <si>
+    <t>UseCoin</t>
+  </si>
+  <si>
+    <t>ReachPlayerLevel</t>
+  </si>
+  <si>
+    <t>S_EquipEtcIcon</t>
+  </si>
+  <si>
+    <t>Basic</t>
   </si>
   <si>
     <t>Difficult</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Challenge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Insane</t>
   </si>
   <si>
     <t>Nightmare</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Insane</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Unexpected</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Basic</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>detailType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>questGame</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>데일리 / 통상</t>
+  </si>
+  <si>
+    <t>detailType2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 세부 타입(필요시)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필요.. 한가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_PlayEndRoll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CubeState_TooFast</t>
+  </si>
+  <si>
+    <t>CubeState_Fast</t>
+  </si>
+  <si>
+    <t>CubeState_Perfect</t>
+  </si>
+  <si>
+    <t>CubeState_Slow</t>
+  </si>
+  <si>
+    <t>CubeState_TooSlow</t>
+  </si>
+  <si>
+    <t>WingTtoItem_Gimbab</t>
+  </si>
+  <si>
+    <t>WingTtoItem_SpeedUp</t>
+  </si>
+  <si>
+    <t>WingTtoItem_Coin</t>
+  </si>
+  <si>
+    <t>WingTtoItem_Exp</t>
+  </si>
+  <si>
+    <t>TowerStat_Atk</t>
+  </si>
+  <si>
+    <t>TowerStat_Def</t>
+  </si>
+  <si>
+    <t>TowerStat_Hp</t>
+  </si>
+  <si>
+    <t>TowerStat_CriRate</t>
+  </si>
+  <si>
+    <t>TowerStat_CriDmg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> // cube</t>
+  </si>
+  <si>
+    <t>미션 수치</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -181,7 +362,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,6 +390,19 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -264,7 +458,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -294,6 +488,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -601,22 +810,30 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U53"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="4" width="19.625" style="3" customWidth="1"/>
-    <col min="5" max="7" width="19.625" style="5" customWidth="1"/>
-    <col min="8" max="9" width="19.625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="19.625" style="9" customWidth="1"/>
-    <col min="11" max="11" width="19.625" style="5" customWidth="1"/>
-    <col min="12" max="14" width="12.75" style="2" customWidth="1"/>
-    <col min="15" max="15" width="17.125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="10.625" style="2"/>
-    <col min="17" max="19" width="10.625" style="9"/>
-    <col min="20" max="16384" width="10.625" style="2"/>
+    <col min="1" max="1" width="19.625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="15" style="3" customWidth="1"/>
+    <col min="3" max="5" width="30" style="3" customWidth="1"/>
+    <col min="6" max="6" width="19.5" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30" style="2" customWidth="1"/>
+    <col min="10" max="10" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" style="9" customWidth="1"/>
+    <col min="12" max="12" width="9" style="5" customWidth="1"/>
+    <col min="13" max="14" width="12.75" style="2" customWidth="1"/>
+    <col min="15" max="15" width="14.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="42.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="42.5" style="2" customWidth="1"/>
+    <col min="19" max="19" width="11.75" style="9" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="10.625" style="9"/>
+    <col min="22" max="16384" width="10.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -624,147 +841,1242 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="O1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T1" s="2"/>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="8">
-        <v>10</v>
-      </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="K2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="L2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="O2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="T2" s="2"/>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="7"/>
-      <c r="M3" s="2" t="s">
+      <c r="B3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="7">
+        <v>1</v>
+      </c>
+      <c r="H3" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J3" s="8">
+        <v>100</v>
+      </c>
+      <c r="K3" s="10">
+        <v>100</v>
+      </c>
+      <c r="L3" s="7">
+        <v>1</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="T3" s="2"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" s="11">
+        <f>ROW()-3</f>
+        <v>1</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="13">
+        <v>1</v>
+      </c>
+      <c r="H4" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="12"/>
+      <c r="J4" s="14">
+        <v>100</v>
+      </c>
+      <c r="K4" s="15">
+        <v>100</v>
+      </c>
+      <c r="L4" s="13">
+        <v>1</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T4" s="2"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" s="11">
+        <f t="shared" ref="A5:A53" si="0">ROW()-3</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="13"/>
+      <c r="P5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="T5" s="2"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" s="11">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="13"/>
+      <c r="P6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="T6" s="2"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" s="11">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="13"/>
+      <c r="P7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" s="11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="13"/>
+      <c r="O8" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" s="11">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="13"/>
+      <c r="O9" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" s="11">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="13"/>
+      <c r="O10" s="9"/>
+      <c r="Q10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" s="11">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="13"/>
+      <c r="Q11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" s="11">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="13"/>
+      <c r="Q12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" s="11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="13"/>
+      <c r="Q13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" s="11">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="13"/>
+      <c r="Q14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15" s="11">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="13"/>
+      <c r="Q15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16" s="11">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="13"/>
+      <c r="Q16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="11">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="13"/>
+      <c r="Q17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" s="11">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="13"/>
+      <c r="Q18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" s="11">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="13"/>
+      <c r="Q19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" s="11">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="13"/>
+      <c r="Q20" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" s="11">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="13"/>
+      <c r="Q21" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" s="11">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="13"/>
+      <c r="Q22" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" s="11">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="13"/>
+      <c r="Q23" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" s="11">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="13"/>
+      <c r="Q24" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25" s="11">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="13"/>
+      <c r="Q25" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" s="11">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="13"/>
+      <c r="Q26" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" s="11">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="13"/>
+      <c r="Q27" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" s="11">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="13"/>
+      <c r="Q28" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" s="11">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="13"/>
+      <c r="Q29" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="A30" s="11">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="M4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="M5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="O5" s="2" t="s">
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="13"/>
+      <c r="Q30" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31" s="11">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="13"/>
+      <c r="Q31" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="A32" s="11">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="M6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="M7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="O7" s="2" t="s">
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="13"/>
+      <c r="Q32" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33" s="11">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="13"/>
+      <c r="Q33" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" s="11">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="13"/>
+      <c r="Q34" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="A35" s="11">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="13"/>
+      <c r="Q35" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" s="11">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="13"/>
+      <c r="Q36" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" s="11">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="13"/>
+      <c r="Q37" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38" s="11">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" spans="1:17">
+      <c r="A39" s="11">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="A40" s="11">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="13"/>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41" s="11">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="A42" s="11">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="13"/>
+    </row>
+    <row r="43" spans="1:17">
+      <c r="A43" s="11">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="15"/>
+      <c r="L43" s="13"/>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="A44" s="11">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="13"/>
+    </row>
+    <row r="45" spans="1:17">
+      <c r="A45" s="11">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="14"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="13"/>
+    </row>
+    <row r="46" spans="1:17">
+      <c r="A46" s="11">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="13"/>
+    </row>
+    <row r="47" spans="1:17">
+      <c r="A47" s="11">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="13"/>
+    </row>
+    <row r="48" spans="1:17">
+      <c r="A48" s="11">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="13"/>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="11">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="15"/>
+      <c r="L49" s="13"/>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="11">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="15"/>
+      <c r="L50" s="13"/>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="11">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="12"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="15"/>
+      <c r="L51" s="13"/>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="11">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="12"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="15"/>
+      <c r="L52" s="13"/>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="11">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="12"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="15"/>
+      <c r="L53" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B53" xr:uid="{EA80D64E-578A-4FE2-B978-0712AFDAAEE6}">
+      <formula1>$O$2:$O$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C53" xr:uid="{A88927D6-C705-42EA-93F9-56044FBF1090}">
+      <formula1>$P$2:$P$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F53" xr:uid="{B197848D-F103-4380-83AB-2CDAAF2AFD3C}">
+      <formula1>$S$2:$S$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H53" xr:uid="{4A1BC11C-DA03-43AB-9BCE-E2B3D7ABF0B6}">
+      <formula1>$O$8:$O$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E53" xr:uid="{269CC43C-2462-4F32-A11C-04284C405092}">
+      <formula1>$R$2:$R$43</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D53" xr:uid="{2F6AB2AA-CDCC-4A9C-BBFD-3B4002AE4F9B}">
+      <formula1>$Q$2:$Q$61</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Assets/AddressableResource/Data/Excels/QuestData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/QuestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CAEE002-1CD5-49DE-8179-5F54EBA52A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2CF0C0E-3C80-4FEB-9213-338DF1C46197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="102">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -87,10 +87,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>#1</t>
   </si>
   <si>
@@ -351,7 +347,27 @@
     <t xml:space="preserve"> // cube</t>
   </si>
   <si>
-    <t>미션 수치</t>
+    <t>tryCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도달 횟수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특수 이벤트는 1회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reachCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시도 횟수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정 점수 등에 도달에 사용</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -490,19 +506,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -810,7 +826,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:U53"/>
+  <dimension ref="A1:V53"/>
   <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="17.25"/>
   <cols>
     <col min="1" max="1" width="19.625" style="3" customWidth="1"/>
@@ -820,20 +836,21 @@
     <col min="7" max="7" width="11.5" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15" style="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="30" style="2" customWidth="1"/>
-    <col min="10" max="10" width="10.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9" style="9" customWidth="1"/>
-    <col min="12" max="12" width="9" style="5" customWidth="1"/>
-    <col min="13" max="14" width="12.75" style="2" customWidth="1"/>
-    <col min="15" max="15" width="14.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="42.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="42.5" style="2" customWidth="1"/>
-    <col min="19" max="19" width="11.75" style="9" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="10.625" style="9"/>
-    <col min="22" max="16384" width="10.625" style="2"/>
+    <col min="10" max="10" width="28.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9" style="9" customWidth="1"/>
+    <col min="13" max="13" width="9" style="5" customWidth="1"/>
+    <col min="14" max="15" width="12.75" style="2" customWidth="1"/>
+    <col min="16" max="16" width="14.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="42.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="42.5" style="2" customWidth="1"/>
+    <col min="20" max="20" width="11.75" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="10.625" style="9"/>
+    <col min="23" max="16384" width="10.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -841,13 +858,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>2</v>
@@ -862,55 +879,58 @@
         <v>4</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="K1" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="S1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="T1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R1" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="T1" s="2"/>
-    </row>
-    <row r="2" spans="1:20">
+      <c r="U1" s="2"/>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>16</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>12</v>
@@ -918,47 +938,50 @@
       <c r="J2" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="L2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="M2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="P2" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="Q2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="U2" s="2"/>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="R2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="T2" s="2"/>
-    </row>
-    <row r="3" spans="1:20">
-      <c r="A3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>36</v>
-      </c>
       <c r="E3" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G3" s="7">
         <v>1</v>
@@ -967,53 +990,56 @@
         <v>0</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="J3" s="8">
+        <v>79</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L3" s="10">
         <v>100</v>
       </c>
-      <c r="K3" s="10">
-        <v>100</v>
-      </c>
-      <c r="L3" s="7">
+      <c r="M3" s="7">
         <v>1</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="P3" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="T3" s="2"/>
-    </row>
-    <row r="4" spans="1:20">
+        <v>95</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="U3" s="2"/>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" s="11">
         <f>ROW()-3</f>
         <v>1</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G4" s="13">
         <v>1</v>
@@ -1023,59 +1049,85 @@
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="14">
+        <v>0</v>
+      </c>
+      <c r="K4" s="14">
         <v>100</v>
       </c>
-      <c r="K4" s="15">
+      <c r="L4" s="15">
         <v>100</v>
       </c>
-      <c r="L4" s="13">
+      <c r="M4" s="13">
         <v>1</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="Q4" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T4" s="2"/>
-    </row>
-    <row r="5" spans="1:20">
+        <v>81</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="U4" s="2"/>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" s="11">
         <f t="shared" ref="A5:A53" si="0">ROW()-3</f>
         <v>2</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
+      <c r="B5" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="13">
+        <v>1</v>
+      </c>
+      <c r="H5" s="13" t="b">
+        <v>0</v>
+      </c>
       <c r="I5" s="12"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="13"/>
-      <c r="P5" s="2" t="s">
-        <v>30</v>
+      <c r="J5" s="14">
+        <v>3500</v>
+      </c>
+      <c r="K5" s="14">
+        <v>1</v>
+      </c>
+      <c r="L5" s="15">
+        <v>100</v>
+      </c>
+      <c r="M5" s="13">
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="T5" s="2"/>
-    </row>
-    <row r="6" spans="1:20">
+        <v>82</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U5" s="2"/>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1083,29 +1135,32 @@
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
+      <c r="E6" s="12" t="s">
+        <v>77</v>
+      </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
       <c r="I6" s="12"/>
       <c r="J6" s="14"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="13"/>
-      <c r="P6" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="K6" s="14"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="13"/>
       <c r="Q6" s="2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="T6" s="2"/>
-    </row>
-    <row r="7" spans="1:20">
+        <v>83</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="U6" s="2"/>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1113,32 +1168,32 @@
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
+      <c r="E7" s="12" t="s">
+        <v>77</v>
+      </c>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
       <c r="I7" s="12"/>
       <c r="J7" s="14"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="13"/>
-      <c r="P7" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="K7" s="14"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="13"/>
       <c r="Q7" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="S7" s="9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20">
-      <c r="A8" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" s="11"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
       <c r="D8" s="12"/>
@@ -1148,26 +1203,24 @@
       <c r="H8" s="13"/>
       <c r="I8" s="12"/>
       <c r="J8" s="14"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="13"/>
-      <c r="O8" s="9" t="b">
+      <c r="K8" s="14"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="13"/>
+      <c r="P8" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="Q8" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
-      <c r="A9" s="11">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="11"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
@@ -1177,26 +1230,24 @@
       <c r="H9" s="13"/>
       <c r="I9" s="12"/>
       <c r="J9" s="14"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="13"/>
-      <c r="O9" s="9" t="b">
+      <c r="K9" s="14"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="13"/>
+      <c r="P9" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="Q9" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
-      <c r="A10" s="11">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="11"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -1206,21 +1257,19 @@
       <c r="H10" s="13"/>
       <c r="I10" s="12"/>
       <c r="J10" s="14"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="13"/>
-      <c r="O10" s="9"/>
-      <c r="Q10" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="K10" s="14"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="13"/>
+      <c r="P10" s="9"/>
       <c r="R10" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20">
-      <c r="A11" s="11">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" s="11"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -1230,20 +1279,18 @@
       <c r="H11" s="13"/>
       <c r="I11" s="12"/>
       <c r="J11" s="14"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="13"/>
-      <c r="Q11" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="K11" s="14"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="13"/>
       <c r="R11" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20">
-      <c r="A12" s="11">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" s="11"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
@@ -1253,20 +1300,18 @@
       <c r="H12" s="13"/>
       <c r="I12" s="12"/>
       <c r="J12" s="14"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="13"/>
-      <c r="Q12" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="K12" s="14"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="13"/>
       <c r="R12" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20">
-      <c r="A13" s="11">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" s="11"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
@@ -1276,20 +1321,18 @@
       <c r="H13" s="13"/>
       <c r="I13" s="12"/>
       <c r="J13" s="14"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="13"/>
-      <c r="Q13" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="K13" s="14"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="13"/>
       <c r="R13" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20">
-      <c r="A14" s="11">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
+      <c r="A14" s="11"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
@@ -1299,20 +1342,18 @@
       <c r="H14" s="13"/>
       <c r="I14" s="12"/>
       <c r="J14" s="14"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="13"/>
-      <c r="Q14" s="2" t="s">
-        <v>47</v>
-      </c>
+      <c r="K14" s="14"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="13"/>
       <c r="R14" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20">
-      <c r="A15" s="11">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
+      <c r="A15" s="11"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
@@ -1322,20 +1363,18 @@
       <c r="H15" s="13"/>
       <c r="I15" s="12"/>
       <c r="J15" s="14"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="13"/>
-      <c r="Q15" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="K15" s="14"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="13"/>
       <c r="R15" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20">
-      <c r="A16" s="11">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
+      <c r="A16" s="11"/>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
@@ -1345,20 +1384,18 @@
       <c r="H16" s="13"/>
       <c r="I16" s="12"/>
       <c r="J16" s="14"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="13"/>
-      <c r="Q16" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="K16" s="14"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="13"/>
       <c r="R16" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="11">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" s="11"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -1368,20 +1405,18 @@
       <c r="H17" s="13"/>
       <c r="I17" s="12"/>
       <c r="J17" s="14"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="13"/>
-      <c r="Q17" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="K17" s="14"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="13"/>
       <c r="R17" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="11">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" s="11"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -1391,20 +1426,18 @@
       <c r="H18" s="13"/>
       <c r="I18" s="12"/>
       <c r="J18" s="14"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="13"/>
-      <c r="Q18" s="2" t="s">
-        <v>51</v>
-      </c>
+      <c r="K18" s="14"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="13"/>
       <c r="R18" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="11">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19" s="11"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -1414,20 +1447,18 @@
       <c r="H19" s="13"/>
       <c r="I19" s="12"/>
       <c r="J19" s="14"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="13"/>
-      <c r="Q19" s="2" t="s">
-        <v>52</v>
-      </c>
+      <c r="K19" s="14"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="13"/>
       <c r="R19" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="11">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" s="11"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -1437,17 +1468,15 @@
       <c r="H20" s="13"/>
       <c r="I20" s="12"/>
       <c r="J20" s="14"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="13"/>
-      <c r="Q20" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21" s="11">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
+      <c r="K20" s="14"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="13"/>
+      <c r="R20" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="A21" s="11"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -1457,17 +1486,15 @@
       <c r="H21" s="13"/>
       <c r="I21" s="12"/>
       <c r="J21" s="14"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="13"/>
-      <c r="Q21" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22" s="11">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
+      <c r="K21" s="14"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="13"/>
+      <c r="R21" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" s="11"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -1477,17 +1504,15 @@
       <c r="H22" s="13"/>
       <c r="I22" s="12"/>
       <c r="J22" s="14"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="13"/>
-      <c r="Q22" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="11">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
+      <c r="K22" s="14"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="13"/>
+      <c r="R22" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" s="11"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -1497,17 +1522,15 @@
       <c r="H23" s="13"/>
       <c r="I23" s="12"/>
       <c r="J23" s="14"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="13"/>
-      <c r="Q23" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24" s="11">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
+      <c r="K23" s="14"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="13"/>
+      <c r="R23" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="A24" s="11"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -1517,17 +1540,15 @@
       <c r="H24" s="13"/>
       <c r="I24" s="12"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="13"/>
-      <c r="Q24" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
-      <c r="A25" s="11">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
+      <c r="K24" s="14"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="13"/>
+      <c r="R24" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" s="11"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -1537,17 +1558,15 @@
       <c r="H25" s="13"/>
       <c r="I25" s="12"/>
       <c r="J25" s="14"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="13"/>
-      <c r="Q25" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
-      <c r="A26" s="11">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
+      <c r="K25" s="14"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="13"/>
+      <c r="R25" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" s="11"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
@@ -1557,17 +1576,15 @@
       <c r="H26" s="13"/>
       <c r="I26" s="12"/>
       <c r="J26" s="14"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="13"/>
-      <c r="Q26" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
-      <c r="A27" s="11">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
+      <c r="K26" s="14"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="13"/>
+      <c r="R26" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" s="11"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
@@ -1577,17 +1594,15 @@
       <c r="H27" s="13"/>
       <c r="I27" s="12"/>
       <c r="J27" s="14"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="13"/>
-      <c r="Q27" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18">
-      <c r="A28" s="11">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
+      <c r="K27" s="14"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="13"/>
+      <c r="R27" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
+      <c r="A28" s="11"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
@@ -1597,17 +1612,15 @@
       <c r="H28" s="13"/>
       <c r="I28" s="12"/>
       <c r="J28" s="14"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="13"/>
-      <c r="Q28" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18">
-      <c r="A29" s="11">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
+      <c r="K28" s="14"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="13"/>
+      <c r="R28" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
+      <c r="A29" s="11"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
@@ -1617,17 +1630,15 @@
       <c r="H29" s="13"/>
       <c r="I29" s="12"/>
       <c r="J29" s="14"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="13"/>
-      <c r="Q29" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18">
-      <c r="A30" s="11">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
+      <c r="K29" s="14"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="13"/>
+      <c r="R29" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="A30" s="11"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
@@ -1637,17 +1648,15 @@
       <c r="H30" s="13"/>
       <c r="I30" s="12"/>
       <c r="J30" s="14"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="13"/>
-      <c r="Q30" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18">
-      <c r="A31" s="11">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
+      <c r="K30" s="14"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="13"/>
+      <c r="R30" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
+      <c r="A31" s="11"/>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
@@ -1657,17 +1666,15 @@
       <c r="H31" s="13"/>
       <c r="I31" s="12"/>
       <c r="J31" s="14"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="13"/>
-      <c r="Q31" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18">
-      <c r="A32" s="11">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
+      <c r="K31" s="14"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="13"/>
+      <c r="R31" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="A32" s="11"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
@@ -1677,17 +1684,15 @@
       <c r="H32" s="13"/>
       <c r="I32" s="12"/>
       <c r="J32" s="14"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="13"/>
-      <c r="Q32" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17">
-      <c r="A33" s="11">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
+      <c r="K32" s="14"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="13"/>
+      <c r="R32" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33" s="11"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
@@ -1697,17 +1702,15 @@
       <c r="H33" s="13"/>
       <c r="I33" s="12"/>
       <c r="J33" s="14"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="13"/>
-      <c r="Q33" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17">
-      <c r="A34" s="11">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
+      <c r="K33" s="14"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="13"/>
+      <c r="R33" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="A34" s="11"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
@@ -1717,17 +1720,15 @@
       <c r="H34" s="13"/>
       <c r="I34" s="12"/>
       <c r="J34" s="14"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="13"/>
-      <c r="Q34" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17">
-      <c r="A35" s="11">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
+      <c r="K34" s="14"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="13"/>
+      <c r="R34" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35" s="11"/>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
@@ -1737,17 +1738,15 @@
       <c r="H35" s="13"/>
       <c r="I35" s="12"/>
       <c r="J35" s="14"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="13"/>
-      <c r="Q35" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17">
-      <c r="A36" s="11">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
+      <c r="K35" s="14"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="13"/>
+      <c r="R35" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="A36" s="11"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
@@ -1757,17 +1756,15 @@
       <c r="H36" s="13"/>
       <c r="I36" s="12"/>
       <c r="J36" s="14"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="13"/>
-      <c r="Q36" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17">
-      <c r="A37" s="11">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
+      <c r="K36" s="14"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="13"/>
+      <c r="R36" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
+      <c r="A37" s="11"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
@@ -1777,17 +1774,15 @@
       <c r="H37" s="13"/>
       <c r="I37" s="12"/>
       <c r="J37" s="14"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="13"/>
-      <c r="Q37" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17">
-      <c r="A38" s="11">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
+      <c r="K37" s="14"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="13"/>
+      <c r="R37" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
+      <c r="A38" s="11"/>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
@@ -1797,14 +1792,12 @@
       <c r="H38" s="13"/>
       <c r="I38" s="12"/>
       <c r="J38" s="14"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="13"/>
-    </row>
-    <row r="39" spans="1:17">
-      <c r="A39" s="11">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
+      <c r="K38" s="14"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="13"/>
+    </row>
+    <row r="39" spans="1:18">
+      <c r="A39" s="11"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
@@ -1814,14 +1807,12 @@
       <c r="H39" s="13"/>
       <c r="I39" s="12"/>
       <c r="J39" s="14"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="13"/>
-    </row>
-    <row r="40" spans="1:17">
-      <c r="A40" s="11">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
+      <c r="K39" s="14"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="13"/>
+    </row>
+    <row r="40" spans="1:18">
+      <c r="A40" s="11"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
@@ -1831,14 +1822,12 @@
       <c r="H40" s="13"/>
       <c r="I40" s="12"/>
       <c r="J40" s="14"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="13"/>
-    </row>
-    <row r="41" spans="1:17">
-      <c r="A41" s="11">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
+      <c r="K40" s="14"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="13"/>
+    </row>
+    <row r="41" spans="1:18">
+      <c r="A41" s="11"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
@@ -1848,14 +1837,12 @@
       <c r="H41" s="13"/>
       <c r="I41" s="12"/>
       <c r="J41" s="14"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="13"/>
-    </row>
-    <row r="42" spans="1:17">
-      <c r="A42" s="11">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
+      <c r="K41" s="14"/>
+      <c r="L41" s="15"/>
+      <c r="M41" s="13"/>
+    </row>
+    <row r="42" spans="1:18">
+      <c r="A42" s="11"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
@@ -1865,14 +1852,12 @@
       <c r="H42" s="13"/>
       <c r="I42" s="12"/>
       <c r="J42" s="14"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="13"/>
-    </row>
-    <row r="43" spans="1:17">
-      <c r="A43" s="11">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
+      <c r="K42" s="14"/>
+      <c r="L42" s="15"/>
+      <c r="M42" s="13"/>
+    </row>
+    <row r="43" spans="1:18">
+      <c r="A43" s="11"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
@@ -1882,14 +1867,12 @@
       <c r="H43" s="13"/>
       <c r="I43" s="12"/>
       <c r="J43" s="14"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="13"/>
-    </row>
-    <row r="44" spans="1:17">
-      <c r="A44" s="11">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
+      <c r="K43" s="14"/>
+      <c r="L43" s="15"/>
+      <c r="M43" s="13"/>
+    </row>
+    <row r="44" spans="1:18">
+      <c r="A44" s="11"/>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
@@ -1899,14 +1882,12 @@
       <c r="H44" s="13"/>
       <c r="I44" s="12"/>
       <c r="J44" s="14"/>
-      <c r="K44" s="15"/>
-      <c r="L44" s="13"/>
-    </row>
-    <row r="45" spans="1:17">
-      <c r="A45" s="11">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
+      <c r="K44" s="14"/>
+      <c r="L44" s="15"/>
+      <c r="M44" s="13"/>
+    </row>
+    <row r="45" spans="1:18">
+      <c r="A45" s="11"/>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
@@ -1916,14 +1897,12 @@
       <c r="H45" s="13"/>
       <c r="I45" s="12"/>
       <c r="J45" s="14"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="13"/>
-    </row>
-    <row r="46" spans="1:17">
-      <c r="A46" s="11">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
+      <c r="K45" s="14"/>
+      <c r="L45" s="15"/>
+      <c r="M45" s="13"/>
+    </row>
+    <row r="46" spans="1:18">
+      <c r="A46" s="11"/>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
@@ -1933,14 +1912,12 @@
       <c r="H46" s="13"/>
       <c r="I46" s="12"/>
       <c r="J46" s="14"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="13"/>
-    </row>
-    <row r="47" spans="1:17">
-      <c r="A47" s="11">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
+      <c r="K46" s="14"/>
+      <c r="L46" s="15"/>
+      <c r="M46" s="13"/>
+    </row>
+    <row r="47" spans="1:18">
+      <c r="A47" s="11"/>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
@@ -1950,14 +1927,12 @@
       <c r="H47" s="13"/>
       <c r="I47" s="12"/>
       <c r="J47" s="14"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="13"/>
-    </row>
-    <row r="48" spans="1:17">
-      <c r="A48" s="11">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
+      <c r="K47" s="14"/>
+      <c r="L47" s="15"/>
+      <c r="M47" s="13"/>
+    </row>
+    <row r="48" spans="1:18">
+      <c r="A48" s="11"/>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
@@ -1967,14 +1942,12 @@
       <c r="H48" s="13"/>
       <c r="I48" s="12"/>
       <c r="J48" s="14"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="13"/>
-    </row>
-    <row r="49" spans="1:12">
-      <c r="A49" s="11">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
+      <c r="K48" s="14"/>
+      <c r="L48" s="15"/>
+      <c r="M48" s="13"/>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="11"/>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
@@ -1984,14 +1957,12 @@
       <c r="H49" s="13"/>
       <c r="I49" s="12"/>
       <c r="J49" s="14"/>
-      <c r="K49" s="15"/>
-      <c r="L49" s="13"/>
-    </row>
-    <row r="50" spans="1:12">
-      <c r="A50" s="11">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
+      <c r="K49" s="14"/>
+      <c r="L49" s="15"/>
+      <c r="M49" s="13"/>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50" s="11"/>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
@@ -2001,14 +1972,12 @@
       <c r="H50" s="13"/>
       <c r="I50" s="12"/>
       <c r="J50" s="14"/>
-      <c r="K50" s="15"/>
-      <c r="L50" s="13"/>
-    </row>
-    <row r="51" spans="1:12">
-      <c r="A51" s="11">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
+      <c r="K50" s="14"/>
+      <c r="L50" s="15"/>
+      <c r="M50" s="13"/>
+    </row>
+    <row r="51" spans="1:13">
+      <c r="A51" s="11"/>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>
@@ -2018,14 +1987,12 @@
       <c r="H51" s="13"/>
       <c r="I51" s="12"/>
       <c r="J51" s="14"/>
-      <c r="K51" s="15"/>
-      <c r="L51" s="13"/>
-    </row>
-    <row r="52" spans="1:12">
-      <c r="A52" s="11">
-        <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
+      <c r="K51" s="14"/>
+      <c r="L51" s="15"/>
+      <c r="M51" s="13"/>
+    </row>
+    <row r="52" spans="1:13">
+      <c r="A52" s="11"/>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
       <c r="D52" s="12"/>
@@ -2035,14 +2002,12 @@
       <c r="H52" s="13"/>
       <c r="I52" s="12"/>
       <c r="J52" s="14"/>
-      <c r="K52" s="15"/>
-      <c r="L52" s="13"/>
-    </row>
-    <row r="53" spans="1:12">
-      <c r="A53" s="11">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
+      <c r="K52" s="14"/>
+      <c r="L52" s="15"/>
+      <c r="M52" s="13"/>
+    </row>
+    <row r="53" spans="1:13">
+      <c r="A53" s="11"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
       <c r="D53" s="12"/>
@@ -2052,29 +2017,30 @@
       <c r="H53" s="13"/>
       <c r="I53" s="12"/>
       <c r="J53" s="14"/>
-      <c r="K53" s="15"/>
-      <c r="L53" s="13"/>
+      <c r="K53" s="14"/>
+      <c r="L53" s="15"/>
+      <c r="M53" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B53" xr:uid="{EA80D64E-578A-4FE2-B978-0712AFDAAEE6}">
-      <formula1>$O$2:$O$3</formula1>
+      <formula1>$P$2:$P$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C53" xr:uid="{A88927D6-C705-42EA-93F9-56044FBF1090}">
-      <formula1>$P$2:$P$9</formula1>
+      <formula1>$Q$2:$Q$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F53" xr:uid="{B197848D-F103-4380-83AB-2CDAAF2AFD3C}">
-      <formula1>$S$2:$S$7</formula1>
+      <formula1>$T$2:$T$7</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H53" xr:uid="{4A1BC11C-DA03-43AB-9BCE-E2B3D7ABF0B6}">
-      <formula1>$O$8:$O$9</formula1>
+      <formula1>$P$8:$P$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E53" xr:uid="{269CC43C-2462-4F32-A11C-04284C405092}">
-      <formula1>$R$2:$R$43</formula1>
+      <formula1>$S$2:$S$43</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D53" xr:uid="{2F6AB2AA-CDCC-4A9C-BBFD-3B4002AE4F9B}">
-      <formula1>$Q$2:$Q$61</formula1>
+      <formula1>$R$2:$R$61</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/AddressableResource/Data/Excels/QuestData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/QuestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2CF0C0E-3C80-4FEB-9213-338DF1C46197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03806A70-C718-43BB-8CF7-51DE660E5C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="5" spans="1:21">
       <c r="A5" s="11">
-        <f t="shared" ref="A5:A53" si="0">ROW()-3</f>
+        <f t="shared" ref="A5:A7" si="0">ROW()-3</f>
         <v>2</v>
       </c>
       <c r="B5" s="12" t="s">

--- a/Assets/AddressableResource/Data/Excels/QuestData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/QuestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03806A70-C718-43BB-8CF7-51DE660E5C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E9B84E-F26F-45BE-8FDD-4F3E1A43149F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="105">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -368,6 +368,18 @@
   </si>
   <si>
     <t>특정 점수 등에 도달에 사용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>redeem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리딤 코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>디코 봇 연동코드</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -474,7 +486,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -519,6 +531,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -826,7 +841,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="17.25"/>
   <cols>
     <col min="1" max="1" width="19.625" style="3" customWidth="1"/>
@@ -840,17 +855,18 @@
     <col min="11" max="11" width="19.25" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="9" customWidth="1"/>
     <col min="13" max="13" width="9" style="5" customWidth="1"/>
-    <col min="14" max="15" width="12.75" style="2" customWidth="1"/>
-    <col min="16" max="16" width="14.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="42.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="42.5" style="2" customWidth="1"/>
-    <col min="20" max="20" width="11.75" style="9" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="10.625" style="9"/>
-    <col min="23" max="16384" width="10.625" style="2"/>
+    <col min="14" max="14" width="18" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="12.75" style="2" customWidth="1"/>
+    <col min="17" max="17" width="14.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="42.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="42.5" style="2" customWidth="1"/>
+    <col min="21" max="21" width="11.75" style="9" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="10.625" style="9"/>
+    <col min="24" max="16384" width="10.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -890,24 +906,27 @@
       <c r="M1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U1" s="2"/>
-    </row>
-    <row r="2" spans="1:21">
+      <c r="V1" s="2"/>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -947,24 +966,27 @@
       <c r="M2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="N2" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="U2" s="2"/>
-    </row>
-    <row r="3" spans="1:21">
+      <c r="V2" s="2"/>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3" s="6" t="s">
         <v>13</v>
       </c>
@@ -1004,24 +1026,27 @@
       <c r="M3" s="7">
         <v>1</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="N3" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="U3" s="2"/>
-    </row>
-    <row r="4" spans="1:21">
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4" s="11">
         <f>ROW()-3</f>
         <v>1</v>
@@ -1060,21 +1085,22 @@
       <c r="M4" s="13">
         <v>1</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="N4" s="13"/>
+      <c r="R4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="T4" s="2" t="s">
+      <c r="U4" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="U4" s="2"/>
-    </row>
-    <row r="5" spans="1:21">
+      <c r="V4" s="2"/>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" s="11">
         <f t="shared" ref="A5:A7" si="0">ROW()-3</f>
         <v>2</v>
@@ -1113,21 +1139,22 @@
       <c r="M5" s="13">
         <v>1</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="N5" s="13"/>
+      <c r="R5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="S5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="T5" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="T5" s="2" t="s">
+      <c r="U5" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" spans="1:21">
+      <c r="V5" s="2"/>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1146,21 +1173,22 @@
       <c r="K6" s="14"/>
       <c r="L6" s="15"/>
       <c r="M6" s="13"/>
-      <c r="Q6" s="2" t="s">
+      <c r="N6" s="13"/>
+      <c r="R6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="U6" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="U6" s="2"/>
-    </row>
-    <row r="7" spans="1:21">
+      <c r="V6" s="2"/>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1179,20 +1207,21 @@
       <c r="K7" s="14"/>
       <c r="L7" s="15"/>
       <c r="M7" s="13"/>
-      <c r="Q7" s="2" t="s">
+      <c r="N7" s="13"/>
+      <c r="R7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="T7" s="9" t="s">
+      <c r="U7" s="9" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:22">
       <c r="A8" s="11"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -1206,20 +1235,21 @@
       <c r="K8" s="14"/>
       <c r="L8" s="15"/>
       <c r="M8" s="13"/>
-      <c r="P8" s="9" t="b">
+      <c r="N8" s="13"/>
+      <c r="Q8" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="S8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:22">
       <c r="A9" s="11"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -1233,20 +1263,21 @@
       <c r="K9" s="14"/>
       <c r="L9" s="15"/>
       <c r="M9" s="13"/>
-      <c r="P9" s="9" t="b">
+      <c r="N9" s="13"/>
+      <c r="Q9" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="R9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="R9" s="2" t="s">
+      <c r="S9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:22">
       <c r="A10" s="11"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -1260,15 +1291,16 @@
       <c r="K10" s="14"/>
       <c r="L10" s="15"/>
       <c r="M10" s="13"/>
-      <c r="P10" s="9"/>
-      <c r="R10" s="2" t="s">
+      <c r="N10" s="13"/>
+      <c r="Q10" s="9"/>
+      <c r="S10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="S10" s="2" t="s">
+      <c r="T10" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:22">
       <c r="A11" s="11"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -1282,14 +1314,15 @@
       <c r="K11" s="14"/>
       <c r="L11" s="15"/>
       <c r="M11" s="13"/>
-      <c r="R11" s="2" t="s">
+      <c r="N11" s="13"/>
+      <c r="S11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="S11" s="2" t="s">
+      <c r="T11" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:22">
       <c r="A12" s="11"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -1303,14 +1336,15 @@
       <c r="K12" s="14"/>
       <c r="L12" s="15"/>
       <c r="M12" s="13"/>
-      <c r="R12" s="2" t="s">
+      <c r="N12" s="13"/>
+      <c r="S12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="S12" s="2" t="s">
+      <c r="T12" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:22">
       <c r="A13" s="11"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -1324,14 +1358,15 @@
       <c r="K13" s="14"/>
       <c r="L13" s="15"/>
       <c r="M13" s="13"/>
-      <c r="R13" s="2" t="s">
+      <c r="N13" s="13"/>
+      <c r="S13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="S13" s="2" t="s">
+      <c r="T13" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:22">
       <c r="A14" s="11"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -1345,14 +1380,15 @@
       <c r="K14" s="14"/>
       <c r="L14" s="15"/>
       <c r="M14" s="13"/>
-      <c r="R14" s="2" t="s">
+      <c r="N14" s="13"/>
+      <c r="S14" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="S14" s="2" t="s">
+      <c r="T14" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:22">
       <c r="A15" s="11"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -1366,14 +1402,15 @@
       <c r="K15" s="14"/>
       <c r="L15" s="15"/>
       <c r="M15" s="13"/>
-      <c r="R15" s="2" t="s">
+      <c r="N15" s="13"/>
+      <c r="S15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="S15" s="2" t="s">
+      <c r="T15" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:22">
       <c r="A16" s="11"/>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
@@ -1387,14 +1424,15 @@
       <c r="K16" s="14"/>
       <c r="L16" s="15"/>
       <c r="M16" s="13"/>
-      <c r="R16" s="2" t="s">
+      <c r="N16" s="13"/>
+      <c r="S16" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="S16" s="2" t="s">
+      <c r="T16" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:20">
       <c r="A17" s="11"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -1408,14 +1446,15 @@
       <c r="K17" s="14"/>
       <c r="L17" s="15"/>
       <c r="M17" s="13"/>
-      <c r="R17" s="2" t="s">
+      <c r="N17" s="13"/>
+      <c r="S17" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="S17" s="2" t="s">
+      <c r="T17" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:20">
       <c r="A18" s="11"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
@@ -1429,14 +1468,15 @@
       <c r="K18" s="14"/>
       <c r="L18" s="15"/>
       <c r="M18" s="13"/>
-      <c r="R18" s="2" t="s">
+      <c r="N18" s="13"/>
+      <c r="S18" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="S18" s="2" t="s">
+      <c r="T18" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:20">
       <c r="A19" s="11"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
@@ -1450,14 +1490,15 @@
       <c r="K19" s="14"/>
       <c r="L19" s="15"/>
       <c r="M19" s="13"/>
-      <c r="R19" s="2" t="s">
+      <c r="N19" s="13"/>
+      <c r="S19" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="S19" s="2" t="s">
+      <c r="T19" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:20">
       <c r="A20" s="11"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -1471,11 +1512,12 @@
       <c r="K20" s="14"/>
       <c r="L20" s="15"/>
       <c r="M20" s="13"/>
-      <c r="R20" s="2" t="s">
+      <c r="N20" s="13"/>
+      <c r="S20" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:20">
       <c r="A21" s="11"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -1489,11 +1531,12 @@
       <c r="K21" s="14"/>
       <c r="L21" s="15"/>
       <c r="M21" s="13"/>
-      <c r="R21" s="2" t="s">
+      <c r="N21" s="13"/>
+      <c r="S21" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:20">
       <c r="A22" s="11"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -1507,11 +1550,12 @@
       <c r="K22" s="14"/>
       <c r="L22" s="15"/>
       <c r="M22" s="13"/>
-      <c r="R22" s="2" t="s">
+      <c r="N22" s="13"/>
+      <c r="S22" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:20">
       <c r="A23" s="11"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -1525,11 +1569,12 @@
       <c r="K23" s="14"/>
       <c r="L23" s="15"/>
       <c r="M23" s="13"/>
-      <c r="R23" s="2" t="s">
+      <c r="N23" s="13"/>
+      <c r="S23" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:20">
       <c r="A24" s="11"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -1543,11 +1588,12 @@
       <c r="K24" s="14"/>
       <c r="L24" s="15"/>
       <c r="M24" s="13"/>
-      <c r="R24" s="2" t="s">
+      <c r="N24" s="13"/>
+      <c r="S24" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:20">
       <c r="A25" s="11"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -1561,11 +1607,12 @@
       <c r="K25" s="14"/>
       <c r="L25" s="15"/>
       <c r="M25" s="13"/>
-      <c r="R25" s="2" t="s">
+      <c r="N25" s="13"/>
+      <c r="S25" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:20">
       <c r="A26" s="11"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -1579,11 +1626,12 @@
       <c r="K26" s="14"/>
       <c r="L26" s="15"/>
       <c r="M26" s="13"/>
-      <c r="R26" s="2" t="s">
+      <c r="N26" s="13"/>
+      <c r="S26" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:20">
       <c r="A27" s="11"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
@@ -1597,11 +1645,12 @@
       <c r="K27" s="14"/>
       <c r="L27" s="15"/>
       <c r="M27" s="13"/>
-      <c r="R27" s="2" t="s">
+      <c r="N27" s="13"/>
+      <c r="S27" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:20">
       <c r="A28" s="11"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
@@ -1615,11 +1664,12 @@
       <c r="K28" s="14"/>
       <c r="L28" s="15"/>
       <c r="M28" s="13"/>
-      <c r="R28" s="2" t="s">
+      <c r="N28" s="13"/>
+      <c r="S28" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:20">
       <c r="A29" s="11"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -1633,11 +1683,12 @@
       <c r="K29" s="14"/>
       <c r="L29" s="15"/>
       <c r="M29" s="13"/>
-      <c r="R29" s="2" t="s">
+      <c r="N29" s="13"/>
+      <c r="S29" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:20">
       <c r="A30" s="11"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -1651,11 +1702,12 @@
       <c r="K30" s="14"/>
       <c r="L30" s="15"/>
       <c r="M30" s="13"/>
-      <c r="R30" s="2" t="s">
+      <c r="N30" s="13"/>
+      <c r="S30" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:20">
       <c r="A31" s="11"/>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
@@ -1669,11 +1721,12 @@
       <c r="K31" s="14"/>
       <c r="L31" s="15"/>
       <c r="M31" s="13"/>
-      <c r="R31" s="2" t="s">
+      <c r="N31" s="13"/>
+      <c r="S31" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:20">
       <c r="A32" s="11"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
@@ -1687,11 +1740,12 @@
       <c r="K32" s="14"/>
       <c r="L32" s="15"/>
       <c r="M32" s="13"/>
-      <c r="R32" s="2" t="s">
+      <c r="N32" s="13"/>
+      <c r="S32" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:18">
+    <row r="33" spans="1:19">
       <c r="A33" s="11"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -1705,11 +1759,12 @@
       <c r="K33" s="14"/>
       <c r="L33" s="15"/>
       <c r="M33" s="13"/>
-      <c r="R33" s="2" t="s">
+      <c r="N33" s="13"/>
+      <c r="S33" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:18">
+    <row r="34" spans="1:19">
       <c r="A34" s="11"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
@@ -1723,11 +1778,12 @@
       <c r="K34" s="14"/>
       <c r="L34" s="15"/>
       <c r="M34" s="13"/>
-      <c r="R34" s="2" t="s">
+      <c r="N34" s="13"/>
+      <c r="S34" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:18">
+    <row r="35" spans="1:19">
       <c r="A35" s="11"/>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
@@ -1741,11 +1797,12 @@
       <c r="K35" s="14"/>
       <c r="L35" s="15"/>
       <c r="M35" s="13"/>
-      <c r="R35" s="2" t="s">
+      <c r="N35" s="13"/>
+      <c r="S35" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:18">
+    <row r="36" spans="1:19">
       <c r="A36" s="11"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -1759,11 +1816,12 @@
       <c r="K36" s="14"/>
       <c r="L36" s="15"/>
       <c r="M36" s="13"/>
-      <c r="R36" s="2" t="s">
+      <c r="N36" s="13"/>
+      <c r="S36" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="37" spans="1:18">
+    <row r="37" spans="1:19">
       <c r="A37" s="11"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
@@ -1777,11 +1835,12 @@
       <c r="K37" s="14"/>
       <c r="L37" s="15"/>
       <c r="M37" s="13"/>
-      <c r="R37" s="2" t="s">
+      <c r="N37" s="13"/>
+      <c r="S37" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="1:18">
+    <row r="38" spans="1:19">
       <c r="A38" s="11"/>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
@@ -1795,8 +1854,9 @@
       <c r="K38" s="14"/>
       <c r="L38" s="15"/>
       <c r="M38" s="13"/>
-    </row>
-    <row r="39" spans="1:18">
+      <c r="N38" s="13"/>
+    </row>
+    <row r="39" spans="1:19">
       <c r="A39" s="11"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
@@ -1810,8 +1870,9 @@
       <c r="K39" s="14"/>
       <c r="L39" s="15"/>
       <c r="M39" s="13"/>
-    </row>
-    <row r="40" spans="1:18">
+      <c r="N39" s="13"/>
+    </row>
+    <row r="40" spans="1:19">
       <c r="A40" s="11"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -1825,8 +1886,9 @@
       <c r="K40" s="14"/>
       <c r="L40" s="15"/>
       <c r="M40" s="13"/>
-    </row>
-    <row r="41" spans="1:18">
+      <c r="N40" s="13"/>
+    </row>
+    <row r="41" spans="1:19">
       <c r="A41" s="11"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -1840,8 +1902,9 @@
       <c r="K41" s="14"/>
       <c r="L41" s="15"/>
       <c r="M41" s="13"/>
-    </row>
-    <row r="42" spans="1:18">
+      <c r="N41" s="13"/>
+    </row>
+    <row r="42" spans="1:19">
       <c r="A42" s="11"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
@@ -1855,8 +1918,9 @@
       <c r="K42" s="14"/>
       <c r="L42" s="15"/>
       <c r="M42" s="13"/>
-    </row>
-    <row r="43" spans="1:18">
+      <c r="N42" s="13"/>
+    </row>
+    <row r="43" spans="1:19">
       <c r="A43" s="11"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
@@ -1870,8 +1934,9 @@
       <c r="K43" s="14"/>
       <c r="L43" s="15"/>
       <c r="M43" s="13"/>
-    </row>
-    <row r="44" spans="1:18">
+      <c r="N43" s="13"/>
+    </row>
+    <row r="44" spans="1:19">
       <c r="A44" s="11"/>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
@@ -1885,8 +1950,9 @@
       <c r="K44" s="14"/>
       <c r="L44" s="15"/>
       <c r="M44" s="13"/>
-    </row>
-    <row r="45" spans="1:18">
+      <c r="N44" s="13"/>
+    </row>
+    <row r="45" spans="1:19">
       <c r="A45" s="11"/>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
@@ -1900,8 +1966,9 @@
       <c r="K45" s="14"/>
       <c r="L45" s="15"/>
       <c r="M45" s="13"/>
-    </row>
-    <row r="46" spans="1:18">
+      <c r="N45" s="13"/>
+    </row>
+    <row r="46" spans="1:19">
       <c r="A46" s="11"/>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
@@ -1915,8 +1982,9 @@
       <c r="K46" s="14"/>
       <c r="L46" s="15"/>
       <c r="M46" s="13"/>
-    </row>
-    <row r="47" spans="1:18">
+      <c r="N46" s="13"/>
+    </row>
+    <row r="47" spans="1:19">
       <c r="A47" s="11"/>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
@@ -1930,8 +1998,9 @@
       <c r="K47" s="14"/>
       <c r="L47" s="15"/>
       <c r="M47" s="13"/>
-    </row>
-    <row r="48" spans="1:18">
+      <c r="N47" s="13"/>
+    </row>
+    <row r="48" spans="1:19">
       <c r="A48" s="11"/>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
@@ -1945,8 +2014,9 @@
       <c r="K48" s="14"/>
       <c r="L48" s="15"/>
       <c r="M48" s="13"/>
-    </row>
-    <row r="49" spans="1:13">
+      <c r="N48" s="13"/>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" s="11"/>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
@@ -1960,8 +2030,9 @@
       <c r="K49" s="14"/>
       <c r="L49" s="15"/>
       <c r="M49" s="13"/>
-    </row>
-    <row r="50" spans="1:13">
+      <c r="N49" s="13"/>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" s="11"/>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
@@ -1975,8 +2046,9 @@
       <c r="K50" s="14"/>
       <c r="L50" s="15"/>
       <c r="M50" s="13"/>
-    </row>
-    <row r="51" spans="1:13">
+      <c r="N50" s="13"/>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" s="11"/>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
@@ -1990,8 +2062,9 @@
       <c r="K51" s="14"/>
       <c r="L51" s="15"/>
       <c r="M51" s="13"/>
-    </row>
-    <row r="52" spans="1:13">
+      <c r="N51" s="13"/>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" s="11"/>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
@@ -2005,8 +2078,9 @@
       <c r="K52" s="14"/>
       <c r="L52" s="15"/>
       <c r="M52" s="13"/>
-    </row>
-    <row r="53" spans="1:13">
+      <c r="N52" s="13"/>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" s="11"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -2020,27 +2094,28 @@
       <c r="K53" s="14"/>
       <c r="L53" s="15"/>
       <c r="M53" s="13"/>
+      <c r="N53" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B53" xr:uid="{EA80D64E-578A-4FE2-B978-0712AFDAAEE6}">
-      <formula1>$P$2:$P$3</formula1>
+      <formula1>$Q$2:$Q$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C53" xr:uid="{A88927D6-C705-42EA-93F9-56044FBF1090}">
-      <formula1>$Q$2:$Q$9</formula1>
+      <formula1>$R$2:$R$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F53" xr:uid="{B197848D-F103-4380-83AB-2CDAAF2AFD3C}">
-      <formula1>$T$2:$T$7</formula1>
+      <formula1>$U$2:$U$7</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H53" xr:uid="{4A1BC11C-DA03-43AB-9BCE-E2B3D7ABF0B6}">
-      <formula1>$P$8:$P$9</formula1>
+      <formula1>$Q$8:$Q$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E53" xr:uid="{269CC43C-2462-4F32-A11C-04284C405092}">
-      <formula1>$S$2:$S$43</formula1>
+      <formula1>$T$2:$T$43</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D53" xr:uid="{2F6AB2AA-CDCC-4A9C-BBFD-3B4002AE4F9B}">
-      <formula1>$R$2:$R$61</formula1>
+      <formula1>$S$2:$S$61</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/AddressableResource/Data/Excels/QuestData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/QuestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E9B84E-F26F-45BE-8FDD-4F3E1A43149F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE7E5D38-6534-477B-816A-566839D36571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="104">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,10 +51,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>coin</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -83,10 +79,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내용. {0}을 {1}하라</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>#1</t>
   </si>
   <si>
@@ -294,10 +286,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>필요.. 한가?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>E_PlayEndRoll</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -381,6 +369,13 @@
   <si>
     <t>디코 봇 연동코드</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가뷁ABCabc1230</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_PlayEndRoll</t>
   </si>
 </sst>
 </file>
@@ -841,32 +836,33 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:W53"/>
+  <dimension ref="A1:V53"/>
   <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="17.25"/>
   <cols>
     <col min="1" max="1" width="19.625" style="3" customWidth="1"/>
     <col min="2" max="2" width="15" style="3" customWidth="1"/>
-    <col min="3" max="5" width="30" style="3" customWidth="1"/>
+    <col min="3" max="3" width="30" style="3" customWidth="1"/>
+    <col min="4" max="4" width="42.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30" style="3" customWidth="1"/>
     <col min="6" max="6" width="19.5" style="5" customWidth="1"/>
     <col min="7" max="7" width="11.5" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30" style="2" customWidth="1"/>
-    <col min="10" max="10" width="28.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9" style="9" customWidth="1"/>
-    <col min="13" max="13" width="9" style="5" customWidth="1"/>
-    <col min="14" max="14" width="18" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="12.75" style="2" customWidth="1"/>
-    <col min="17" max="17" width="14.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="42.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="42.5" style="2" customWidth="1"/>
-    <col min="21" max="21" width="11.75" style="9" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="10.625" style="9"/>
-    <col min="24" max="16384" width="10.625" style="2"/>
+    <col min="9" max="9" width="28.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" style="9" customWidth="1"/>
+    <col min="12" max="12" width="9" style="5" customWidth="1"/>
+    <col min="13" max="13" width="18" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="12.75" style="2" customWidth="1"/>
+    <col min="16" max="16" width="14.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="42.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="42.5" style="2" customWidth="1"/>
+    <col min="20" max="20" width="11.75" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="10.625" style="9"/>
+    <col min="23" max="16384" width="10.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -874,13 +870,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>2</v>
@@ -889,121 +885,115 @@
         <v>3</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I1" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>4</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U1" s="2"/>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V1" s="2"/>
-    </row>
-    <row r="2" spans="1:22">
-      <c r="A2" s="6" t="s">
+      <c r="B2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>9</v>
-      </c>
       <c r="G2" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>94</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="P2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="U2" s="2"/>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="V2" s="2"/>
-    </row>
-    <row r="3" spans="1:22">
-      <c r="A3" s="6" t="s">
-        <v>13</v>
-      </c>
       <c r="B3" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G3" s="7">
         <v>1</v>
@@ -1011,60 +1001,57 @@
       <c r="H3" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="I3" s="6" t="s">
-        <v>79</v>
+      <c r="I3" s="8" t="s">
+        <v>98</v>
       </c>
       <c r="J3" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="K3" s="10">
+        <v>100</v>
+      </c>
+      <c r="L3" s="7">
+        <v>1</v>
+      </c>
+      <c r="M3" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="K3" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="L3" s="10">
-        <v>100</v>
-      </c>
-      <c r="M3" s="7">
-        <v>1</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>104</v>
+      <c r="P3" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="V3" s="2"/>
-    </row>
-    <row r="4" spans="1:22">
+        <v>68</v>
+      </c>
+      <c r="U3" s="2"/>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" s="11">
         <f>ROW()-3</f>
         <v>1</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G4" s="13">
         <v>1</v>
@@ -1072,53 +1059,54 @@
       <c r="H4" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="I4" s="12"/>
+      <c r="I4" s="14">
+        <v>0</v>
+      </c>
       <c r="J4" s="14">
-        <v>0</v>
-      </c>
-      <c r="K4" s="14">
-        <v>100</v>
-      </c>
-      <c r="L4" s="15">
-        <v>100</v>
+        <v>5</v>
+      </c>
+      <c r="K4" s="15">
+        <v>10</v>
+      </c>
+      <c r="L4" s="13">
+        <v>1</v>
       </c>
       <c r="M4" s="13">
-        <v>1</v>
-      </c>
-      <c r="N4" s="13"/>
+        <v>123</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="R4" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="V4" s="2"/>
-    </row>
-    <row r="5" spans="1:22">
+        <v>69</v>
+      </c>
+      <c r="U4" s="2"/>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" s="11">
-        <f t="shared" ref="A5:A7" si="0">ROW()-3</f>
+        <f t="shared" ref="A5:A11" si="0">ROW()-3</f>
         <v>2</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G5" s="13">
         <v>1</v>
@@ -1126,203 +1114,344 @@
       <c r="H5" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="I5" s="12"/>
+      <c r="I5" s="14">
+        <v>3500</v>
+      </c>
       <c r="J5" s="14">
-        <v>3500</v>
-      </c>
-      <c r="K5" s="14">
         <v>1</v>
       </c>
-      <c r="L5" s="15">
-        <v>100</v>
-      </c>
-      <c r="M5" s="13">
-        <v>1</v>
-      </c>
-      <c r="N5" s="13"/>
+      <c r="K5" s="15">
+        <v>10</v>
+      </c>
+      <c r="L5" s="13">
+        <v>2</v>
+      </c>
+      <c r="M5" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="R5" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V5" s="2"/>
-    </row>
-    <row r="6" spans="1:22">
+        <v>70</v>
+      </c>
+      <c r="U5" s="2"/>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
+      <c r="B6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>42</v>
+      </c>
       <c r="E6" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
+        <v>80</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="13">
+        <v>1</v>
+      </c>
+      <c r="H6" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="14">
+        <v>0</v>
+      </c>
+      <c r="J6" s="14">
+        <v>1000</v>
+      </c>
+      <c r="K6" s="15">
+        <v>11</v>
+      </c>
+      <c r="L6" s="13">
+        <v>3</v>
+      </c>
+      <c r="M6" s="13">
+        <v>22</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="R6" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="V6" s="2"/>
-    </row>
-    <row r="7" spans="1:22">
+        <v>71</v>
+      </c>
+      <c r="U6" s="2"/>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
+      <c r="B7" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="E7" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="15"/>
+        <v>85</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="13">
+        <v>1</v>
+      </c>
+      <c r="H7" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="14">
+        <v>0</v>
+      </c>
+      <c r="J7" s="14">
+        <v>300</v>
+      </c>
+      <c r="K7" s="15">
+        <v>12</v>
+      </c>
+      <c r="L7" s="13">
+        <v>4</v>
+      </c>
       <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
+      <c r="Q7" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="R7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" s="11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="13">
+        <v>1</v>
+      </c>
+      <c r="H8" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="14">
+        <v>0</v>
+      </c>
+      <c r="J8" s="14">
+        <v>99999999</v>
+      </c>
+      <c r="K8" s="15">
+        <v>13</v>
+      </c>
+      <c r="L8" s="13">
+        <v>5</v>
+      </c>
+      <c r="M8" s="13"/>
+      <c r="P8" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="11">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="13">
+        <v>1</v>
+      </c>
+      <c r="H9" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="14">
+        <v>0</v>
+      </c>
+      <c r="J9" s="14">
+        <v>3</v>
+      </c>
+      <c r="K9" s="15">
+        <v>14</v>
+      </c>
+      <c r="L9" s="13">
+        <v>6</v>
+      </c>
+      <c r="M9" s="13"/>
+      <c r="P9" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="R9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="S9" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="11">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="13">
+        <v>1</v>
+      </c>
+      <c r="H10" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="14">
+        <v>0</v>
+      </c>
+      <c r="J10" s="14">
+        <v>9000</v>
+      </c>
+      <c r="K10" s="15">
+        <v>15</v>
+      </c>
+      <c r="L10" s="13">
+        <v>7</v>
+      </c>
+      <c r="M10" s="13">
+        <v>13</v>
+      </c>
+      <c r="P10" s="9"/>
+      <c r="R10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" s="11">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="13">
+        <v>2</v>
+      </c>
+      <c r="H11" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="14">
+        <v>0</v>
+      </c>
+      <c r="J11" s="14">
+        <v>1</v>
+      </c>
+      <c r="K11" s="15">
+        <v>16</v>
+      </c>
+      <c r="L11" s="13">
+        <v>8</v>
+      </c>
+      <c r="M11" s="13">
+        <v>12</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S11" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="U7" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="Q8" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="Q9" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="Q10" s="9"/>
-      <c r="S10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="S11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22">
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" s="11"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -1331,20 +1460,19 @@
       <c r="F12" s="13"/>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
-      <c r="I12" s="12"/>
+      <c r="I12" s="14"/>
       <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="13"/>
       <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
+      <c r="R12" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="S12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13" s="11"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -1353,20 +1481,19 @@
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
-      <c r="I13" s="12"/>
+      <c r="I13" s="14"/>
       <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="13"/>
       <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
+      <c r="R13" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="S13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14" s="11"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -1375,20 +1502,19 @@
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
-      <c r="I14" s="12"/>
+      <c r="I14" s="14"/>
       <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="13"/>
       <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
+      <c r="R14" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="S14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15" s="11"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -1397,20 +1523,19 @@
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
-      <c r="I15" s="12"/>
+      <c r="I15" s="14"/>
       <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="13"/>
       <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
+      <c r="R15" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="S15" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" s="11"/>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
@@ -1419,20 +1544,19 @@
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
-      <c r="I16" s="12"/>
+      <c r="I16" s="14"/>
       <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="13"/>
       <c r="M16" s="13"/>
-      <c r="N16" s="13"/>
+      <c r="R16" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="S16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T16" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" s="11"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -1441,20 +1565,19 @@
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
-      <c r="I17" s="12"/>
+      <c r="I17" s="14"/>
       <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="13"/>
       <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
+      <c r="R17" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="S17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" s="11"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
@@ -1463,20 +1586,19 @@
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
-      <c r="I18" s="12"/>
+      <c r="I18" s="14"/>
       <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="13"/>
       <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
+      <c r="R18" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="S18" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" s="11"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
@@ -1485,20 +1607,19 @@
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
-      <c r="I19" s="12"/>
+      <c r="I19" s="14"/>
       <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="13"/>
       <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
+      <c r="R19" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="S19" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" s="11"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -1507,17 +1628,16 @@
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
-      <c r="I20" s="12"/>
+      <c r="I20" s="14"/>
       <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="13"/>
       <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="S20" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20">
+      <c r="R20" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" s="11"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -1526,17 +1646,16 @@
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
-      <c r="I21" s="12"/>
+      <c r="I21" s="14"/>
       <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="13"/>
       <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="S21" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20">
+      <c r="R21" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" s="11"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -1545,17 +1664,16 @@
       <c r="F22" s="13"/>
       <c r="G22" s="13"/>
       <c r="H22" s="13"/>
-      <c r="I22" s="12"/>
+      <c r="I22" s="14"/>
       <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="13"/>
       <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
-      <c r="S22" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
+      <c r="R22" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
       <c r="A23" s="11"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -1564,17 +1682,16 @@
       <c r="F23" s="13"/>
       <c r="G23" s="13"/>
       <c r="H23" s="13"/>
-      <c r="I23" s="12"/>
+      <c r="I23" s="14"/>
       <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="13"/>
       <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="S23" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
+      <c r="R23" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
       <c r="A24" s="11"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -1583,17 +1700,16 @@
       <c r="F24" s="13"/>
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
-      <c r="I24" s="12"/>
+      <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="13"/>
       <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-      <c r="S24" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20">
+      <c r="R24" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
       <c r="A25" s="11"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -1602,17 +1718,16 @@
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
       <c r="H25" s="13"/>
-      <c r="I25" s="12"/>
+      <c r="I25" s="14"/>
       <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="13"/>
       <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
-      <c r="S25" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20">
+      <c r="R25" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" s="11"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -1621,17 +1736,16 @@
       <c r="F26" s="13"/>
       <c r="G26" s="13"/>
       <c r="H26" s="13"/>
-      <c r="I26" s="12"/>
+      <c r="I26" s="14"/>
       <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="13"/>
       <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
-      <c r="S26" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20">
+      <c r="R26" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
       <c r="A27" s="11"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
@@ -1640,17 +1754,16 @@
       <c r="F27" s="13"/>
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
-      <c r="I27" s="12"/>
+      <c r="I27" s="14"/>
       <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="13"/>
       <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
-      <c r="S27" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20">
+      <c r="R27" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
       <c r="A28" s="11"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
@@ -1659,17 +1772,16 @@
       <c r="F28" s="13"/>
       <c r="G28" s="13"/>
       <c r="H28" s="13"/>
-      <c r="I28" s="12"/>
+      <c r="I28" s="14"/>
       <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="13"/>
       <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
-      <c r="S28" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20">
+      <c r="R28" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
       <c r="A29" s="11"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -1678,17 +1790,16 @@
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
       <c r="H29" s="13"/>
-      <c r="I29" s="12"/>
+      <c r="I29" s="14"/>
       <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="13"/>
       <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="S29" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20">
+      <c r="R29" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
       <c r="A30" s="11"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -1697,17 +1808,16 @@
       <c r="F30" s="13"/>
       <c r="G30" s="13"/>
       <c r="H30" s="13"/>
-      <c r="I30" s="12"/>
+      <c r="I30" s="14"/>
       <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="13"/>
       <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
-      <c r="S30" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20">
+      <c r="R30" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
       <c r="A31" s="11"/>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
@@ -1716,17 +1826,16 @@
       <c r="F31" s="13"/>
       <c r="G31" s="13"/>
       <c r="H31" s="13"/>
-      <c r="I31" s="12"/>
+      <c r="I31" s="14"/>
       <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="13"/>
       <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
-      <c r="S31" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20">
+      <c r="R31" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
       <c r="A32" s="11"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
@@ -1735,17 +1844,16 @@
       <c r="F32" s="13"/>
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
-      <c r="I32" s="12"/>
+      <c r="I32" s="14"/>
       <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="13"/>
       <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
-      <c r="S32" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19">
+      <c r="R32" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
       <c r="A33" s="11"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -1754,17 +1862,16 @@
       <c r="F33" s="13"/>
       <c r="G33" s="13"/>
       <c r="H33" s="13"/>
-      <c r="I33" s="12"/>
+      <c r="I33" s="14"/>
       <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="13"/>
       <c r="M33" s="13"/>
-      <c r="N33" s="13"/>
-      <c r="S33" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19">
+      <c r="R33" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
       <c r="A34" s="11"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
@@ -1773,17 +1880,16 @@
       <c r="F34" s="13"/>
       <c r="G34" s="13"/>
       <c r="H34" s="13"/>
-      <c r="I34" s="12"/>
+      <c r="I34" s="14"/>
       <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="13"/>
       <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
-      <c r="S34" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19">
+      <c r="R34" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
       <c r="A35" s="11"/>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
@@ -1792,17 +1898,16 @@
       <c r="F35" s="13"/>
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
-      <c r="I35" s="12"/>
+      <c r="I35" s="14"/>
       <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="13"/>
       <c r="M35" s="13"/>
-      <c r="N35" s="13"/>
-      <c r="S35" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19">
+      <c r="R35" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
       <c r="A36" s="11"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -1811,17 +1916,16 @@
       <c r="F36" s="13"/>
       <c r="G36" s="13"/>
       <c r="H36" s="13"/>
-      <c r="I36" s="12"/>
+      <c r="I36" s="14"/>
       <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="13"/>
       <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
-      <c r="S36" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19">
+      <c r="R36" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
       <c r="A37" s="11"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
@@ -1830,17 +1934,16 @@
       <c r="F37" s="13"/>
       <c r="G37" s="13"/>
       <c r="H37" s="13"/>
-      <c r="I37" s="12"/>
+      <c r="I37" s="14"/>
       <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="13"/>
       <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
-      <c r="S37" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19">
+      <c r="R37" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
       <c r="A38" s="11"/>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
@@ -1849,14 +1952,13 @@
       <c r="F38" s="13"/>
       <c r="G38" s="13"/>
       <c r="H38" s="13"/>
-      <c r="I38" s="12"/>
+      <c r="I38" s="14"/>
       <c r="J38" s="14"/>
-      <c r="K38" s="14"/>
-      <c r="L38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="13"/>
       <c r="M38" s="13"/>
-      <c r="N38" s="13"/>
-    </row>
-    <row r="39" spans="1:19">
+    </row>
+    <row r="39" spans="1:18">
       <c r="A39" s="11"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
@@ -1865,14 +1967,13 @@
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
       <c r="H39" s="13"/>
-      <c r="I39" s="12"/>
+      <c r="I39" s="14"/>
       <c r="J39" s="14"/>
-      <c r="K39" s="14"/>
-      <c r="L39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="13"/>
       <c r="M39" s="13"/>
-      <c r="N39" s="13"/>
-    </row>
-    <row r="40" spans="1:19">
+    </row>
+    <row r="40" spans="1:18">
       <c r="A40" s="11"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -1881,14 +1982,13 @@
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
       <c r="H40" s="13"/>
-      <c r="I40" s="12"/>
+      <c r="I40" s="14"/>
       <c r="J40" s="14"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="13"/>
       <c r="M40" s="13"/>
-      <c r="N40" s="13"/>
-    </row>
-    <row r="41" spans="1:19">
+    </row>
+    <row r="41" spans="1:18">
       <c r="A41" s="11"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -1897,14 +1997,13 @@
       <c r="F41" s="13"/>
       <c r="G41" s="13"/>
       <c r="H41" s="13"/>
-      <c r="I41" s="12"/>
+      <c r="I41" s="14"/>
       <c r="J41" s="14"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="13"/>
       <c r="M41" s="13"/>
-      <c r="N41" s="13"/>
-    </row>
-    <row r="42" spans="1:19">
+    </row>
+    <row r="42" spans="1:18">
       <c r="A42" s="11"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
@@ -1913,14 +2012,13 @@
       <c r="F42" s="13"/>
       <c r="G42" s="13"/>
       <c r="H42" s="13"/>
-      <c r="I42" s="12"/>
+      <c r="I42" s="14"/>
       <c r="J42" s="14"/>
-      <c r="K42" s="14"/>
-      <c r="L42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="13"/>
       <c r="M42" s="13"/>
-      <c r="N42" s="13"/>
-    </row>
-    <row r="43" spans="1:19">
+    </row>
+    <row r="43" spans="1:18">
       <c r="A43" s="11"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
@@ -1929,14 +2027,13 @@
       <c r="F43" s="13"/>
       <c r="G43" s="13"/>
       <c r="H43" s="13"/>
-      <c r="I43" s="12"/>
+      <c r="I43" s="14"/>
       <c r="J43" s="14"/>
-      <c r="K43" s="14"/>
-      <c r="L43" s="15"/>
+      <c r="K43" s="15"/>
+      <c r="L43" s="13"/>
       <c r="M43" s="13"/>
-      <c r="N43" s="13"/>
-    </row>
-    <row r="44" spans="1:19">
+    </row>
+    <row r="44" spans="1:18">
       <c r="A44" s="11"/>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
@@ -1945,14 +2042,13 @@
       <c r="F44" s="13"/>
       <c r="G44" s="13"/>
       <c r="H44" s="13"/>
-      <c r="I44" s="12"/>
+      <c r="I44" s="14"/>
       <c r="J44" s="14"/>
-      <c r="K44" s="14"/>
-      <c r="L44" s="15"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="13"/>
       <c r="M44" s="13"/>
-      <c r="N44" s="13"/>
-    </row>
-    <row r="45" spans="1:19">
+    </row>
+    <row r="45" spans="1:18">
       <c r="A45" s="11"/>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
@@ -1961,14 +2057,13 @@
       <c r="F45" s="13"/>
       <c r="G45" s="13"/>
       <c r="H45" s="13"/>
-      <c r="I45" s="12"/>
+      <c r="I45" s="14"/>
       <c r="J45" s="14"/>
-      <c r="K45" s="14"/>
-      <c r="L45" s="15"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="13"/>
       <c r="M45" s="13"/>
-      <c r="N45" s="13"/>
-    </row>
-    <row r="46" spans="1:19">
+    </row>
+    <row r="46" spans="1:18">
       <c r="A46" s="11"/>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
@@ -1977,14 +2072,13 @@
       <c r="F46" s="13"/>
       <c r="G46" s="13"/>
       <c r="H46" s="13"/>
-      <c r="I46" s="12"/>
+      <c r="I46" s="14"/>
       <c r="J46" s="14"/>
-      <c r="K46" s="14"/>
-      <c r="L46" s="15"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="13"/>
       <c r="M46" s="13"/>
-      <c r="N46" s="13"/>
-    </row>
-    <row r="47" spans="1:19">
+    </row>
+    <row r="47" spans="1:18">
       <c r="A47" s="11"/>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
@@ -1993,14 +2087,13 @@
       <c r="F47" s="13"/>
       <c r="G47" s="13"/>
       <c r="H47" s="13"/>
-      <c r="I47" s="12"/>
+      <c r="I47" s="14"/>
       <c r="J47" s="14"/>
-      <c r="K47" s="14"/>
-      <c r="L47" s="15"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="13"/>
       <c r="M47" s="13"/>
-      <c r="N47" s="13"/>
-    </row>
-    <row r="48" spans="1:19">
+    </row>
+    <row r="48" spans="1:18">
       <c r="A48" s="11"/>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
@@ -2009,14 +2102,13 @@
       <c r="F48" s="13"/>
       <c r="G48" s="13"/>
       <c r="H48" s="13"/>
-      <c r="I48" s="12"/>
+      <c r="I48" s="14"/>
       <c r="J48" s="14"/>
-      <c r="K48" s="14"/>
-      <c r="L48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="13"/>
       <c r="M48" s="13"/>
-      <c r="N48" s="13"/>
-    </row>
-    <row r="49" spans="1:14">
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="11"/>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
@@ -2025,14 +2117,13 @@
       <c r="F49" s="13"/>
       <c r="G49" s="13"/>
       <c r="H49" s="13"/>
-      <c r="I49" s="12"/>
+      <c r="I49" s="14"/>
       <c r="J49" s="14"/>
-      <c r="K49" s="14"/>
-      <c r="L49" s="15"/>
+      <c r="K49" s="15"/>
+      <c r="L49" s="13"/>
       <c r="M49" s="13"/>
-      <c r="N49" s="13"/>
-    </row>
-    <row r="50" spans="1:14">
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="11"/>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
@@ -2041,14 +2132,13 @@
       <c r="F50" s="13"/>
       <c r="G50" s="13"/>
       <c r="H50" s="13"/>
-      <c r="I50" s="12"/>
+      <c r="I50" s="14"/>
       <c r="J50" s="14"/>
-      <c r="K50" s="14"/>
-      <c r="L50" s="15"/>
+      <c r="K50" s="15"/>
+      <c r="L50" s="13"/>
       <c r="M50" s="13"/>
-      <c r="N50" s="13"/>
-    </row>
-    <row r="51" spans="1:14">
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="11"/>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
@@ -2057,14 +2147,13 @@
       <c r="F51" s="13"/>
       <c r="G51" s="13"/>
       <c r="H51" s="13"/>
-      <c r="I51" s="12"/>
+      <c r="I51" s="14"/>
       <c r="J51" s="14"/>
-      <c r="K51" s="14"/>
-      <c r="L51" s="15"/>
+      <c r="K51" s="15"/>
+      <c r="L51" s="13"/>
       <c r="M51" s="13"/>
-      <c r="N51" s="13"/>
-    </row>
-    <row r="52" spans="1:14">
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="11"/>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
@@ -2073,14 +2162,13 @@
       <c r="F52" s="13"/>
       <c r="G52" s="13"/>
       <c r="H52" s="13"/>
-      <c r="I52" s="12"/>
+      <c r="I52" s="14"/>
       <c r="J52" s="14"/>
-      <c r="K52" s="14"/>
-      <c r="L52" s="15"/>
+      <c r="K52" s="15"/>
+      <c r="L52" s="13"/>
       <c r="M52" s="13"/>
-      <c r="N52" s="13"/>
-    </row>
-    <row r="53" spans="1:14">
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="11"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -2089,33 +2177,32 @@
       <c r="F53" s="13"/>
       <c r="G53" s="13"/>
       <c r="H53" s="13"/>
-      <c r="I53" s="12"/>
+      <c r="I53" s="14"/>
       <c r="J53" s="14"/>
-      <c r="K53" s="14"/>
-      <c r="L53" s="15"/>
+      <c r="K53" s="15"/>
+      <c r="L53" s="13"/>
       <c r="M53" s="13"/>
-      <c r="N53" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B53" xr:uid="{EA80D64E-578A-4FE2-B978-0712AFDAAEE6}">
-      <formula1>$Q$2:$Q$3</formula1>
+      <formula1>$P$2:$P$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C53" xr:uid="{A88927D6-C705-42EA-93F9-56044FBF1090}">
-      <formula1>$R$2:$R$9</formula1>
+      <formula1>$Q$2:$Q$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F53" xr:uid="{B197848D-F103-4380-83AB-2CDAAF2AFD3C}">
-      <formula1>$U$2:$U$7</formula1>
+      <formula1>$T$2:$T$7</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H53" xr:uid="{4A1BC11C-DA03-43AB-9BCE-E2B3D7ABF0B6}">
-      <formula1>$Q$8:$Q$9</formula1>
+      <formula1>$P$8:$P$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E53" xr:uid="{269CC43C-2462-4F32-A11C-04284C405092}">
-      <formula1>$T$2:$T$43</formula1>
+      <formula1>$S$2:$S$43</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D53" xr:uid="{2F6AB2AA-CDCC-4A9C-BBFD-3B4002AE4F9B}">
-      <formula1>$S$2:$S$61</formula1>
+      <formula1>$R$2:$R$61</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/AddressableResource/Data/Excels/QuestData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/QuestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8D5C35-F990-4AD0-B069-7F16A0B72F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D04AC2-80DD-4A52-BF19-9540F3B3425F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>

--- a/Assets/AddressableResource/Data/Excels/QuestData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/QuestData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D04AC2-80DD-4A52-BF19-9540F3B3425F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470B6161-F72F-4F8F-9D29-308AF40AE6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="104">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -363,6 +363,18 @@
   </si>
   <si>
     <t>TNKU4PLAY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preQuestId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이전 퀘스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이전꺼 깨야 보임</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -824,7 +836,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:U342"/>
+  <dimension ref="A1:V342"/>
   <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="17.25"/>
   <cols>
     <col min="1" max="1" width="19.625" style="3" customWidth="1"/>
@@ -832,24 +844,26 @@
     <col min="3" max="3" width="30" style="3" customWidth="1"/>
     <col min="4" max="4" width="42.5" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" style="3" customWidth="1"/>
-    <col min="6" max="6" width="19.5" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15" style="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.25" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.625" style="9" customWidth="1"/>
     <col min="11" max="11" width="9" style="5" customWidth="1"/>
     <col min="12" max="12" width="18" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="12.75" style="2" customWidth="1"/>
-    <col min="15" max="15" width="14.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="42.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="42.5" style="2" customWidth="1"/>
-    <col min="19" max="19" width="11.75" style="9" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="10.625" style="9"/>
-    <col min="22" max="16384" width="10.625" style="2"/>
+    <col min="13" max="13" width="18" style="5" customWidth="1"/>
+    <col min="14" max="14" width="12.75" style="2" customWidth="1"/>
+    <col min="15" max="15" width="19.5" style="5" customWidth="1"/>
+    <col min="16" max="16" width="14.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="42.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="42.5" style="2" customWidth="1"/>
+    <col min="20" max="20" width="11.75" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="10.625" style="9"/>
+    <col min="23" max="16384" width="10.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -866,10 +880,10 @@
         <v>73</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>9</v>
@@ -886,24 +900,28 @@
       <c r="L1" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="2"/>
+      <c r="O1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="2"/>
-    </row>
-    <row r="2" spans="1:20">
+      <c r="U1" s="2"/>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
@@ -920,10 +938,10 @@
         <v>74</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>13</v>
@@ -940,24 +958,28 @@
       <c r="L2" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="2"/>
+      <c r="O2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="T2" s="2"/>
-    </row>
-    <row r="3" spans="1:20">
+      <c r="U2" s="2"/>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
@@ -973,11 +995,11 @@
       <c r="E3" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" s="7">
-        <v>1</v>
+      <c r="F3" s="7">
+        <v>1</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="H3" s="7" t="b">
         <v>0</v>
@@ -994,24 +1016,28 @@
       <c r="L3" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>18</v>
+      <c r="M3" s="2"/>
+      <c r="O3" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="P3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="T3" s="2"/>
-    </row>
-    <row r="4" spans="1:20">
+      <c r="U3" s="2"/>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" s="11">
         <f>ROW()-4</f>
         <v>0</v>
@@ -1028,11 +1054,12 @@
       <c r="E4" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="13" t="s">
-        <v>67</v>
+      <c r="F4" s="13">
+        <v>1</v>
       </c>
       <c r="G4" s="13">
-        <v>1</v>
+        <f>F4-1</f>
+        <v>0</v>
       </c>
       <c r="H4" s="13" t="b">
         <v>0</v>
@@ -1047,21 +1074,25 @@
         <v>1</v>
       </c>
       <c r="L4" s="13"/>
-      <c r="P4" s="2" t="s">
+      <c r="M4" s="2"/>
+      <c r="O4" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="T4" s="2"/>
-    </row>
-    <row r="5" spans="1:20">
+      <c r="U4" s="2"/>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" s="11">
         <f t="shared" ref="A5:A68" si="0">ROW()-4</f>
         <v>1</v>
@@ -1078,11 +1109,12 @@
       <c r="E5" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>67</v>
+      <c r="F5" s="13">
+        <v>2</v>
       </c>
       <c r="G5" s="13">
-        <v>2</v>
+        <f t="shared" ref="G5:G68" si="1">F5-1</f>
+        <v>1</v>
       </c>
       <c r="H5" s="13" t="b">
         <v>0</v>
@@ -1096,21 +1128,25 @@
       <c r="K5" s="13">
         <v>3</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="M5" s="2"/>
+      <c r="O5" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="R5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="S5" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="T5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="T5" s="2"/>
-    </row>
-    <row r="6" spans="1:20">
+      <c r="U5" s="2"/>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" s="11">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1127,11 +1163,12 @@
       <c r="E6" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>68</v>
+      <c r="F6" s="13">
+        <v>3</v>
       </c>
       <c r="G6" s="13">
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="H6" s="13" t="b">
         <v>0</v>
@@ -1145,21 +1182,25 @@
       <c r="K6" s="13">
         <v>5</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="M6" s="2"/>
+      <c r="O6" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="T6" s="2"/>
-    </row>
-    <row r="7" spans="1:20">
+      <c r="U6" s="2"/>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1176,11 +1217,12 @@
       <c r="E7" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>68</v>
+      <c r="F7" s="13">
+        <v>4</v>
       </c>
       <c r="G7" s="13">
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="H7" s="13" t="b">
         <v>0</v>
@@ -1194,20 +1236,24 @@
       <c r="K7" s="13">
         <v>8</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="M7" s="2"/>
+      <c r="O7" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="S7" s="9" t="s">
+      <c r="T7" s="9" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:21">
       <c r="A8" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1224,11 +1270,12 @@
       <c r="E8" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="13" t="s">
-        <v>69</v>
+      <c r="F8" s="13">
+        <v>5</v>
       </c>
       <c r="G8" s="13">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="H8" s="13" t="b">
         <v>0</v>
@@ -1242,20 +1289,23 @@
       <c r="K8" s="13">
         <v>13</v>
       </c>
-      <c r="O8" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="P8" s="2" t="s">
+      <c r="O8" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="P8" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="S8" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:21">
       <c r="A9" s="11">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1272,11 +1322,12 @@
       <c r="E9" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F9" s="13" t="s">
-        <v>72</v>
+      <c r="F9" s="13">
+        <v>6</v>
       </c>
       <c r="G9" s="13">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="H9" s="13" t="b">
         <v>0</v>
@@ -1290,20 +1341,23 @@
       <c r="K9" s="13">
         <v>38</v>
       </c>
-      <c r="O9" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2" t="s">
+      <c r="O9" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="P9" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="R9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="R9" s="2" t="s">
+      <c r="S9" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:21">
       <c r="A10" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1320,11 +1374,12 @@
       <c r="E10" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>68</v>
+      <c r="F10" s="13">
+        <v>1</v>
       </c>
       <c r="G10" s="13">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H10" s="13" t="b">
         <v>0</v>
@@ -1338,15 +1393,18 @@
       <c r="K10" s="13">
         <v>1</v>
       </c>
-      <c r="O10" s="9"/>
-      <c r="Q10" s="2" t="s">
+      <c r="O10" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="P10" s="9"/>
+      <c r="R10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="S10" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:21">
       <c r="A11" s="11">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1363,11 +1421,12 @@
       <c r="E11" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>68</v>
+      <c r="F11" s="13">
+        <v>2</v>
       </c>
       <c r="G11" s="13">
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H11" s="13" t="b">
         <v>0</v>
@@ -1381,14 +1440,17 @@
       <c r="K11" s="5">
         <v>3</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="O11" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="R11" s="2" t="s">
+      <c r="S11" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:21">
       <c r="A12" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1405,11 +1467,12 @@
       <c r="E12" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>69</v>
+      <c r="F12" s="13">
+        <v>3</v>
       </c>
       <c r="G12" s="13">
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="H12" s="13" t="b">
         <v>0</v>
@@ -1423,14 +1486,17 @@
       <c r="K12" s="5">
         <v>5</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="O12" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="R12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R12" s="2" t="s">
+      <c r="S12" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:21">
       <c r="A13" s="11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1447,11 +1513,12 @@
       <c r="E13" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F13" s="13" t="s">
-        <v>70</v>
+      <c r="F13" s="13">
+        <v>4</v>
       </c>
       <c r="G13" s="13">
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="H13" s="13" t="b">
         <v>0</v>
@@ -1466,14 +1533,18 @@
         <v>8</v>
       </c>
       <c r="L13" s="13"/>
-      <c r="Q13" s="2" t="s">
+      <c r="M13" s="13"/>
+      <c r="O13" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="R13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R13" s="2" t="s">
+      <c r="S13" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:21">
       <c r="A14" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1490,11 +1561,12 @@
       <c r="E14" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>72</v>
+      <c r="F14" s="13">
+        <v>5</v>
       </c>
       <c r="G14" s="13">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="H14" s="13" t="b">
         <v>0</v>
@@ -1509,14 +1581,18 @@
         <v>23</v>
       </c>
       <c r="L14" s="13"/>
-      <c r="Q14" s="2" t="s">
+      <c r="M14" s="13"/>
+      <c r="O14" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="R14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="R14" s="2" t="s">
+      <c r="S14" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:21">
       <c r="A15" s="11">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1533,11 +1609,12 @@
       <c r="E15" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>67</v>
+      <c r="F15" s="13">
+        <v>1</v>
       </c>
       <c r="G15" s="13">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H15" s="13" t="b">
         <v>0</v>
@@ -1552,14 +1629,18 @@
         <v>1</v>
       </c>
       <c r="L15" s="13"/>
-      <c r="Q15" s="2" t="s">
+      <c r="M15" s="13"/>
+      <c r="O15" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="R15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="R15" s="2" t="s">
+      <c r="S15" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:21">
       <c r="A16" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1576,11 +1657,12 @@
       <c r="E16" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F16" s="13" t="s">
-        <v>67</v>
+      <c r="F16" s="13">
+        <v>2</v>
       </c>
       <c r="G16" s="13">
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H16" s="13" t="b">
         <v>0</v>
@@ -1595,14 +1677,18 @@
         <v>3</v>
       </c>
       <c r="L16" s="13"/>
-      <c r="Q16" s="2" t="s">
+      <c r="M16" s="13"/>
+      <c r="O16" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="R16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="R16" s="2" t="s">
+      <c r="S16" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:19">
       <c r="A17" s="11">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1619,11 +1705,12 @@
       <c r="E17" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="13" t="s">
-        <v>68</v>
+      <c r="F17" s="13">
+        <v>3</v>
       </c>
       <c r="G17" s="13">
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="H17" s="13" t="b">
         <v>0</v>
@@ -1638,14 +1725,18 @@
         <v>5</v>
       </c>
       <c r="L17" s="13"/>
-      <c r="Q17" s="2" t="s">
+      <c r="M17" s="13"/>
+      <c r="O17" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="R17" s="2" t="s">
+      <c r="S17" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:19">
       <c r="A18" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1662,11 +1753,12 @@
       <c r="E18" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="13" t="s">
-        <v>68</v>
+      <c r="F18" s="13">
+        <v>4</v>
       </c>
       <c r="G18" s="13">
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="H18" s="13" t="b">
         <v>0</v>
@@ -1681,14 +1773,18 @@
         <v>8</v>
       </c>
       <c r="L18" s="13"/>
-      <c r="Q18" s="2" t="s">
+      <c r="M18" s="13"/>
+      <c r="O18" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R18" s="2" t="s">
+      <c r="S18" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:19">
       <c r="A19" s="11">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1705,11 +1801,12 @@
       <c r="E19" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F19" s="13" t="s">
-        <v>69</v>
+      <c r="F19" s="13">
+        <v>5</v>
       </c>
       <c r="G19" s="13">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="H19" s="13" t="b">
         <v>0</v>
@@ -1724,14 +1821,18 @@
         <v>13</v>
       </c>
       <c r="L19" s="13"/>
-      <c r="Q19" s="2" t="s">
+      <c r="M19" s="13"/>
+      <c r="O19" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="R19" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="R19" s="2" t="s">
+      <c r="S19" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:19">
       <c r="A20" s="11">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1748,11 +1849,12 @@
       <c r="E20" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F20" s="13" t="s">
-        <v>72</v>
+      <c r="F20" s="13">
+        <v>6</v>
       </c>
       <c r="G20" s="13">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="H20" s="13" t="b">
         <v>0</v>
@@ -1767,11 +1869,15 @@
         <v>38</v>
       </c>
       <c r="L20" s="13"/>
-      <c r="Q20" s="2" t="s">
+      <c r="M20" s="13"/>
+      <c r="O20" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="R20" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:19">
       <c r="A21" s="11">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1788,11 +1894,12 @@
       <c r="E21" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F21" s="13" t="s">
-        <v>68</v>
+      <c r="F21" s="13">
+        <v>1</v>
       </c>
       <c r="G21" s="13">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H21" s="13" t="b">
         <v>0</v>
@@ -1807,11 +1914,15 @@
         <v>1</v>
       </c>
       <c r="L21" s="13"/>
-      <c r="Q21" s="2" t="s">
+      <c r="M21" s="13"/>
+      <c r="O21" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R21" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:19">
       <c r="A22" s="11">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1828,11 +1939,12 @@
       <c r="E22" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>68</v>
+      <c r="F22" s="13">
+        <v>2</v>
       </c>
       <c r="G22" s="13">
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H22" s="13" t="b">
         <v>0</v>
@@ -1847,11 +1959,15 @@
         <v>5</v>
       </c>
       <c r="L22" s="13"/>
-      <c r="Q22" s="2" t="s">
+      <c r="M22" s="13"/>
+      <c r="O22" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R22" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:19">
       <c r="A23" s="11">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1868,11 +1984,12 @@
       <c r="E23" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F23" s="13" t="s">
-        <v>68</v>
+      <c r="F23" s="13">
+        <v>3</v>
       </c>
       <c r="G23" s="13">
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="H23" s="13" t="b">
         <v>0</v>
@@ -1887,11 +2004,15 @@
         <v>8</v>
       </c>
       <c r="L23" s="13"/>
-      <c r="Q23" s="2" t="s">
+      <c r="M23" s="13"/>
+      <c r="O23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R23" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:19">
       <c r="A24" s="11">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1908,11 +2029,12 @@
       <c r="E24" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F24" s="13" t="s">
-        <v>68</v>
+      <c r="F24" s="13">
+        <v>4</v>
       </c>
       <c r="G24" s="13">
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="H24" s="13" t="b">
         <v>0</v>
@@ -1927,11 +2049,15 @@
         <v>13</v>
       </c>
       <c r="L24" s="13"/>
-      <c r="Q24" s="2" t="s">
+      <c r="M24" s="13"/>
+      <c r="O24" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R24" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:19">
       <c r="A25" s="11">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1948,11 +2074,12 @@
       <c r="E25" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F25" s="13" t="s">
-        <v>68</v>
+      <c r="F25" s="13">
+        <v>5</v>
       </c>
       <c r="G25" s="13">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="H25" s="13" t="b">
         <v>0</v>
@@ -1967,11 +2094,15 @@
         <v>38</v>
       </c>
       <c r="L25" s="13"/>
-      <c r="Q25" s="2" t="s">
+      <c r="M25" s="13"/>
+      <c r="O25" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R25" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:19">
       <c r="A26" s="11">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -1988,11 +2119,12 @@
       <c r="E26" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F26" s="13" t="s">
-        <v>67</v>
+      <c r="F26" s="13">
+        <v>1</v>
       </c>
       <c r="G26" s="13">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H26" s="13" t="b">
         <v>0</v>
@@ -2007,11 +2139,15 @@
         <v>1</v>
       </c>
       <c r="L26" s="13"/>
-      <c r="Q26" s="2" t="s">
+      <c r="M26" s="13"/>
+      <c r="O26" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="R26" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:19">
       <c r="A27" s="11">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2028,11 +2164,12 @@
       <c r="E27" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>67</v>
+      <c r="F27" s="13">
+        <v>2</v>
       </c>
       <c r="G27" s="13">
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H27" s="13" t="b">
         <v>0</v>
@@ -2047,11 +2184,15 @@
         <v>3</v>
       </c>
       <c r="L27" s="13"/>
-      <c r="Q27" s="2" t="s">
+      <c r="M27" s="13"/>
+      <c r="O27" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="R27" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:19">
       <c r="A28" s="11">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2068,11 +2209,12 @@
       <c r="E28" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>68</v>
+      <c r="F28" s="13">
+        <v>3</v>
       </c>
       <c r="G28" s="13">
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="H28" s="13" t="b">
         <v>0</v>
@@ -2087,11 +2229,15 @@
         <v>5</v>
       </c>
       <c r="L28" s="13"/>
-      <c r="Q28" s="2" t="s">
+      <c r="M28" s="13"/>
+      <c r="O28" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R28" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:19">
       <c r="A29" s="11">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2108,11 +2254,12 @@
       <c r="E29" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>68</v>
+      <c r="F29" s="13">
+        <v>4</v>
       </c>
       <c r="G29" s="13">
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="H29" s="13" t="b">
         <v>0</v>
@@ -2127,11 +2274,15 @@
         <v>8</v>
       </c>
       <c r="L29" s="13"/>
-      <c r="Q29" s="2" t="s">
+      <c r="M29" s="13"/>
+      <c r="O29" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R29" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:19">
       <c r="A30" s="11">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2148,11 +2299,12 @@
       <c r="E30" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>69</v>
+      <c r="F30" s="13">
+        <v>5</v>
       </c>
       <c r="G30" s="13">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="H30" s="13" t="b">
         <v>0</v>
@@ -2167,11 +2319,15 @@
         <v>13</v>
       </c>
       <c r="L30" s="13"/>
-      <c r="Q30" s="2" t="s">
+      <c r="M30" s="13"/>
+      <c r="O30" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="R30" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:19">
       <c r="A31" s="11">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2188,11 +2344,12 @@
       <c r="E31" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>72</v>
+      <c r="F31" s="13">
+        <v>6</v>
       </c>
       <c r="G31" s="13">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="H31" s="13" t="b">
         <v>0</v>
@@ -2207,11 +2364,15 @@
         <v>38</v>
       </c>
       <c r="L31" s="13"/>
-      <c r="Q31" s="2" t="s">
+      <c r="M31" s="13"/>
+      <c r="O31" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="R31" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:19">
       <c r="A32" s="11">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2228,11 +2389,12 @@
       <c r="E32" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F32" s="13" t="s">
-        <v>67</v>
+      <c r="F32" s="13">
+        <v>1</v>
       </c>
       <c r="G32" s="13">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H32" s="13" t="b">
         <v>0</v>
@@ -2247,11 +2409,15 @@
         <v>1</v>
       </c>
       <c r="L32" s="13"/>
-      <c r="Q32" s="2" t="s">
+      <c r="M32" s="13"/>
+      <c r="O32" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="R32" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:17">
+    <row r="33" spans="1:18">
       <c r="A33" s="11">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2268,11 +2434,12 @@
       <c r="E33" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>67</v>
+      <c r="F33" s="13">
+        <v>2</v>
       </c>
       <c r="G33" s="13">
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H33" s="13" t="b">
         <v>0</v>
@@ -2287,11 +2454,15 @@
         <v>1</v>
       </c>
       <c r="L33" s="13"/>
-      <c r="Q33" s="2" t="s">
+      <c r="M33" s="13"/>
+      <c r="O33" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="R33" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:17">
+    <row r="34" spans="1:18">
       <c r="A34" s="11">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2308,11 +2479,12 @@
       <c r="E34" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F34" s="13" t="s">
-        <v>68</v>
+      <c r="F34" s="13">
+        <v>3</v>
       </c>
       <c r="G34" s="13">
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="H34" s="13" t="b">
         <v>0</v>
@@ -2327,11 +2499,15 @@
         <v>2</v>
       </c>
       <c r="L34" s="13"/>
-      <c r="Q34" s="2" t="s">
+      <c r="M34" s="13"/>
+      <c r="O34" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R34" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:17">
+    <row r="35" spans="1:18">
       <c r="A35" s="11">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2348,11 +2524,12 @@
       <c r="E35" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F35" s="13" t="s">
-        <v>68</v>
+      <c r="F35" s="13">
+        <v>4</v>
       </c>
       <c r="G35" s="13">
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="H35" s="13" t="b">
         <v>0</v>
@@ -2367,11 +2544,15 @@
         <v>2</v>
       </c>
       <c r="L35" s="13"/>
-      <c r="Q35" s="2" t="s">
+      <c r="M35" s="13"/>
+      <c r="O35" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R35" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:17">
+    <row r="36" spans="1:18">
       <c r="A36" s="11">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2388,11 +2569,12 @@
       <c r="E36" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F36" s="13" t="s">
-        <v>69</v>
+      <c r="F36" s="13">
+        <v>5</v>
       </c>
       <c r="G36" s="13">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="H36" s="13" t="b">
         <v>0</v>
@@ -2407,11 +2589,15 @@
         <v>3</v>
       </c>
       <c r="L36" s="13"/>
-      <c r="Q36" s="2" t="s">
+      <c r="M36" s="13"/>
+      <c r="O36" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="R36" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:17">
+    <row r="37" spans="1:18">
       <c r="A37" s="11">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2428,11 +2614,12 @@
       <c r="E37" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F37" s="13" t="s">
-        <v>70</v>
+      <c r="F37" s="13">
+        <v>6</v>
       </c>
       <c r="G37" s="13">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="H37" s="13" t="b">
         <v>0</v>
@@ -2447,11 +2634,15 @@
         <v>5</v>
       </c>
       <c r="L37" s="13"/>
-      <c r="Q37" s="2" t="s">
+      <c r="M37" s="13"/>
+      <c r="O37" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="R37" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:17">
+    <row r="38" spans="1:18">
       <c r="A38" s="11">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2468,11 +2659,12 @@
       <c r="E38" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F38" s="13" t="s">
-        <v>70</v>
+      <c r="F38" s="13">
+        <v>7</v>
       </c>
       <c r="G38" s="13">
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="H38" s="13" t="b">
         <v>0</v>
@@ -2487,8 +2679,12 @@
         <v>8</v>
       </c>
       <c r="L38" s="13"/>
-    </row>
-    <row r="39" spans="1:17">
+      <c r="M38" s="13"/>
+      <c r="O38" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
       <c r="A39" s="11">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2505,11 +2701,12 @@
       <c r="E39" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F39" s="13" t="s">
-        <v>71</v>
+      <c r="F39" s="13">
+        <v>8</v>
       </c>
       <c r="G39" s="13">
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="H39" s="13" t="b">
         <v>0</v>
@@ -2524,8 +2721,12 @@
         <v>13</v>
       </c>
       <c r="L39" s="13"/>
-    </row>
-    <row r="40" spans="1:17">
+      <c r="M39" s="13"/>
+      <c r="O39" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
       <c r="A40" s="11">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -2542,11 +2743,12 @@
       <c r="E40" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F40" s="13" t="s">
-        <v>71</v>
+      <c r="F40" s="13">
+        <v>9</v>
       </c>
       <c r="G40" s="13">
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="H40" s="13" t="b">
         <v>0</v>
@@ -2561,8 +2763,12 @@
         <v>38</v>
       </c>
       <c r="L40" s="13"/>
-    </row>
-    <row r="41" spans="1:17">
+      <c r="M40" s="13"/>
+      <c r="O40" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
       <c r="A41" s="11">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -2579,11 +2785,12 @@
       <c r="E41" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F41" s="13" t="s">
-        <v>72</v>
+      <c r="F41" s="13">
+        <v>10</v>
       </c>
       <c r="G41" s="13">
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="H41" s="13" t="b">
         <v>0</v>
@@ -2598,8 +2805,12 @@
         <v>87</v>
       </c>
       <c r="L41" s="13"/>
-    </row>
-    <row r="42" spans="1:17">
+      <c r="M41" s="13"/>
+      <c r="O41" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
       <c r="A42" s="11">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -2616,11 +2827,12 @@
       <c r="E42" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F42" s="13" t="s">
-        <v>67</v>
+      <c r="F42" s="13">
+        <v>1</v>
       </c>
       <c r="G42" s="13">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H42" s="13" t="b">
         <v>0</v>
@@ -2635,8 +2847,12 @@
         <v>1</v>
       </c>
       <c r="L42" s="13"/>
-    </row>
-    <row r="43" spans="1:17">
+      <c r="M42" s="13"/>
+      <c r="O42" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
       <c r="A43" s="11">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -2653,11 +2869,12 @@
       <c r="E43" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F43" s="13" t="s">
-        <v>67</v>
+      <c r="F43" s="13">
+        <v>2</v>
       </c>
       <c r="G43" s="13">
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H43" s="13" t="b">
         <v>0</v>
@@ -2672,8 +2889,12 @@
         <v>2</v>
       </c>
       <c r="L43" s="13"/>
-    </row>
-    <row r="44" spans="1:17">
+      <c r="M43" s="13"/>
+      <c r="O43" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
       <c r="A44" s="11">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -2690,11 +2911,12 @@
       <c r="E44" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F44" s="13" t="s">
-        <v>68</v>
+      <c r="F44" s="13">
+        <v>3</v>
       </c>
       <c r="G44" s="13">
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="H44" s="13" t="b">
         <v>0</v>
@@ -2709,8 +2931,12 @@
         <v>3</v>
       </c>
       <c r="L44" s="13"/>
-    </row>
-    <row r="45" spans="1:17">
+      <c r="M44" s="13"/>
+      <c r="O44" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
       <c r="A45" s="11">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -2727,11 +2953,12 @@
       <c r="E45" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F45" s="13" t="s">
-        <v>68</v>
+      <c r="F45" s="13">
+        <v>4</v>
       </c>
       <c r="G45" s="13">
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="H45" s="13" t="b">
         <v>0</v>
@@ -2746,8 +2973,12 @@
         <v>5</v>
       </c>
       <c r="L45" s="13"/>
-    </row>
-    <row r="46" spans="1:17">
+      <c r="M45" s="13"/>
+      <c r="O45" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
       <c r="A46" s="11">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -2764,11 +2995,12 @@
       <c r="E46" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F46" s="13" t="s">
-        <v>69</v>
+      <c r="F46" s="13">
+        <v>5</v>
       </c>
       <c r="G46" s="13">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="H46" s="13" t="b">
         <v>0</v>
@@ -2783,8 +3015,12 @@
         <v>8</v>
       </c>
       <c r="L46" s="13"/>
-    </row>
-    <row r="47" spans="1:17">
+      <c r="M46" s="13"/>
+      <c r="O46" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
       <c r="A47" s="11">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -2801,11 +3037,12 @@
       <c r="E47" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F47" s="13" t="s">
-        <v>69</v>
+      <c r="F47" s="13">
+        <v>6</v>
       </c>
       <c r="G47" s="13">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="H47" s="13" t="b">
         <v>0</v>
@@ -2820,8 +3057,12 @@
         <v>8</v>
       </c>
       <c r="L47" s="13"/>
-    </row>
-    <row r="48" spans="1:17">
+      <c r="M47" s="13"/>
+      <c r="O47" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
       <c r="A48" s="11">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -2838,11 +3079,12 @@
       <c r="E48" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F48" s="13" t="s">
-        <v>70</v>
+      <c r="F48" s="13">
+        <v>7</v>
       </c>
       <c r="G48" s="13">
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="H48" s="13" t="b">
         <v>0</v>
@@ -2857,8 +3099,12 @@
         <v>13</v>
       </c>
       <c r="L48" s="13"/>
-    </row>
-    <row r="49" spans="1:12">
+      <c r="M48" s="13"/>
+      <c r="O48" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
       <c r="A49" s="11">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -2875,11 +3121,12 @@
       <c r="E49" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F49" s="13" t="s">
-        <v>71</v>
+      <c r="F49" s="13">
+        <v>8</v>
       </c>
       <c r="G49" s="13">
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="H49" s="13" t="b">
         <v>0</v>
@@ -2894,8 +3141,12 @@
         <v>13</v>
       </c>
       <c r="L49" s="13"/>
-    </row>
-    <row r="50" spans="1:12">
+      <c r="M49" s="13"/>
+      <c r="O49" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
       <c r="A50" s="11">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -2912,11 +3163,12 @@
       <c r="E50" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F50" s="13" t="s">
-        <v>72</v>
+      <c r="F50" s="13">
+        <v>9</v>
       </c>
       <c r="G50" s="13">
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="H50" s="13" t="b">
         <v>0</v>
@@ -2931,8 +3183,12 @@
         <v>38</v>
       </c>
       <c r="L50" s="13"/>
-    </row>
-    <row r="51" spans="1:12">
+      <c r="M50" s="13"/>
+      <c r="O50" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
       <c r="A51" s="11">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -2949,11 +3205,12 @@
       <c r="E51" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="F51" s="13" t="s">
-        <v>67</v>
+      <c r="F51" s="13">
+        <v>1</v>
       </c>
       <c r="G51" s="13">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H51" s="13" t="b">
         <v>0</v>
@@ -2968,8 +3225,12 @@
         <v>1</v>
       </c>
       <c r="L51" s="13"/>
-    </row>
-    <row r="52" spans="1:12">
+      <c r="M51" s="13"/>
+      <c r="O51" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52" s="11">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -2986,11 +3247,12 @@
       <c r="E52" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="F52" s="13" t="s">
-        <v>67</v>
+      <c r="F52" s="13">
+        <v>2</v>
       </c>
       <c r="G52" s="13">
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H52" s="13" t="b">
         <v>0</v>
@@ -3005,8 +3267,12 @@
         <v>2</v>
       </c>
       <c r="L52" s="13"/>
-    </row>
-    <row r="53" spans="1:12">
+      <c r="M52" s="13"/>
+      <c r="O52" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53" s="11">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -3023,11 +3289,12 @@
       <c r="E53" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="F53" s="13" t="s">
-        <v>68</v>
+      <c r="F53" s="13">
+        <v>3</v>
       </c>
       <c r="G53" s="13">
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="H53" s="13" t="b">
         <v>0</v>
@@ -3042,8 +3309,12 @@
         <v>3</v>
       </c>
       <c r="L53" s="13"/>
-    </row>
-    <row r="54" spans="1:12">
+      <c r="M53" s="13"/>
+      <c r="O53" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54" s="11">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -3060,11 +3331,12 @@
       <c r="E54" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="F54" s="13" t="s">
-        <v>68</v>
+      <c r="F54" s="13">
+        <v>4</v>
       </c>
       <c r="G54" s="13">
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="H54" s="13" t="b">
         <v>0</v>
@@ -3078,8 +3350,11 @@
       <c r="K54" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="1:12">
+      <c r="O54" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
       <c r="A55" s="11">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -3096,11 +3371,12 @@
       <c r="E55" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="F55" s="13" t="s">
-        <v>69</v>
+      <c r="F55" s="13">
+        <v>5</v>
       </c>
       <c r="G55" s="13">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="H55" s="13" t="b">
         <v>0</v>
@@ -3114,8 +3390,11 @@
       <c r="K55" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="56" spans="1:12">
+      <c r="O55" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
       <c r="A56" s="11">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -3132,11 +3411,12 @@
       <c r="E56" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="F56" s="13" t="s">
-        <v>67</v>
+      <c r="F56" s="13">
+        <v>6</v>
       </c>
       <c r="G56" s="13">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="H56" s="13" t="b">
         <v>0</v>
@@ -3150,8 +3430,11 @@
       <c r="K56" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:12">
+      <c r="O56" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
       <c r="A57" s="11">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -3168,11 +3451,12 @@
       <c r="E57" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="F57" s="13" t="s">
-        <v>67</v>
+      <c r="F57" s="13">
+        <v>7</v>
       </c>
       <c r="G57" s="13">
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="H57" s="13" t="b">
         <v>0</v>
@@ -3186,8 +3470,11 @@
       <c r="K57" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="58" spans="1:12">
+      <c r="O57" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
       <c r="A58" s="11">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -3204,11 +3491,12 @@
       <c r="E58" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="F58" s="13" t="s">
-        <v>68</v>
+      <c r="F58" s="13">
+        <v>8</v>
       </c>
       <c r="G58" s="13">
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="H58" s="13" t="b">
         <v>0</v>
@@ -3222,8 +3510,11 @@
       <c r="K58" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="1:12">
+      <c r="O58" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
       <c r="A59" s="11">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -3240,11 +3531,12 @@
       <c r="E59" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="F59" s="13" t="s">
-        <v>68</v>
+      <c r="F59" s="13">
+        <v>9</v>
       </c>
       <c r="G59" s="13">
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="H59" s="13" t="b">
         <v>0</v>
@@ -3258,8 +3550,11 @@
       <c r="K59" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="1:12">
+      <c r="O59" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
       <c r="A60" s="11">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -3276,11 +3571,12 @@
       <c r="E60" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="F60" s="13" t="s">
-        <v>69</v>
+      <c r="F60" s="13">
+        <v>10</v>
       </c>
       <c r="G60" s="13">
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="H60" s="13" t="b">
         <v>0</v>
@@ -3294,8 +3590,11 @@
       <c r="K60" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="1:12">
+      <c r="O60" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
       <c r="A61" s="11">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -3312,11 +3611,12 @@
       <c r="E61" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F61" s="13" t="s">
-        <v>67</v>
+      <c r="F61" s="13">
+        <v>11</v>
       </c>
       <c r="G61" s="13">
-        <v>11</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="H61" s="13" t="b">
         <v>0</v>
@@ -3330,8 +3630,11 @@
       <c r="K61" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:12">
+      <c r="O61" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
       <c r="A62" s="11">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -3348,11 +3651,12 @@
       <c r="E62" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F62" s="13" t="s">
-        <v>67</v>
+      <c r="F62" s="13">
+        <v>12</v>
       </c>
       <c r="G62" s="13">
-        <v>12</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="H62" s="13" t="b">
         <v>0</v>
@@ -3366,8 +3670,11 @@
       <c r="K62" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="63" spans="1:12">
+      <c r="O62" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
       <c r="A63" s="11">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -3384,11 +3691,12 @@
       <c r="E63" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F63" s="13" t="s">
-        <v>68</v>
+      <c r="F63" s="13">
+        <v>13</v>
       </c>
       <c r="G63" s="13">
-        <v>13</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="H63" s="13" t="b">
         <v>0</v>
@@ -3402,8 +3710,11 @@
       <c r="K63" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="64" spans="1:12">
+      <c r="O63" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
       <c r="A64" s="11">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -3420,11 +3731,12 @@
       <c r="E64" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F64" s="13" t="s">
-        <v>68</v>
+      <c r="F64" s="13">
+        <v>14</v>
       </c>
       <c r="G64" s="13">
-        <v>14</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="H64" s="13" t="b">
         <v>0</v>
@@ -3438,8 +3750,11 @@
       <c r="K64" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="65" spans="1:11">
+      <c r="O64" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
       <c r="A65" s="11">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -3456,11 +3771,12 @@
       <c r="E65" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F65" s="13" t="s">
-        <v>69</v>
+      <c r="F65" s="13">
+        <v>15</v>
       </c>
       <c r="G65" s="13">
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="H65" s="13" t="b">
         <v>0</v>
@@ -3474,8 +3790,11 @@
       <c r="K65" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="66" spans="1:11">
+      <c r="O65" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
       <c r="A66" s="11">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -3492,11 +3811,12 @@
       <c r="E66" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F66" s="13" t="s">
-        <v>69</v>
+      <c r="F66" s="13">
+        <v>16</v>
       </c>
       <c r="G66" s="13">
-        <v>16</v>
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="H66" s="13" t="b">
         <v>0</v>
@@ -3510,8 +3830,11 @@
       <c r="K66" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="1:11">
+      <c r="O66" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
       <c r="A67" s="11">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -3528,11 +3851,12 @@
       <c r="E67" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F67" s="13" t="s">
-        <v>70</v>
+      <c r="F67" s="13">
+        <v>17</v>
       </c>
       <c r="G67" s="13">
-        <v>17</v>
+        <f t="shared" si="1"/>
+        <v>16</v>
       </c>
       <c r="H67" s="13" t="b">
         <v>0</v>
@@ -3546,8 +3870,11 @@
       <c r="K67" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="68" spans="1:11">
+      <c r="O67" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
       <c r="A68" s="11">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -3564,11 +3891,12 @@
       <c r="E68" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F68" s="13" t="s">
-        <v>70</v>
+      <c r="F68" s="13">
+        <v>18</v>
       </c>
       <c r="G68" s="13">
-        <v>18</v>
+        <f t="shared" si="1"/>
+        <v>17</v>
       </c>
       <c r="H68" s="13" t="b">
         <v>0</v>
@@ -3582,10 +3910,13 @@
       <c r="K68" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="69" spans="1:11">
+      <c r="O68" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
       <c r="A69" s="11">
-        <f t="shared" ref="A69:A132" si="1">ROW()-4</f>
+        <f t="shared" ref="A69:A132" si="2">ROW()-4</f>
         <v>65</v>
       </c>
       <c r="B69" s="12" t="s">
@@ -3600,11 +3931,12 @@
       <c r="E69" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F69" s="13" t="s">
-        <v>71</v>
+      <c r="F69" s="13">
+        <v>19</v>
       </c>
       <c r="G69" s="13">
-        <v>19</v>
+        <f t="shared" ref="G69:G132" si="3">F69-1</f>
+        <v>18</v>
       </c>
       <c r="H69" s="13" t="b">
         <v>0</v>
@@ -3618,10 +3950,13 @@
       <c r="K69" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="70" spans="1:11">
+      <c r="O69" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
       <c r="A70" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>66</v>
       </c>
       <c r="B70" s="12" t="s">
@@ -3636,11 +3971,12 @@
       <c r="E70" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F70" s="13" t="s">
-        <v>71</v>
+      <c r="F70" s="13">
+        <v>20</v>
       </c>
       <c r="G70" s="13">
-        <v>20</v>
+        <f t="shared" si="3"/>
+        <v>19</v>
       </c>
       <c r="H70" s="13" t="b">
         <v>0</v>
@@ -3654,10 +3990,13 @@
       <c r="K70" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="71" spans="1:11">
+      <c r="O70" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
       <c r="A71" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>67</v>
       </c>
       <c r="B71" s="12" t="s">
@@ -3672,11 +4011,12 @@
       <c r="E71" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F71" s="13" t="s">
-        <v>72</v>
+      <c r="F71" s="13">
+        <v>21</v>
       </c>
       <c r="G71" s="13">
-        <v>21</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="H71" s="13" t="b">
         <v>0</v>
@@ -3690,10 +4030,13 @@
       <c r="K71" s="13">
         <v>87</v>
       </c>
-    </row>
-    <row r="72" spans="1:11">
+      <c r="O71" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
       <c r="A72" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>68</v>
       </c>
       <c r="B72" s="12" t="s">
@@ -3708,11 +4051,12 @@
       <c r="E72" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F72" s="13" t="s">
-        <v>67</v>
+      <c r="F72" s="13">
+        <v>22</v>
       </c>
       <c r="G72" s="13">
-        <v>22</v>
+        <f t="shared" si="3"/>
+        <v>21</v>
       </c>
       <c r="H72" s="13" t="b">
         <v>0</v>
@@ -3726,10 +4070,13 @@
       <c r="K72" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:11">
+      <c r="O72" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
       <c r="A73" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>69</v>
       </c>
       <c r="B73" s="12" t="s">
@@ -3744,11 +4091,12 @@
       <c r="E73" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F73" s="13" t="s">
-        <v>67</v>
+      <c r="F73" s="13">
+        <v>23</v>
       </c>
       <c r="G73" s="13">
-        <v>23</v>
+        <f t="shared" si="3"/>
+        <v>22</v>
       </c>
       <c r="H73" s="13" t="b">
         <v>0</v>
@@ -3762,10 +4110,13 @@
       <c r="K73" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="74" spans="1:11">
+      <c r="O73" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
       <c r="A74" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
       <c r="B74" s="12" t="s">
@@ -3780,11 +4131,12 @@
       <c r="E74" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F74" s="13" t="s">
-        <v>68</v>
+      <c r="F74" s="13">
+        <v>24</v>
       </c>
       <c r="G74" s="13">
-        <v>24</v>
+        <f t="shared" si="3"/>
+        <v>23</v>
       </c>
       <c r="H74" s="13" t="b">
         <v>0</v>
@@ -3798,10 +4150,13 @@
       <c r="K74" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="75" spans="1:11">
+      <c r="O74" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
       <c r="A75" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>71</v>
       </c>
       <c r="B75" s="12" t="s">
@@ -3816,11 +4171,12 @@
       <c r="E75" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F75" s="13" t="s">
-        <v>68</v>
+      <c r="F75" s="13">
+        <v>25</v>
       </c>
       <c r="G75" s="13">
-        <v>25</v>
+        <f t="shared" si="3"/>
+        <v>24</v>
       </c>
       <c r="H75" s="13" t="b">
         <v>0</v>
@@ -3834,10 +4190,13 @@
       <c r="K75" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="76" spans="1:11">
+      <c r="O75" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
       <c r="A76" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="B76" s="12" t="s">
@@ -3852,11 +4211,12 @@
       <c r="E76" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F76" s="13" t="s">
-        <v>69</v>
+      <c r="F76" s="13">
+        <v>26</v>
       </c>
       <c r="G76" s="13">
-        <v>26</v>
+        <f t="shared" si="3"/>
+        <v>25</v>
       </c>
       <c r="H76" s="13" t="b">
         <v>0</v>
@@ -3870,10 +4230,13 @@
       <c r="K76" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="1:11">
+      <c r="O76" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
       <c r="A77" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>73</v>
       </c>
       <c r="B77" s="12" t="s">
@@ -3888,11 +4251,12 @@
       <c r="E77" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="F77" s="13" t="s">
-        <v>67</v>
+      <c r="F77" s="13">
+        <v>27</v>
       </c>
       <c r="G77" s="13">
-        <v>27</v>
+        <f t="shared" si="3"/>
+        <v>26</v>
       </c>
       <c r="H77" s="13" t="b">
         <v>0</v>
@@ -3906,10 +4270,13 @@
       <c r="K77" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:11">
+      <c r="O77" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
       <c r="A78" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>74</v>
       </c>
       <c r="B78" s="12" t="s">
@@ -3924,11 +4291,12 @@
       <c r="E78" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="F78" s="13" t="s">
-        <v>67</v>
+      <c r="F78" s="13">
+        <v>28</v>
       </c>
       <c r="G78" s="13">
-        <v>28</v>
+        <f t="shared" si="3"/>
+        <v>27</v>
       </c>
       <c r="H78" s="13" t="b">
         <v>0</v>
@@ -3942,10 +4310,13 @@
       <c r="K78" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="79" spans="1:11">
+      <c r="O78" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
       <c r="A79" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>75</v>
       </c>
       <c r="B79" s="12" t="s">
@@ -3960,11 +4331,12 @@
       <c r="E79" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="F79" s="13" t="s">
-        <v>68</v>
+      <c r="F79" s="13">
+        <v>29</v>
       </c>
       <c r="G79" s="13">
-        <v>29</v>
+        <f t="shared" si="3"/>
+        <v>28</v>
       </c>
       <c r="H79" s="13" t="b">
         <v>0</v>
@@ -3978,10 +4350,13 @@
       <c r="K79" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="80" spans="1:11">
+      <c r="O79" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
       <c r="A80" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>76</v>
       </c>
       <c r="B80" s="12" t="s">
@@ -3996,11 +4371,12 @@
       <c r="E80" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="F80" s="13" t="s">
-        <v>68</v>
+      <c r="F80" s="13">
+        <v>30</v>
       </c>
       <c r="G80" s="13">
-        <v>30</v>
+        <f t="shared" si="3"/>
+        <v>29</v>
       </c>
       <c r="H80" s="13" t="b">
         <v>0</v>
@@ -4014,10 +4390,13 @@
       <c r="K80" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="81" spans="1:11">
+      <c r="O80" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
       <c r="A81" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>77</v>
       </c>
       <c r="B81" s="12" t="s">
@@ -4032,11 +4411,12 @@
       <c r="E81" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="F81" s="13" t="s">
-        <v>69</v>
+      <c r="F81" s="13">
+        <v>31</v>
       </c>
       <c r="G81" s="13">
-        <v>31</v>
+        <f t="shared" si="3"/>
+        <v>30</v>
       </c>
       <c r="H81" s="13" t="b">
         <v>0</v>
@@ -4050,10 +4430,13 @@
       <c r="K81" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="82" spans="1:11">
+      <c r="O81" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
       <c r="A82" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>78</v>
       </c>
       <c r="B82" s="12" t="s">
@@ -4068,11 +4451,12 @@
       <c r="E82" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F82" s="13" t="s">
-        <v>71</v>
+      <c r="F82" s="13">
+        <v>1</v>
       </c>
       <c r="G82" s="13">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="H82" s="13" t="b">
         <v>1</v>
@@ -4086,10 +4470,13 @@
       <c r="K82" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="83" spans="1:11">
+      <c r="O82" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
       <c r="A83" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>79</v>
       </c>
       <c r="B83" s="12" t="s">
@@ -4104,11 +4491,12 @@
       <c r="E83" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F83" s="13" t="s">
-        <v>72</v>
+      <c r="F83" s="13">
+        <v>2</v>
       </c>
       <c r="G83" s="13">
-        <v>2</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="H83" s="13" t="b">
         <v>1</v>
@@ -4122,10 +4510,13 @@
       <c r="K83" s="13">
         <v>87</v>
       </c>
-    </row>
-    <row r="84" spans="1:11">
+      <c r="O83" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
       <c r="A84" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>80</v>
       </c>
       <c r="B84" s="12" t="s">
@@ -4140,11 +4531,12 @@
       <c r="E84" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F84" s="13" t="s">
-        <v>71</v>
+      <c r="F84" s="13">
+        <v>1</v>
       </c>
       <c r="G84" s="13">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="H84" s="13" t="b">
         <v>1</v>
@@ -4158,10 +4550,13 @@
       <c r="K84" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="85" spans="1:11">
+      <c r="O84" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
       <c r="A85" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>81</v>
       </c>
       <c r="B85" s="12" t="s">
@@ -4176,11 +4571,12 @@
       <c r="E85" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F85" s="13" t="s">
-        <v>72</v>
+      <c r="F85" s="13">
+        <v>2</v>
       </c>
       <c r="G85" s="13">
-        <v>2</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="H85" s="13" t="b">
         <v>1</v>
@@ -4194,10 +4590,13 @@
       <c r="K85" s="13">
         <v>87</v>
       </c>
-    </row>
-    <row r="86" spans="1:11">
+      <c r="O85" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
       <c r="A86" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>82</v>
       </c>
       <c r="B86" s="12" t="s">
@@ -4212,11 +4611,12 @@
       <c r="E86" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F86" s="13" t="s">
-        <v>67</v>
+      <c r="F86" s="13">
+        <v>1</v>
       </c>
       <c r="G86" s="13">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="H86" s="13" t="b">
         <v>0</v>
@@ -4230,10 +4630,13 @@
       <c r="K86" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:11">
+      <c r="O86" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
       <c r="A87" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>83</v>
       </c>
       <c r="B87" s="12" t="s">
@@ -4248,11 +4651,12 @@
       <c r="E87" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F87" s="13" t="s">
-        <v>67</v>
+      <c r="F87" s="13">
+        <v>2</v>
       </c>
       <c r="G87" s="13">
-        <v>2</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="H87" s="13" t="b">
         <v>0</v>
@@ -4266,10 +4670,13 @@
       <c r="K87" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="88" spans="1:11">
+      <c r="O87" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15">
       <c r="A88" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>84</v>
       </c>
       <c r="B88" s="12" t="s">
@@ -4284,11 +4691,12 @@
       <c r="E88" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F88" s="13" t="s">
-        <v>68</v>
+      <c r="F88" s="13">
+        <v>3</v>
       </c>
       <c r="G88" s="13">
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="H88" s="13" t="b">
         <v>0</v>
@@ -4302,10 +4710,13 @@
       <c r="K88" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="89" spans="1:11">
+      <c r="O88" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
       <c r="A89" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>85</v>
       </c>
       <c r="B89" s="12" t="s">
@@ -4320,11 +4731,12 @@
       <c r="E89" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F89" s="13" t="s">
-        <v>68</v>
+      <c r="F89" s="13">
+        <v>4</v>
       </c>
       <c r="G89" s="13">
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
       <c r="H89" s="13" t="b">
         <v>0</v>
@@ -4338,10 +4750,13 @@
       <c r="K89" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="1:11">
+      <c r="O89" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
       <c r="A90" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>86</v>
       </c>
       <c r="B90" s="12" t="s">
@@ -4356,11 +4771,12 @@
       <c r="E90" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F90" s="13" t="s">
-        <v>69</v>
+      <c r="F90" s="13">
+        <v>5</v>
       </c>
       <c r="G90" s="13">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="H90" s="13" t="b">
         <v>0</v>
@@ -4374,10 +4790,13 @@
       <c r="K90" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="91" spans="1:11">
+      <c r="O90" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
       <c r="A91" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>87</v>
       </c>
       <c r="B91" s="12" t="s">
@@ -4392,11 +4811,12 @@
       <c r="E91" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F91" s="13" t="s">
-        <v>72</v>
+      <c r="F91" s="13">
+        <v>6</v>
       </c>
       <c r="G91" s="13">
-        <v>6</v>
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="H91" s="13" t="b">
         <v>0</v>
@@ -4410,10 +4830,13 @@
       <c r="K91" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="92" spans="1:11">
+      <c r="O91" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15">
       <c r="A92" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>88</v>
       </c>
       <c r="B92" s="12" t="s">
@@ -4428,11 +4851,12 @@
       <c r="E92" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F92" s="13" t="s">
-        <v>67</v>
+      <c r="F92" s="13">
+        <v>1</v>
       </c>
       <c r="G92" s="13">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="H92" s="13" t="b">
         <v>0</v>
@@ -4446,10 +4870,13 @@
       <c r="K92" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:11">
+      <c r="O92" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
       <c r="A93" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>89</v>
       </c>
       <c r="B93" s="12" t="s">
@@ -4464,11 +4891,12 @@
       <c r="E93" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F93" s="13" t="s">
-        <v>67</v>
+      <c r="F93" s="13">
+        <v>2</v>
       </c>
       <c r="G93" s="13">
-        <v>2</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="H93" s="13" t="b">
         <v>0</v>
@@ -4482,10 +4910,13 @@
       <c r="K93" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:11">
+      <c r="O93" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15">
       <c r="A94" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="B94" s="12" t="s">
@@ -4500,11 +4931,12 @@
       <c r="E94" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F94" s="13" t="s">
-        <v>67</v>
+      <c r="F94" s="13">
+        <v>3</v>
       </c>
       <c r="G94" s="13">
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="H94" s="13" t="b">
         <v>0</v>
@@ -4518,10 +4950,13 @@
       <c r="K94" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="95" spans="1:11">
+      <c r="O94" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15">
       <c r="A95" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>91</v>
       </c>
       <c r="B95" s="12" t="s">
@@ -4536,11 +4971,12 @@
       <c r="E95" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F95" s="13" t="s">
-        <v>68</v>
+      <c r="F95" s="13">
+        <v>4</v>
       </c>
       <c r="G95" s="13">
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
       <c r="H95" s="13" t="b">
         <v>0</v>
@@ -4554,10 +4990,13 @@
       <c r="K95" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="96" spans="1:11">
+      <c r="O95" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
       <c r="A96" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>92</v>
       </c>
       <c r="B96" s="12" t="s">
@@ -4572,11 +5011,12 @@
       <c r="E96" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F96" s="13" t="s">
-        <v>68</v>
+      <c r="F96" s="13">
+        <v>5</v>
       </c>
       <c r="G96" s="13">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="H96" s="13" t="b">
         <v>0</v>
@@ -4590,10 +5030,13 @@
       <c r="K96" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="1:11">
+      <c r="O96" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15">
       <c r="A97" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>93</v>
       </c>
       <c r="B97" s="12" t="s">
@@ -4608,11 +5051,12 @@
       <c r="E97" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F97" s="13" t="s">
-        <v>69</v>
+      <c r="F97" s="13">
+        <v>6</v>
       </c>
       <c r="G97" s="13">
-        <v>6</v>
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="H97" s="13" t="b">
         <v>0</v>
@@ -4626,10 +5070,13 @@
       <c r="K97" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="98" spans="1:11">
+      <c r="O97" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15">
       <c r="A98" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>94</v>
       </c>
       <c r="B98" s="12" t="s">
@@ -4644,11 +5091,12 @@
       <c r="E98" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F98" s="13" t="s">
-        <v>69</v>
+      <c r="F98" s="13">
+        <v>7</v>
       </c>
       <c r="G98" s="13">
-        <v>7</v>
+        <f t="shared" si="3"/>
+        <v>6</v>
       </c>
       <c r="H98" s="13" t="b">
         <v>0</v>
@@ -4662,10 +5110,13 @@
       <c r="K98" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="99" spans="1:11">
+      <c r="O98" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15">
       <c r="A99" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95</v>
       </c>
       <c r="B99" s="12" t="s">
@@ -4680,11 +5131,12 @@
       <c r="E99" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F99" s="13" t="s">
-        <v>70</v>
+      <c r="F99" s="13">
+        <v>8</v>
       </c>
       <c r="G99" s="13">
-        <v>8</v>
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="H99" s="13" t="b">
         <v>0</v>
@@ -4698,10 +5150,13 @@
       <c r="K99" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="100" spans="1:11">
+      <c r="O99" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15">
       <c r="A100" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="B100" s="12" t="s">
@@ -4716,11 +5171,12 @@
       <c r="E100" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F100" s="13" t="s">
-        <v>70</v>
+      <c r="F100" s="13">
+        <v>9</v>
       </c>
       <c r="G100" s="13">
-        <v>9</v>
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="H100" s="13" t="b">
         <v>0</v>
@@ -4734,10 +5190,13 @@
       <c r="K100" s="13">
         <v>20</v>
       </c>
-    </row>
-    <row r="101" spans="1:11">
+      <c r="O100" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15">
       <c r="A101" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>97</v>
       </c>
       <c r="B101" s="12" t="s">
@@ -4752,11 +5211,12 @@
       <c r="E101" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F101" s="13" t="s">
-        <v>71</v>
+      <c r="F101" s="13">
+        <v>10</v>
       </c>
       <c r="G101" s="13">
-        <v>10</v>
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="H101" s="13" t="b">
         <v>0</v>
@@ -4770,10 +5230,13 @@
       <c r="K101" s="13">
         <v>28</v>
       </c>
-    </row>
-    <row r="102" spans="1:11">
+      <c r="O101" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15">
       <c r="A102" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>98</v>
       </c>
       <c r="B102" s="12" t="s">
@@ -4788,11 +5251,12 @@
       <c r="E102" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F102" s="13" t="s">
-        <v>71</v>
+      <c r="F102" s="13">
+        <v>11</v>
       </c>
       <c r="G102" s="13">
-        <v>11</v>
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="H102" s="13" t="b">
         <v>0</v>
@@ -4806,10 +5270,13 @@
       <c r="K102" s="13">
         <v>37</v>
       </c>
-    </row>
-    <row r="103" spans="1:11">
+      <c r="O102" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15">
       <c r="A103" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>99</v>
       </c>
       <c r="B103" s="12" t="s">
@@ -4824,11 +5291,12 @@
       <c r="E103" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F103" s="13" t="s">
-        <v>71</v>
+      <c r="F103" s="13">
+        <v>12</v>
       </c>
       <c r="G103" s="13">
-        <v>12</v>
+        <f t="shared" si="3"/>
+        <v>11</v>
       </c>
       <c r="H103" s="13" t="b">
         <v>0</v>
@@ -4842,10 +5310,13 @@
       <c r="K103" s="13">
         <v>47</v>
       </c>
-    </row>
-    <row r="104" spans="1:11">
+      <c r="O103" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15">
       <c r="A104" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="B104" s="12" t="s">
@@ -4860,11 +5331,12 @@
       <c r="E104" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F104" s="13" t="s">
-        <v>72</v>
+      <c r="F104" s="13">
+        <v>13</v>
       </c>
       <c r="G104" s="13">
-        <v>13</v>
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="H104" s="13" t="b">
         <v>0</v>
@@ -4878,10 +5350,13 @@
       <c r="K104" s="13">
         <v>58</v>
       </c>
-    </row>
-    <row r="105" spans="1:11">
+      <c r="O104" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
       <c r="A105" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>101</v>
       </c>
       <c r="B105" s="12" t="s">
@@ -4896,11 +5371,12 @@
       <c r="E105" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F105" s="13" t="s">
-        <v>72</v>
+      <c r="F105" s="13">
+        <v>14</v>
       </c>
       <c r="G105" s="13">
-        <v>14</v>
+        <f t="shared" si="3"/>
+        <v>13</v>
       </c>
       <c r="H105" s="13" t="b">
         <v>0</v>
@@ -4914,10 +5390,13 @@
       <c r="K105" s="13">
         <v>87</v>
       </c>
-    </row>
-    <row r="106" spans="1:11">
+      <c r="O105" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15">
       <c r="A106" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>102</v>
       </c>
       <c r="B106" s="12" t="s">
@@ -4932,11 +5411,12 @@
       <c r="E106" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F106" s="13" t="s">
-        <v>67</v>
+      <c r="F106" s="13">
+        <v>1</v>
       </c>
       <c r="G106" s="13">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="H106" s="13" t="b">
         <v>0</v>
@@ -4950,10 +5430,13 @@
       <c r="K106" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:11">
+      <c r="O106" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15">
       <c r="A107" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>103</v>
       </c>
       <c r="B107" s="12" t="s">
@@ -4968,11 +5451,12 @@
       <c r="E107" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F107" s="13" t="s">
-        <v>67</v>
+      <c r="F107" s="13">
+        <v>2</v>
       </c>
       <c r="G107" s="13">
-        <v>2</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="H107" s="13" t="b">
         <v>0</v>
@@ -4986,10 +5470,13 @@
       <c r="K107" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="108" spans="1:11">
+      <c r="O107" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15">
       <c r="A108" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>104</v>
       </c>
       <c r="B108" s="12" t="s">
@@ -5004,11 +5491,12 @@
       <c r="E108" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F108" s="13" t="s">
-        <v>67</v>
+      <c r="F108" s="13">
+        <v>3</v>
       </c>
       <c r="G108" s="13">
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="H108" s="13" t="b">
         <v>0</v>
@@ -5022,10 +5510,13 @@
       <c r="K108" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="109" spans="1:11">
+      <c r="O108" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15">
       <c r="A109" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>105</v>
       </c>
       <c r="B109" s="12" t="s">
@@ -5040,11 +5531,12 @@
       <c r="E109" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F109" s="13" t="s">
-        <v>68</v>
+      <c r="F109" s="13">
+        <v>4</v>
       </c>
       <c r="G109" s="13">
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
       <c r="H109" s="13" t="b">
         <v>0</v>
@@ -5058,10 +5550,13 @@
       <c r="K109" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="110" spans="1:11">
+      <c r="O109" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
       <c r="A110" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>106</v>
       </c>
       <c r="B110" s="12" t="s">
@@ -5076,11 +5571,12 @@
       <c r="E110" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F110" s="13" t="s">
-        <v>68</v>
+      <c r="F110" s="13">
+        <v>5</v>
       </c>
       <c r="G110" s="13">
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="H110" s="13" t="b">
         <v>0</v>
@@ -5094,10 +5590,13 @@
       <c r="K110" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="111" spans="1:11">
+      <c r="O110" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15">
       <c r="A111" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>107</v>
       </c>
       <c r="B111" s="12" t="s">
@@ -5112,11 +5611,12 @@
       <c r="E111" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F111" s="13" t="s">
-        <v>69</v>
+      <c r="F111" s="13">
+        <v>6</v>
       </c>
       <c r="G111" s="13">
-        <v>6</v>
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="H111" s="13" t="b">
         <v>0</v>
@@ -5130,10 +5630,13 @@
       <c r="K111" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="112" spans="1:11">
+      <c r="O111" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15">
       <c r="A112" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>108</v>
       </c>
       <c r="B112" s="12" t="s">
@@ -5148,11 +5651,12 @@
       <c r="E112" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="F112" s="13" t="s">
-        <v>67</v>
+      <c r="F112" s="13">
+        <v>7</v>
       </c>
       <c r="G112" s="13">
-        <v>7</v>
+        <f t="shared" si="3"/>
+        <v>6</v>
       </c>
       <c r="H112" s="13" t="b">
         <v>0</v>
@@ -5166,10 +5670,13 @@
       <c r="K112" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:11">
+      <c r="O112" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
       <c r="A113" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>109</v>
       </c>
       <c r="B113" s="12" t="s">
@@ -5184,11 +5691,12 @@
       <c r="E113" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="F113" s="13" t="s">
-        <v>67</v>
+      <c r="F113" s="13">
+        <v>8</v>
       </c>
       <c r="G113" s="13">
-        <v>8</v>
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="H113" s="13" t="b">
         <v>0</v>
@@ -5202,10 +5710,13 @@
       <c r="K113" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="114" spans="1:11">
+      <c r="O113" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
       <c r="A114" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>110</v>
       </c>
       <c r="B114" s="12" t="s">
@@ -5220,11 +5731,12 @@
       <c r="E114" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="F114" s="13" t="s">
-        <v>67</v>
+      <c r="F114" s="13">
+        <v>9</v>
       </c>
       <c r="G114" s="13">
-        <v>9</v>
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="H114" s="13" t="b">
         <v>0</v>
@@ -5238,10 +5750,13 @@
       <c r="K114" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="115" spans="1:11">
+      <c r="O114" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15">
       <c r="A115" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>111</v>
       </c>
       <c r="B115" s="12" t="s">
@@ -5256,11 +5771,12 @@
       <c r="E115" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="F115" s="13" t="s">
-        <v>68</v>
+      <c r="F115" s="13">
+        <v>10</v>
       </c>
       <c r="G115" s="13">
-        <v>10</v>
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="H115" s="13" t="b">
         <v>0</v>
@@ -5274,10 +5790,13 @@
       <c r="K115" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="116" spans="1:11">
+      <c r="O115" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15">
       <c r="A116" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>112</v>
       </c>
       <c r="B116" s="12" t="s">
@@ -5292,11 +5811,12 @@
       <c r="E116" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="F116" s="13" t="s">
-        <v>68</v>
+      <c r="F116" s="13">
+        <v>11</v>
       </c>
       <c r="G116" s="13">
-        <v>11</v>
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="H116" s="13" t="b">
         <v>0</v>
@@ -5310,10 +5830,13 @@
       <c r="K116" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="117" spans="1:11">
+      <c r="O116" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
       <c r="A117" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>113</v>
       </c>
       <c r="B117" s="12" t="s">
@@ -5328,11 +5851,12 @@
       <c r="E117" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="F117" s="13" t="s">
-        <v>69</v>
+      <c r="F117" s="13">
+        <v>12</v>
       </c>
       <c r="G117" s="13">
-        <v>12</v>
+        <f t="shared" si="3"/>
+        <v>11</v>
       </c>
       <c r="H117" s="13" t="b">
         <v>0</v>
@@ -5346,10 +5870,13 @@
       <c r="K117" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="118" spans="1:11">
+      <c r="O117" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
       <c r="A118" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>114</v>
       </c>
       <c r="B118" s="12" t="s">
@@ -5364,11 +5891,12 @@
       <c r="E118" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="F118" s="13" t="s">
-        <v>67</v>
+      <c r="F118" s="13">
+        <v>13</v>
       </c>
       <c r="G118" s="13">
-        <v>13</v>
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="H118" s="13" t="b">
         <v>0</v>
@@ -5382,10 +5910,13 @@
       <c r="K118" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:11">
+      <c r="O118" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
       <c r="A119" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>115</v>
       </c>
       <c r="B119" s="12" t="s">
@@ -5400,11 +5931,12 @@
       <c r="E119" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="F119" s="13" t="s">
-        <v>67</v>
+      <c r="F119" s="13">
+        <v>14</v>
       </c>
       <c r="G119" s="13">
-        <v>14</v>
+        <f t="shared" si="3"/>
+        <v>13</v>
       </c>
       <c r="H119" s="13" t="b">
         <v>0</v>
@@ -5418,10 +5950,13 @@
       <c r="K119" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="120" spans="1:11">
+      <c r="O119" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
       <c r="A120" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>116</v>
       </c>
       <c r="B120" s="12" t="s">
@@ -5436,11 +5971,12 @@
       <c r="E120" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="F120" s="13" t="s">
-        <v>67</v>
+      <c r="F120" s="13">
+        <v>15</v>
       </c>
       <c r="G120" s="13">
-        <v>15</v>
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
       <c r="H120" s="13" t="b">
         <v>0</v>
@@ -5454,10 +5990,13 @@
       <c r="K120" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="121" spans="1:11">
+      <c r="O120" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
       <c r="A121" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>117</v>
       </c>
       <c r="B121" s="12" t="s">
@@ -5472,11 +6011,12 @@
       <c r="E121" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="F121" s="13" t="s">
-        <v>68</v>
+      <c r="F121" s="13">
+        <v>16</v>
       </c>
       <c r="G121" s="13">
-        <v>16</v>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="H121" s="13" t="b">
         <v>0</v>
@@ -5490,10 +6030,13 @@
       <c r="K121" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="122" spans="1:11">
+      <c r="O121" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15">
       <c r="A122" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>118</v>
       </c>
       <c r="B122" s="12" t="s">
@@ -5508,11 +6051,12 @@
       <c r="E122" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="F122" s="13" t="s">
-        <v>68</v>
+      <c r="F122" s="13">
+        <v>17</v>
       </c>
       <c r="G122" s="13">
-        <v>17</v>
+        <f t="shared" si="3"/>
+        <v>16</v>
       </c>
       <c r="H122" s="13" t="b">
         <v>0</v>
@@ -5526,10 +6070,13 @@
       <c r="K122" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="123" spans="1:11">
+      <c r="O122" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15">
       <c r="A123" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>119</v>
       </c>
       <c r="B123" s="12" t="s">
@@ -5544,11 +6091,12 @@
       <c r="E123" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="F123" s="13" t="s">
-        <v>69</v>
+      <c r="F123" s="13">
+        <v>18</v>
       </c>
       <c r="G123" s="13">
-        <v>18</v>
+        <f t="shared" si="3"/>
+        <v>17</v>
       </c>
       <c r="H123" s="13" t="b">
         <v>0</v>
@@ -5562,10 +6110,13 @@
       <c r="K123" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="124" spans="1:11">
+      <c r="O123" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15">
       <c r="A124" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>120</v>
       </c>
       <c r="B124" s="12" t="s">
@@ -5580,11 +6131,12 @@
       <c r="E124" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="F124" s="13" t="s">
-        <v>67</v>
+      <c r="F124" s="13">
+        <v>19</v>
       </c>
       <c r="G124" s="13">
-        <v>19</v>
+        <f t="shared" si="3"/>
+        <v>18</v>
       </c>
       <c r="H124" s="13" t="b">
         <v>0</v>
@@ -5598,10 +6150,13 @@
       <c r="K124" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:11">
+      <c r="O124" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15">
       <c r="A125" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>121</v>
       </c>
       <c r="B125" s="12" t="s">
@@ -5616,11 +6171,12 @@
       <c r="E125" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="F125" s="13" t="s">
-        <v>67</v>
+      <c r="F125" s="13">
+        <v>20</v>
       </c>
       <c r="G125" s="13">
-        <v>20</v>
+        <f t="shared" si="3"/>
+        <v>19</v>
       </c>
       <c r="H125" s="13" t="b">
         <v>0</v>
@@ -5634,10 +6190,13 @@
       <c r="K125" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="126" spans="1:11">
+      <c r="O125" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15">
       <c r="A126" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>122</v>
       </c>
       <c r="B126" s="12" t="s">
@@ -5652,11 +6211,12 @@
       <c r="E126" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="F126" s="13" t="s">
-        <v>67</v>
+      <c r="F126" s="13">
+        <v>21</v>
       </c>
       <c r="G126" s="13">
-        <v>21</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="H126" s="13" t="b">
         <v>0</v>
@@ -5670,10 +6230,13 @@
       <c r="K126" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="127" spans="1:11">
+      <c r="O126" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15">
       <c r="A127" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>123</v>
       </c>
       <c r="B127" s="12" t="s">
@@ -5688,11 +6251,12 @@
       <c r="E127" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="F127" s="13" t="s">
-        <v>68</v>
+      <c r="F127" s="13">
+        <v>22</v>
       </c>
       <c r="G127" s="13">
-        <v>22</v>
+        <f t="shared" si="3"/>
+        <v>21</v>
       </c>
       <c r="H127" s="13" t="b">
         <v>0</v>
@@ -5706,10 +6270,13 @@
       <c r="K127" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="128" spans="1:11">
+      <c r="O127" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15">
       <c r="A128" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>124</v>
       </c>
       <c r="B128" s="12" t="s">
@@ -5724,11 +6291,12 @@
       <c r="E128" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="F128" s="13" t="s">
-        <v>68</v>
+      <c r="F128" s="13">
+        <v>23</v>
       </c>
       <c r="G128" s="13">
-        <v>23</v>
+        <f t="shared" si="3"/>
+        <v>22</v>
       </c>
       <c r="H128" s="13" t="b">
         <v>0</v>
@@ -5742,10 +6310,13 @@
       <c r="K128" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="129" spans="1:13">
+      <c r="O128" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15">
       <c r="A129" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>125</v>
       </c>
       <c r="B129" s="12" t="s">
@@ -5760,11 +6331,12 @@
       <c r="E129" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="F129" s="13" t="s">
-        <v>69</v>
+      <c r="F129" s="13">
+        <v>24</v>
       </c>
       <c r="G129" s="13">
-        <v>24</v>
+        <f t="shared" si="3"/>
+        <v>23</v>
       </c>
       <c r="H129" s="13" t="b">
         <v>0</v>
@@ -5778,10 +6350,13 @@
       <c r="K129" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="130" spans="1:13">
+      <c r="O129" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15">
       <c r="A130" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>126</v>
       </c>
       <c r="B130" s="12" t="s">
@@ -5796,11 +6371,12 @@
       <c r="E130" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F130" s="13" t="s">
-        <v>71</v>
+      <c r="F130" s="13">
+        <v>1</v>
       </c>
       <c r="G130" s="13">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="H130" s="13" t="b">
         <v>1</v>
@@ -5814,10 +6390,13 @@
       <c r="K130" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="131" spans="1:13">
+      <c r="O130" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15">
       <c r="A131" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>127</v>
       </c>
       <c r="B131" s="12" t="s">
@@ -5832,11 +6411,12 @@
       <c r="E131" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F131" s="13" t="s">
-        <v>72</v>
+      <c r="F131" s="13">
+        <v>2</v>
       </c>
       <c r="G131" s="13">
-        <v>2</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="H131" s="13" t="b">
         <v>1</v>
@@ -5850,10 +6430,13 @@
       <c r="K131" s="13">
         <v>87</v>
       </c>
-    </row>
-    <row r="132" spans="1:13">
+      <c r="O131" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15">
       <c r="A132" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>128</v>
       </c>
       <c r="B132" s="12" t="s">
@@ -5868,11 +6451,12 @@
       <c r="E132" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F132" s="13" t="s">
-        <v>71</v>
+      <c r="F132" s="13">
+        <v>1</v>
       </c>
       <c r="G132" s="13">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="H132" s="13" t="b">
         <v>1</v>
@@ -5886,10 +6470,13 @@
       <c r="K132" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="133" spans="1:13">
+      <c r="O132" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15">
       <c r="A133" s="11">
-        <f t="shared" ref="A133:A196" si="2">ROW()-4</f>
+        <f t="shared" ref="A133:A196" si="4">ROW()-4</f>
         <v>129</v>
       </c>
       <c r="B133" s="12" t="s">
@@ -5904,11 +6491,12 @@
       <c r="E133" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F133" s="13" t="s">
-        <v>72</v>
+      <c r="F133" s="13">
+        <v>2</v>
       </c>
       <c r="G133" s="13">
-        <v>2</v>
+        <f t="shared" ref="G133:G196" si="5">F133-1</f>
+        <v>1</v>
       </c>
       <c r="H133" s="13" t="b">
         <v>1</v>
@@ -5922,10 +6510,13 @@
       <c r="K133" s="13">
         <v>87</v>
       </c>
-    </row>
-    <row r="134" spans="1:13">
+      <c r="O133" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15">
       <c r="A134" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>130</v>
       </c>
       <c r="B134" s="12" t="s">
@@ -5940,11 +6531,12 @@
       <c r="E134" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F134" s="13" t="s">
-        <v>67</v>
+      <c r="F134" s="13">
+        <v>1</v>
       </c>
       <c r="G134" s="13">
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="H134" s="13" t="b">
         <v>0</v>
@@ -5958,10 +6550,13 @@
       <c r="K134" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:13">
+      <c r="O134" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15">
       <c r="A135" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>131</v>
       </c>
       <c r="B135" s="12" t="s">
@@ -5976,11 +6571,12 @@
       <c r="E135" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F135" s="13" t="s">
-        <v>67</v>
+      <c r="F135" s="13">
+        <v>2</v>
       </c>
       <c r="G135" s="13">
-        <v>2</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="H135" s="13" t="b">
         <v>0</v>
@@ -5994,10 +6590,13 @@
       <c r="K135" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="136" spans="1:13">
+      <c r="O135" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15">
       <c r="A136" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>132</v>
       </c>
       <c r="B136" s="12" t="s">
@@ -6012,11 +6611,12 @@
       <c r="E136" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F136" s="13" t="s">
-        <v>67</v>
+      <c r="F136" s="13">
+        <v>3</v>
       </c>
       <c r="G136" s="13">
-        <v>3</v>
+        <f t="shared" si="5"/>
+        <v>2</v>
       </c>
       <c r="H136" s="13" t="b">
         <v>0</v>
@@ -6030,10 +6630,13 @@
       <c r="K136" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="137" spans="1:13">
+      <c r="O136" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15">
       <c r="A137" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>133</v>
       </c>
       <c r="B137" s="12" t="s">
@@ -6048,11 +6651,12 @@
       <c r="E137" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F137" s="13" t="s">
-        <v>68</v>
+      <c r="F137" s="13">
+        <v>4</v>
       </c>
       <c r="G137" s="13">
-        <v>4</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="H137" s="13" t="b">
         <v>0</v>
@@ -6066,10 +6670,13 @@
       <c r="K137" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="138" spans="1:13">
+      <c r="O137" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15">
       <c r="A138" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>134</v>
       </c>
       <c r="B138" s="12" t="s">
@@ -6084,11 +6691,12 @@
       <c r="E138" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F138" s="13" t="s">
-        <v>68</v>
+      <c r="F138" s="13">
+        <v>5</v>
       </c>
       <c r="G138" s="13">
-        <v>5</v>
+        <f t="shared" si="5"/>
+        <v>4</v>
       </c>
       <c r="H138" s="13" t="b">
         <v>0</v>
@@ -6102,10 +6710,13 @@
       <c r="K138" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="139" spans="1:13">
+      <c r="O138" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15">
       <c r="A139" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>135</v>
       </c>
       <c r="B139" s="12" t="s">
@@ -6120,11 +6731,12 @@
       <c r="E139" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F139" s="13" t="s">
-        <v>69</v>
+      <c r="F139" s="13">
+        <v>6</v>
       </c>
       <c r="G139" s="13">
-        <v>6</v>
+        <f t="shared" si="5"/>
+        <v>5</v>
       </c>
       <c r="H139" s="13" t="b">
         <v>0</v>
@@ -6138,10 +6750,13 @@
       <c r="K139" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="140" spans="1:13">
+      <c r="O139" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15">
       <c r="A140" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>136</v>
       </c>
       <c r="B140" s="12" t="s">
@@ -6156,11 +6771,12 @@
       <c r="E140" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F140" s="13" t="s">
-        <v>69</v>
+      <c r="F140" s="13">
+        <v>7</v>
       </c>
       <c r="G140" s="13">
-        <v>7</v>
+        <f t="shared" si="5"/>
+        <v>6</v>
       </c>
       <c r="H140" s="13" t="b">
         <v>0</v>
@@ -6175,11 +6791,15 @@
         <v>13</v>
       </c>
       <c r="L140" s="15"/>
-      <c r="M140" s="13"/>
-    </row>
-    <row r="141" spans="1:13">
+      <c r="M140" s="15"/>
+      <c r="N140" s="13"/>
+      <c r="O140" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15">
       <c r="A141" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>137</v>
       </c>
       <c r="B141" s="12" t="s">
@@ -6194,11 +6814,12 @@
       <c r="E141" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F141" s="13" t="s">
-        <v>70</v>
+      <c r="F141" s="13">
+        <v>8</v>
       </c>
       <c r="G141" s="13">
-        <v>8</v>
+        <f t="shared" si="5"/>
+        <v>7</v>
       </c>
       <c r="H141" s="13" t="b">
         <v>0</v>
@@ -6213,11 +6834,15 @@
         <v>38</v>
       </c>
       <c r="L141" s="15"/>
-      <c r="M141" s="13"/>
-    </row>
-    <row r="142" spans="1:13">
+      <c r="M141" s="15"/>
+      <c r="N141" s="13"/>
+      <c r="O141" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15">
       <c r="A142" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>138</v>
       </c>
       <c r="B142" s="12" t="s">
@@ -6232,11 +6857,12 @@
       <c r="E142" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F142" s="13" t="s">
-        <v>70</v>
+      <c r="F142" s="13">
+        <v>9</v>
       </c>
       <c r="G142" s="13">
-        <v>9</v>
+        <f t="shared" si="5"/>
+        <v>8</v>
       </c>
       <c r="H142" s="13" t="b">
         <v>0</v>
@@ -6251,11 +6877,15 @@
         <v>38</v>
       </c>
       <c r="L142" s="15"/>
-      <c r="M142" s="13"/>
-    </row>
-    <row r="143" spans="1:13">
+      <c r="M142" s="15"/>
+      <c r="N142" s="13"/>
+      <c r="O142" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15">
       <c r="A143" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>139</v>
       </c>
       <c r="B143" s="12" t="s">
@@ -6270,11 +6900,12 @@
       <c r="E143" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F143" s="13" t="s">
-        <v>71</v>
+      <c r="F143" s="13">
+        <v>10</v>
       </c>
       <c r="G143" s="13">
-        <v>10</v>
+        <f t="shared" si="5"/>
+        <v>9</v>
       </c>
       <c r="H143" s="13" t="b">
         <v>1</v>
@@ -6288,10 +6919,13 @@
       <c r="K143" s="13">
         <v>87</v>
       </c>
-    </row>
-    <row r="144" spans="1:13">
+      <c r="O143" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15">
       <c r="A144" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>140</v>
       </c>
       <c r="B144" s="12" t="s">
@@ -6306,11 +6940,12 @@
       <c r="E144" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F144" s="13" t="s">
-        <v>71</v>
+      <c r="F144" s="13">
+        <v>11</v>
       </c>
       <c r="G144" s="13">
-        <v>11</v>
+        <f t="shared" si="5"/>
+        <v>10</v>
       </c>
       <c r="H144" s="13" t="b">
         <v>1</v>
@@ -6324,10 +6959,13 @@
       <c r="K144" s="13">
         <v>87</v>
       </c>
-    </row>
-    <row r="145" spans="1:11">
+      <c r="O144" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15">
       <c r="A145" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>141</v>
       </c>
       <c r="B145" s="12" t="s">
@@ -6342,11 +6980,12 @@
       <c r="E145" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F145" s="13" t="s">
-        <v>72</v>
+      <c r="F145" s="13">
+        <v>12</v>
       </c>
       <c r="G145" s="13">
-        <v>12</v>
+        <f t="shared" si="5"/>
+        <v>11</v>
       </c>
       <c r="H145" s="13" t="b">
         <v>1</v>
@@ -6360,10 +6999,13 @@
       <c r="K145" s="13">
         <v>87</v>
       </c>
-    </row>
-    <row r="146" spans="1:11">
+      <c r="O145" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15">
       <c r="A146" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>142</v>
       </c>
       <c r="B146" s="12" t="s">
@@ -6378,11 +7020,12 @@
       <c r="E146" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="F146" s="13" t="s">
-        <v>67</v>
+      <c r="F146" s="13">
+        <v>1</v>
       </c>
       <c r="G146" s="13">
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="H146" s="13" t="b">
         <v>0</v>
@@ -6396,10 +7039,13 @@
       <c r="K146" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" spans="1:11">
+      <c r="O146" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15">
       <c r="A147" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>143</v>
       </c>
       <c r="B147" s="12" t="s">
@@ -6414,11 +7060,12 @@
       <c r="E147" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="F147" s="13" t="s">
-        <v>67</v>
+      <c r="F147" s="13">
+        <v>2</v>
       </c>
       <c r="G147" s="13">
-        <v>2</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="H147" s="13" t="b">
         <v>0</v>
@@ -6432,10 +7079,13 @@
       <c r="K147" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="148" spans="1:11">
+      <c r="O147" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15">
       <c r="A148" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>144</v>
       </c>
       <c r="B148" s="12" t="s">
@@ -6450,11 +7100,12 @@
       <c r="E148" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="F148" s="13" t="s">
-        <v>68</v>
+      <c r="F148" s="13">
+        <v>3</v>
       </c>
       <c r="G148" s="13">
-        <v>3</v>
+        <f t="shared" si="5"/>
+        <v>2</v>
       </c>
       <c r="H148" s="13" t="b">
         <v>0</v>
@@ -6468,10 +7119,13 @@
       <c r="K148" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="149" spans="1:11">
+      <c r="O148" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15">
       <c r="A149" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>145</v>
       </c>
       <c r="B149" s="12" t="s">
@@ -6486,11 +7140,12 @@
       <c r="E149" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="F149" s="13" t="s">
-        <v>68</v>
+      <c r="F149" s="13">
+        <v>4</v>
       </c>
       <c r="G149" s="13">
-        <v>4</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="H149" s="13" t="b">
         <v>0</v>
@@ -6504,10 +7159,13 @@
       <c r="K149" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="150" spans="1:11">
+      <c r="O149" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15">
       <c r="A150" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>146</v>
       </c>
       <c r="B150" s="12" t="s">
@@ -6522,11 +7180,12 @@
       <c r="E150" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="F150" s="13" t="s">
-        <v>69</v>
+      <c r="F150" s="13">
+        <v>5</v>
       </c>
       <c r="G150" s="13">
-        <v>5</v>
+        <f t="shared" si="5"/>
+        <v>4</v>
       </c>
       <c r="H150" s="13" t="b">
         <v>0</v>
@@ -6540,10 +7199,13 @@
       <c r="K150" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="151" spans="1:11">
+      <c r="O150" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15">
       <c r="A151" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>147</v>
       </c>
       <c r="B151" s="12" t="s">
@@ -6558,11 +7220,12 @@
       <c r="E151" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="F151" s="13" t="s">
-        <v>71</v>
+      <c r="F151" s="13">
+        <v>6</v>
       </c>
       <c r="G151" s="13">
-        <v>6</v>
+        <f t="shared" si="5"/>
+        <v>5</v>
       </c>
       <c r="H151" s="13" t="b">
         <v>1</v>
@@ -6576,10 +7239,13 @@
       <c r="K151" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="152" spans="1:11">
+      <c r="O151" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15">
       <c r="A152" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>148</v>
       </c>
       <c r="B152" s="12" t="s">
@@ -6594,11 +7260,12 @@
       <c r="E152" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="F152" s="13" t="s">
-        <v>71</v>
+      <c r="F152" s="13">
+        <v>7</v>
       </c>
       <c r="G152" s="13">
-        <v>7</v>
+        <f t="shared" si="5"/>
+        <v>6</v>
       </c>
       <c r="H152" s="13" t="b">
         <v>1</v>
@@ -6612,10 +7279,13 @@
       <c r="K152" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="153" spans="1:11">
+      <c r="O152" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15">
       <c r="A153" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>149</v>
       </c>
       <c r="B153" s="12" t="s">
@@ -6630,11 +7300,12 @@
       <c r="E153" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="F153" s="13" t="s">
-        <v>72</v>
+      <c r="F153" s="13">
+        <v>8</v>
       </c>
       <c r="G153" s="13">
-        <v>8</v>
+        <f t="shared" si="5"/>
+        <v>7</v>
       </c>
       <c r="H153" s="13" t="b">
         <v>1</v>
@@ -6648,10 +7319,13 @@
       <c r="K153" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="154" spans="1:11">
+      <c r="O153" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15">
       <c r="A154" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>150</v>
       </c>
       <c r="B154" s="12" t="s">
@@ -6666,11 +7340,12 @@
       <c r="E154" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F154" s="13" t="s">
-        <v>67</v>
+      <c r="F154" s="13">
+        <v>9</v>
       </c>
       <c r="G154" s="13">
-        <v>9</v>
+        <f t="shared" si="5"/>
+        <v>8</v>
       </c>
       <c r="H154" s="13" t="b">
         <v>0</v>
@@ -6684,10 +7359,13 @@
       <c r="K154" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="155" spans="1:11">
+      <c r="O154" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15">
       <c r="A155" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>151</v>
       </c>
       <c r="B155" s="12" t="s">
@@ -6702,11 +7380,12 @@
       <c r="E155" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F155" s="13" t="s">
-        <v>67</v>
+      <c r="F155" s="13">
+        <v>10</v>
       </c>
       <c r="G155" s="13">
-        <v>10</v>
+        <f t="shared" si="5"/>
+        <v>9</v>
       </c>
       <c r="H155" s="13" t="b">
         <v>0</v>
@@ -6720,10 +7399,13 @@
       <c r="K155" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="156" spans="1:11">
+      <c r="O155" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15">
       <c r="A156" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>152</v>
       </c>
       <c r="B156" s="12" t="s">
@@ -6738,11 +7420,12 @@
       <c r="E156" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F156" s="13" t="s">
-        <v>68</v>
+      <c r="F156" s="13">
+        <v>11</v>
       </c>
       <c r="G156" s="13">
-        <v>11</v>
+        <f t="shared" si="5"/>
+        <v>10</v>
       </c>
       <c r="H156" s="13" t="b">
         <v>0</v>
@@ -6756,10 +7439,13 @@
       <c r="K156" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="157" spans="1:11">
+      <c r="O156" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15">
       <c r="A157" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>153</v>
       </c>
       <c r="B157" s="12" t="s">
@@ -6774,11 +7460,12 @@
       <c r="E157" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F157" s="13" t="s">
-        <v>68</v>
+      <c r="F157" s="13">
+        <v>12</v>
       </c>
       <c r="G157" s="13">
-        <v>12</v>
+        <f t="shared" si="5"/>
+        <v>11</v>
       </c>
       <c r="H157" s="13" t="b">
         <v>0</v>
@@ -6792,10 +7479,13 @@
       <c r="K157" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="158" spans="1:11">
+      <c r="O157" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15">
       <c r="A158" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>154</v>
       </c>
       <c r="B158" s="12" t="s">
@@ -6810,11 +7500,12 @@
       <c r="E158" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F158" s="13" t="s">
-        <v>69</v>
+      <c r="F158" s="13">
+        <v>13</v>
       </c>
       <c r="G158" s="13">
-        <v>13</v>
+        <f t="shared" si="5"/>
+        <v>12</v>
       </c>
       <c r="H158" s="13" t="b">
         <v>0</v>
@@ -6828,10 +7519,13 @@
       <c r="K158" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="159" spans="1:11">
+      <c r="O158" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15">
       <c r="A159" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>155</v>
       </c>
       <c r="B159" s="12" t="s">
@@ -6846,11 +7540,12 @@
       <c r="E159" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F159" s="13" t="s">
-        <v>71</v>
+      <c r="F159" s="13">
+        <v>14</v>
       </c>
       <c r="G159" s="13">
-        <v>14</v>
+        <f t="shared" si="5"/>
+        <v>13</v>
       </c>
       <c r="H159" s="13" t="b">
         <v>1</v>
@@ -6864,10 +7559,13 @@
       <c r="K159" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="160" spans="1:11">
+      <c r="O159" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15">
       <c r="A160" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>156</v>
       </c>
       <c r="B160" s="12" t="s">
@@ -6882,11 +7580,12 @@
       <c r="E160" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F160" s="13" t="s">
-        <v>71</v>
+      <c r="F160" s="13">
+        <v>15</v>
       </c>
       <c r="G160" s="13">
-        <v>15</v>
+        <f t="shared" si="5"/>
+        <v>14</v>
       </c>
       <c r="H160" s="13" t="b">
         <v>1</v>
@@ -6900,10 +7599,13 @@
       <c r="K160" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="161" spans="1:11">
+      <c r="O160" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15">
       <c r="A161" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>157</v>
       </c>
       <c r="B161" s="12" t="s">
@@ -6918,11 +7620,12 @@
       <c r="E161" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F161" s="13" t="s">
-        <v>72</v>
+      <c r="F161" s="13">
+        <v>16</v>
       </c>
       <c r="G161" s="13">
-        <v>16</v>
+        <f t="shared" si="5"/>
+        <v>15</v>
       </c>
       <c r="H161" s="13" t="b">
         <v>1</v>
@@ -6936,10 +7639,13 @@
       <c r="K161" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="162" spans="1:11">
+      <c r="O161" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15">
       <c r="A162" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>158</v>
       </c>
       <c r="B162" s="12" t="s">
@@ -6954,11 +7660,12 @@
       <c r="E162" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="F162" s="13" t="s">
-        <v>67</v>
+      <c r="F162" s="13">
+        <v>17</v>
       </c>
       <c r="G162" s="13">
-        <v>17</v>
+        <f t="shared" si="5"/>
+        <v>16</v>
       </c>
       <c r="H162" s="13" t="b">
         <v>0</v>
@@ -6972,10 +7679,13 @@
       <c r="K162" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="163" spans="1:11">
+      <c r="O162" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15">
       <c r="A163" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>159</v>
       </c>
       <c r="B163" s="12" t="s">
@@ -6990,11 +7700,12 @@
       <c r="E163" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="F163" s="13" t="s">
-        <v>67</v>
+      <c r="F163" s="13">
+        <v>18</v>
       </c>
       <c r="G163" s="13">
-        <v>18</v>
+        <f t="shared" si="5"/>
+        <v>17</v>
       </c>
       <c r="H163" s="13" t="b">
         <v>0</v>
@@ -7008,10 +7719,13 @@
       <c r="K163" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="164" spans="1:11">
+      <c r="O163" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15">
       <c r="A164" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="B164" s="12" t="s">
@@ -7026,11 +7740,12 @@
       <c r="E164" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="F164" s="13" t="s">
-        <v>68</v>
+      <c r="F164" s="13">
+        <v>19</v>
       </c>
       <c r="G164" s="13">
-        <v>19</v>
+        <f t="shared" si="5"/>
+        <v>18</v>
       </c>
       <c r="H164" s="13" t="b">
         <v>0</v>
@@ -7044,10 +7759,13 @@
       <c r="K164" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="165" spans="1:11">
+      <c r="O164" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15">
       <c r="A165" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>161</v>
       </c>
       <c r="B165" s="12" t="s">
@@ -7062,11 +7780,12 @@
       <c r="E165" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="F165" s="13" t="s">
-        <v>68</v>
+      <c r="F165" s="13">
+        <v>20</v>
       </c>
       <c r="G165" s="13">
-        <v>20</v>
+        <f t="shared" si="5"/>
+        <v>19</v>
       </c>
       <c r="H165" s="13" t="b">
         <v>0</v>
@@ -7080,10 +7799,13 @@
       <c r="K165" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="166" spans="1:11">
+      <c r="O165" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15">
       <c r="A166" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>162</v>
       </c>
       <c r="B166" s="12" t="s">
@@ -7098,11 +7820,12 @@
       <c r="E166" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="F166" s="13" t="s">
-        <v>69</v>
+      <c r="F166" s="13">
+        <v>21</v>
       </c>
       <c r="G166" s="13">
-        <v>21</v>
+        <f t="shared" si="5"/>
+        <v>20</v>
       </c>
       <c r="H166" s="13" t="b">
         <v>0</v>
@@ -7116,10 +7839,13 @@
       <c r="K166" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="167" spans="1:11">
+      <c r="O166" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15">
       <c r="A167" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>163</v>
       </c>
       <c r="B167" s="12" t="s">
@@ -7134,11 +7860,12 @@
       <c r="E167" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="F167" s="13" t="s">
-        <v>71</v>
+      <c r="F167" s="13">
+        <v>22</v>
       </c>
       <c r="G167" s="13">
-        <v>22</v>
+        <f t="shared" si="5"/>
+        <v>21</v>
       </c>
       <c r="H167" s="13" t="b">
         <v>1</v>
@@ -7152,10 +7879,13 @@
       <c r="K167" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="168" spans="1:11">
+      <c r="O167" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15">
       <c r="A168" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>164</v>
       </c>
       <c r="B168" s="12" t="s">
@@ -7170,11 +7900,12 @@
       <c r="E168" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="F168" s="13" t="s">
-        <v>71</v>
+      <c r="F168" s="13">
+        <v>23</v>
       </c>
       <c r="G168" s="13">
-        <v>23</v>
+        <f t="shared" si="5"/>
+        <v>22</v>
       </c>
       <c r="H168" s="13" t="b">
         <v>1</v>
@@ -7188,10 +7919,13 @@
       <c r="K168" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="169" spans="1:11">
+      <c r="O168" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15">
       <c r="A169" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>165</v>
       </c>
       <c r="B169" s="12" t="s">
@@ -7206,11 +7940,12 @@
       <c r="E169" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="F169" s="13" t="s">
-        <v>72</v>
+      <c r="F169" s="13">
+        <v>24</v>
       </c>
       <c r="G169" s="13">
-        <v>24</v>
+        <f t="shared" si="5"/>
+        <v>23</v>
       </c>
       <c r="H169" s="13" t="b">
         <v>1</v>
@@ -7224,10 +7959,13 @@
       <c r="K169" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="170" spans="1:11">
+      <c r="O169" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15">
       <c r="A170" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>166</v>
       </c>
       <c r="B170" s="12" t="s">
@@ -7242,11 +7980,12 @@
       <c r="E170" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F170" s="13" t="s">
-        <v>67</v>
+      <c r="F170" s="13">
+        <v>25</v>
       </c>
       <c r="G170" s="13">
-        <v>25</v>
+        <f t="shared" si="5"/>
+        <v>24</v>
       </c>
       <c r="H170" s="13" t="b">
         <v>0</v>
@@ -7260,10 +7999,13 @@
       <c r="K170" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="171" spans="1:11">
+      <c r="O170" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15">
       <c r="A171" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>167</v>
       </c>
       <c r="B171" s="12" t="s">
@@ -7278,11 +8020,12 @@
       <c r="E171" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F171" s="13" t="s">
-        <v>67</v>
+      <c r="F171" s="13">
+        <v>26</v>
       </c>
       <c r="G171" s="13">
-        <v>26</v>
+        <f t="shared" si="5"/>
+        <v>25</v>
       </c>
       <c r="H171" s="13" t="b">
         <v>0</v>
@@ -7296,10 +8039,13 @@
       <c r="K171" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="172" spans="1:11">
+      <c r="O171" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15">
       <c r="A172" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>168</v>
       </c>
       <c r="B172" s="12" t="s">
@@ -7314,11 +8060,12 @@
       <c r="E172" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F172" s="13" t="s">
-        <v>68</v>
+      <c r="F172" s="13">
+        <v>27</v>
       </c>
       <c r="G172" s="13">
-        <v>27</v>
+        <f t="shared" si="5"/>
+        <v>26</v>
       </c>
       <c r="H172" s="13" t="b">
         <v>0</v>
@@ -7332,10 +8079,13 @@
       <c r="K172" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="173" spans="1:11">
+      <c r="O172" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15">
       <c r="A173" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>169</v>
       </c>
       <c r="B173" s="12" t="s">
@@ -7350,11 +8100,12 @@
       <c r="E173" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F173" s="13" t="s">
-        <v>68</v>
+      <c r="F173" s="13">
+        <v>28</v>
       </c>
       <c r="G173" s="13">
-        <v>28</v>
+        <f t="shared" si="5"/>
+        <v>27</v>
       </c>
       <c r="H173" s="13" t="b">
         <v>0</v>
@@ -7368,10 +8119,13 @@
       <c r="K173" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="174" spans="1:11">
+      <c r="O173" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15">
       <c r="A174" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>170</v>
       </c>
       <c r="B174" s="12" t="s">
@@ -7386,11 +8140,12 @@
       <c r="E174" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F174" s="13" t="s">
-        <v>69</v>
+      <c r="F174" s="13">
+        <v>29</v>
       </c>
       <c r="G174" s="13">
-        <v>29</v>
+        <f t="shared" si="5"/>
+        <v>28</v>
       </c>
       <c r="H174" s="13" t="b">
         <v>0</v>
@@ -7404,10 +8159,13 @@
       <c r="K174" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="175" spans="1:11">
+      <c r="O174" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15">
       <c r="A175" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>171</v>
       </c>
       <c r="B175" s="12" t="s">
@@ -7422,11 +8180,12 @@
       <c r="E175" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F175" s="13" t="s">
-        <v>71</v>
+      <c r="F175" s="13">
+        <v>30</v>
       </c>
       <c r="G175" s="13">
-        <v>30</v>
+        <f t="shared" si="5"/>
+        <v>29</v>
       </c>
       <c r="H175" s="13" t="b">
         <v>1</v>
@@ -7440,10 +8199,13 @@
       <c r="K175" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="176" spans="1:11">
+      <c r="O175" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15">
       <c r="A176" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>172</v>
       </c>
       <c r="B176" s="12" t="s">
@@ -7458,11 +8220,12 @@
       <c r="E176" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F176" s="13" t="s">
-        <v>72</v>
+      <c r="F176" s="13">
+        <v>31</v>
       </c>
       <c r="G176" s="13">
-        <v>31</v>
+        <f t="shared" si="5"/>
+        <v>30</v>
       </c>
       <c r="H176" s="13" t="b">
         <v>1</v>
@@ -7476,10 +8239,13 @@
       <c r="K176" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="177" spans="1:11">
+      <c r="O176" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15">
       <c r="A177" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>173</v>
       </c>
       <c r="B177" s="12" t="s">
@@ -7494,11 +8260,12 @@
       <c r="E177" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="F177" s="13" t="s">
-        <v>67</v>
+      <c r="F177" s="13">
+        <v>32</v>
       </c>
       <c r="G177" s="13">
-        <v>32</v>
+        <f t="shared" si="5"/>
+        <v>31</v>
       </c>
       <c r="H177" s="13" t="b">
         <v>0</v>
@@ -7512,10 +8279,13 @@
       <c r="K177" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="178" spans="1:11">
+      <c r="O177" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15">
       <c r="A178" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>174</v>
       </c>
       <c r="B178" s="12" t="s">
@@ -7530,11 +8300,12 @@
       <c r="E178" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="F178" s="13" t="s">
-        <v>67</v>
+      <c r="F178" s="13">
+        <v>33</v>
       </c>
       <c r="G178" s="13">
-        <v>33</v>
+        <f t="shared" si="5"/>
+        <v>32</v>
       </c>
       <c r="H178" s="13" t="b">
         <v>0</v>
@@ -7548,10 +8319,13 @@
       <c r="K178" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="179" spans="1:11">
+      <c r="O178" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15">
       <c r="A179" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>175</v>
       </c>
       <c r="B179" s="12" t="s">
@@ -7566,11 +8340,12 @@
       <c r="E179" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="F179" s="13" t="s">
-        <v>68</v>
+      <c r="F179" s="13">
+        <v>34</v>
       </c>
       <c r="G179" s="13">
-        <v>34</v>
+        <f t="shared" si="5"/>
+        <v>33</v>
       </c>
       <c r="H179" s="13" t="b">
         <v>0</v>
@@ -7584,10 +8359,13 @@
       <c r="K179" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="180" spans="1:11">
+      <c r="O179" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15">
       <c r="A180" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>176</v>
       </c>
       <c r="B180" s="12" t="s">
@@ -7602,11 +8380,12 @@
       <c r="E180" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="F180" s="13" t="s">
-        <v>69</v>
+      <c r="F180" s="13">
+        <v>35</v>
       </c>
       <c r="G180" s="13">
-        <v>35</v>
+        <f t="shared" si="5"/>
+        <v>34</v>
       </c>
       <c r="H180" s="13" t="b">
         <v>0</v>
@@ -7620,10 +8399,13 @@
       <c r="K180" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="181" spans="1:11">
+      <c r="O180" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15">
       <c r="A181" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>177</v>
       </c>
       <c r="B181" s="12" t="s">
@@ -7638,11 +8420,12 @@
       <c r="E181" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="F181" s="13" t="s">
-        <v>71</v>
+      <c r="F181" s="13">
+        <v>36</v>
       </c>
       <c r="G181" s="13">
-        <v>36</v>
+        <f t="shared" si="5"/>
+        <v>35</v>
       </c>
       <c r="H181" s="13" t="b">
         <v>1</v>
@@ -7656,10 +8439,13 @@
       <c r="K181" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="182" spans="1:11">
+      <c r="O181" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15">
       <c r="A182" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>178</v>
       </c>
       <c r="B182" s="12" t="s">
@@ -7674,11 +8460,12 @@
       <c r="E182" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="F182" s="13" t="s">
-        <v>71</v>
+      <c r="F182" s="13">
+        <v>37</v>
       </c>
       <c r="G182" s="13">
-        <v>37</v>
+        <f t="shared" si="5"/>
+        <v>36</v>
       </c>
       <c r="H182" s="13" t="b">
         <v>1</v>
@@ -7692,10 +8479,13 @@
       <c r="K182" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="183" spans="1:11">
+      <c r="O182" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15">
       <c r="A183" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>179</v>
       </c>
       <c r="B183" s="12" t="s">
@@ -7710,11 +8500,12 @@
       <c r="E183" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="F183" s="13" t="s">
-        <v>72</v>
+      <c r="F183" s="13">
+        <v>38</v>
       </c>
       <c r="G183" s="13">
-        <v>38</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
       <c r="H183" s="13" t="b">
         <v>1</v>
@@ -7728,10 +8519,13 @@
       <c r="K183" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="184" spans="1:11">
+      <c r="O183" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15">
       <c r="A184" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>180</v>
       </c>
       <c r="B184" s="12" t="s">
@@ -7746,11 +8540,12 @@
       <c r="E184" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F184" s="13" t="s">
-        <v>67</v>
+      <c r="F184" s="13">
+        <v>1</v>
       </c>
       <c r="G184" s="13">
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="H184" s="13" t="b">
         <v>0</v>
@@ -7764,10 +8559,13 @@
       <c r="K184" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="185" spans="1:11">
+      <c r="O184" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15">
       <c r="A185" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>181</v>
       </c>
       <c r="B185" s="12" t="s">
@@ -7782,11 +8580,12 @@
       <c r="E185" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F185" s="13" t="s">
-        <v>68</v>
+      <c r="F185" s="13">
+        <v>2</v>
       </c>
       <c r="G185" s="13">
-        <v>2</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="H185" s="13" t="b">
         <v>0</v>
@@ -7800,10 +8599,13 @@
       <c r="K185" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="186" spans="1:11">
+      <c r="O185" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15">
       <c r="A186" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>182</v>
       </c>
       <c r="B186" s="12" t="s">
@@ -7818,11 +8620,12 @@
       <c r="E186" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F186" s="13" t="s">
-        <v>68</v>
+      <c r="F186" s="13">
+        <v>3</v>
       </c>
       <c r="G186" s="13">
-        <v>3</v>
+        <f t="shared" si="5"/>
+        <v>2</v>
       </c>
       <c r="H186" s="13" t="b">
         <v>0</v>
@@ -7836,10 +8639,13 @@
       <c r="K186" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="187" spans="1:11">
+      <c r="O186" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15">
       <c r="A187" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>183</v>
       </c>
       <c r="B187" s="12" t="s">
@@ -7854,11 +8660,12 @@
       <c r="E187" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F187" s="13" t="s">
-        <v>69</v>
+      <c r="F187" s="13">
+        <v>4</v>
       </c>
       <c r="G187" s="13">
-        <v>4</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="H187" s="13" t="b">
         <v>0</v>
@@ -7872,10 +8679,13 @@
       <c r="K187" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="188" spans="1:11">
+      <c r="O187" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15">
       <c r="A188" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>184</v>
       </c>
       <c r="B188" s="12" t="s">
@@ -7890,11 +8700,12 @@
       <c r="E188" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F188" s="13" t="s">
-        <v>69</v>
+      <c r="F188" s="13">
+        <v>5</v>
       </c>
       <c r="G188" s="13">
-        <v>5</v>
+        <f t="shared" si="5"/>
+        <v>4</v>
       </c>
       <c r="H188" s="13" t="b">
         <v>0</v>
@@ -7908,10 +8719,13 @@
       <c r="K188" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="189" spans="1:11">
+      <c r="O188" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15">
       <c r="A189" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>185</v>
       </c>
       <c r="B189" s="12" t="s">
@@ -7926,11 +8740,12 @@
       <c r="E189" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F189" s="13" t="s">
-        <v>70</v>
+      <c r="F189" s="13">
+        <v>6</v>
       </c>
       <c r="G189" s="13">
-        <v>6</v>
+        <f t="shared" si="5"/>
+        <v>5</v>
       </c>
       <c r="H189" s="13" t="b">
         <v>0</v>
@@ -7944,10 +8759,13 @@
       <c r="K189" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="190" spans="1:11">
+      <c r="O189" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15">
       <c r="A190" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>186</v>
       </c>
       <c r="B190" s="12" t="s">
@@ -7962,11 +8780,12 @@
       <c r="E190" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F190" s="13" t="s">
-        <v>70</v>
+      <c r="F190" s="13">
+        <v>7</v>
       </c>
       <c r="G190" s="13">
-        <v>7</v>
+        <f t="shared" si="5"/>
+        <v>6</v>
       </c>
       <c r="H190" s="13" t="b">
         <v>1</v>
@@ -7980,10 +8799,13 @@
       <c r="K190" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="191" spans="1:11">
+      <c r="O190" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15">
       <c r="A191" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>187</v>
       </c>
       <c r="B191" s="12" t="s">
@@ -7998,11 +8820,12 @@
       <c r="E191" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F191" s="13" t="s">
-        <v>70</v>
+      <c r="F191" s="13">
+        <v>8</v>
       </c>
       <c r="G191" s="13">
-        <v>8</v>
+        <f t="shared" si="5"/>
+        <v>7</v>
       </c>
       <c r="H191" s="13" t="b">
         <v>1</v>
@@ -8016,10 +8839,13 @@
       <c r="K191" s="5">
         <v>38</v>
       </c>
-    </row>
-    <row r="192" spans="1:11">
+      <c r="O191" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15">
       <c r="A192" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>188</v>
       </c>
       <c r="B192" s="12" t="s">
@@ -8034,11 +8860,12 @@
       <c r="E192" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F192" s="13" t="s">
-        <v>71</v>
+      <c r="F192" s="13">
+        <v>9</v>
       </c>
       <c r="G192" s="13">
-        <v>9</v>
+        <f t="shared" si="5"/>
+        <v>8</v>
       </c>
       <c r="H192" s="13" t="b">
         <v>1</v>
@@ -8052,10 +8879,13 @@
       <c r="K192" s="5">
         <v>38</v>
       </c>
-    </row>
-    <row r="193" spans="1:12">
+      <c r="O192" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15">
       <c r="A193" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>189</v>
       </c>
       <c r="B193" s="12" t="s">
@@ -8070,11 +8900,12 @@
       <c r="E193" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F193" s="13" t="s">
-        <v>71</v>
+      <c r="F193" s="13">
+        <v>10</v>
       </c>
       <c r="G193" s="13">
-        <v>10</v>
+        <f t="shared" si="5"/>
+        <v>9</v>
       </c>
       <c r="H193" s="13" t="b">
         <v>1</v>
@@ -8088,10 +8919,13 @@
       <c r="K193" s="5">
         <v>38</v>
       </c>
-    </row>
-    <row r="194" spans="1:12">
+      <c r="O193" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15">
       <c r="A194" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="B194" s="12" t="s">
@@ -8106,11 +8940,12 @@
       <c r="E194" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F194" s="13" t="s">
-        <v>71</v>
+      <c r="F194" s="13">
+        <v>11</v>
       </c>
       <c r="G194" s="13">
-        <v>11</v>
+        <f t="shared" si="5"/>
+        <v>10</v>
       </c>
       <c r="H194" s="13" t="b">
         <v>1</v>
@@ -8124,10 +8959,13 @@
       <c r="K194" s="5">
         <v>87</v>
       </c>
-    </row>
-    <row r="195" spans="1:12">
+      <c r="O194" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15">
       <c r="A195" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>191</v>
       </c>
       <c r="B195" s="12" t="s">
@@ -8142,11 +8980,12 @@
       <c r="E195" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F195" s="13" t="s">
-        <v>72</v>
+      <c r="F195" s="13">
+        <v>12</v>
       </c>
       <c r="G195" s="13">
-        <v>12</v>
+        <f t="shared" si="5"/>
+        <v>11</v>
       </c>
       <c r="H195" s="13" t="b">
         <v>1</v>
@@ -8160,10 +8999,13 @@
       <c r="K195" s="5">
         <v>87</v>
       </c>
-    </row>
-    <row r="196" spans="1:12">
+      <c r="O195" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15">
       <c r="A196" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>192</v>
       </c>
       <c r="B196" s="12" t="s">
@@ -8178,11 +9020,12 @@
       <c r="E196" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F196" s="13" t="s">
-        <v>72</v>
+      <c r="F196" s="13">
+        <v>13</v>
       </c>
       <c r="G196" s="13">
-        <v>13</v>
+        <f t="shared" si="5"/>
+        <v>12</v>
       </c>
       <c r="H196" s="13" t="b">
         <v>1</v>
@@ -8196,10 +9039,13 @@
       <c r="K196" s="5">
         <v>87</v>
       </c>
-    </row>
-    <row r="197" spans="1:12">
+      <c r="O196" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15">
       <c r="A197" s="11">
-        <f t="shared" ref="A197:A260" si="3">ROW()-4</f>
+        <f t="shared" ref="A197:A260" si="6">ROW()-4</f>
         <v>193</v>
       </c>
       <c r="B197" s="12" t="s">
@@ -8214,11 +9060,12 @@
       <c r="E197" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F197" s="13" t="s">
-        <v>72</v>
+      <c r="F197" s="13">
+        <v>14</v>
       </c>
       <c r="G197" s="13">
-        <v>14</v>
+        <f t="shared" ref="G197:G260" si="7">F197-1</f>
+        <v>13</v>
       </c>
       <c r="H197" s="13" t="b">
         <v>1</v>
@@ -8233,10 +9080,14 @@
         <v>198</v>
       </c>
       <c r="L197" s="13"/>
-    </row>
-    <row r="198" spans="1:12">
+      <c r="M197" s="13"/>
+      <c r="O197" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15">
       <c r="A198" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>194</v>
       </c>
       <c r="B198" s="12" t="s">
@@ -8251,11 +9102,12 @@
       <c r="E198" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F198" s="13" t="s">
-        <v>72</v>
+      <c r="F198" s="13">
+        <v>15</v>
       </c>
       <c r="G198" s="13">
-        <v>15</v>
+        <f t="shared" si="7"/>
+        <v>14</v>
       </c>
       <c r="H198" s="13" t="b">
         <v>1</v>
@@ -8270,10 +9122,14 @@
         <v>594</v>
       </c>
       <c r="L198" s="13"/>
-    </row>
-    <row r="199" spans="1:12">
+      <c r="M198" s="13"/>
+      <c r="O198" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15">
       <c r="A199" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>195</v>
       </c>
       <c r="B199" s="12" t="s">
@@ -8288,11 +9144,12 @@
       <c r="E199" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F199" s="13" t="s">
-        <v>69</v>
+      <c r="F199" s="13">
+        <v>1</v>
       </c>
       <c r="G199" s="13">
-        <v>1</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="H199" s="13" t="b">
         <v>1</v>
@@ -8307,10 +9164,14 @@
         <v>38</v>
       </c>
       <c r="L199" s="13"/>
-    </row>
-    <row r="200" spans="1:12">
+      <c r="M199" s="13"/>
+      <c r="O199" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15">
       <c r="A200" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>196</v>
       </c>
       <c r="B200" s="12" t="s">
@@ -8325,11 +9186,12 @@
       <c r="E200" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F200" s="13" t="s">
-        <v>69</v>
+      <c r="F200" s="13">
+        <v>2</v>
       </c>
       <c r="G200" s="13">
-        <v>2</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="H200" s="13" t="b">
         <v>1</v>
@@ -8343,10 +9205,13 @@
       <c r="K200" s="13">
         <v>87</v>
       </c>
-    </row>
-    <row r="201" spans="1:12">
+      <c r="O200" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15">
       <c r="A201" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>197</v>
       </c>
       <c r="B201" s="12" t="s">
@@ -8361,11 +9226,12 @@
       <c r="E201" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F201" s="13" t="s">
-        <v>69</v>
+      <c r="F201" s="13">
+        <v>3</v>
       </c>
       <c r="G201" s="13">
-        <v>3</v>
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
       <c r="H201" s="13" t="b">
         <v>1</v>
@@ -8379,10 +9245,13 @@
       <c r="K201" s="13">
         <v>198</v>
       </c>
-    </row>
-    <row r="202" spans="1:12">
+      <c r="O201" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15">
       <c r="A202" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>198</v>
       </c>
       <c r="B202" s="12" t="s">
@@ -8397,11 +9266,12 @@
       <c r="E202" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F202" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G202" s="5">
-        <v>1</v>
+      <c r="F202" s="5">
+        <v>1</v>
+      </c>
+      <c r="G202" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="H202" s="13" t="b">
         <v>0</v>
@@ -8415,10 +9285,13 @@
       <c r="K202" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="203" spans="1:12">
+      <c r="O202" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15">
       <c r="A203" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>199</v>
       </c>
       <c r="B203" s="12" t="s">
@@ -8433,11 +9306,12 @@
       <c r="E203" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F203" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G203" s="5">
+      <c r="F203" s="5">
         <v>2</v>
+      </c>
+      <c r="G203" s="13">
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="H203" s="13" t="b">
         <v>0</v>
@@ -8451,10 +9325,13 @@
       <c r="K203" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="204" spans="1:12">
+      <c r="O203" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15">
       <c r="A204" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>200</v>
       </c>
       <c r="B204" s="12" t="s">
@@ -8469,11 +9346,12 @@
       <c r="E204" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F204" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G204" s="5">
+      <c r="F204" s="5">
         <v>3</v>
+      </c>
+      <c r="G204" s="13">
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
       <c r="H204" s="13" t="b">
         <v>0</v>
@@ -8487,10 +9365,13 @@
       <c r="K204" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="205" spans="1:12">
+      <c r="O204" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15">
       <c r="A205" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>201</v>
       </c>
       <c r="B205" s="12" t="s">
@@ -8505,11 +9386,12 @@
       <c r="E205" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F205" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G205" s="5">
+      <c r="F205" s="5">
         <v>4</v>
+      </c>
+      <c r="G205" s="13">
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
       <c r="H205" s="13" t="b">
         <v>0</v>
@@ -8523,10 +9405,13 @@
       <c r="K205" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="206" spans="1:12">
+      <c r="O205" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15">
       <c r="A206" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>202</v>
       </c>
       <c r="B206" s="12" t="s">
@@ -8541,11 +9426,12 @@
       <c r="E206" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F206" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G206" s="5">
+      <c r="F206" s="5">
         <v>5</v>
+      </c>
+      <c r="G206" s="13">
+        <f t="shared" si="7"/>
+        <v>4</v>
       </c>
       <c r="H206" s="13" t="b">
         <v>0</v>
@@ -8559,10 +9445,13 @@
       <c r="K206" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="207" spans="1:12">
+      <c r="O206" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15">
       <c r="A207" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>203</v>
       </c>
       <c r="B207" s="12" t="s">
@@ -8577,11 +9466,12 @@
       <c r="E207" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F207" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G207" s="5">
-        <v>1</v>
+      <c r="F207" s="5">
+        <v>1</v>
+      </c>
+      <c r="G207" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="H207" s="13" t="b">
         <v>0</v>
@@ -8595,10 +9485,13 @@
       <c r="K207" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="208" spans="1:12">
+      <c r="O207" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15">
       <c r="A208" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>204</v>
       </c>
       <c r="B208" s="12" t="s">
@@ -8613,11 +9506,12 @@
       <c r="E208" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F208" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G208" s="5">
+      <c r="F208" s="5">
         <v>2</v>
+      </c>
+      <c r="G208" s="13">
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="H208" s="13" t="b">
         <v>0</v>
@@ -8631,10 +9525,13 @@
       <c r="K208" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="209" spans="1:11">
+      <c r="O208" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15">
       <c r="A209" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>205</v>
       </c>
       <c r="B209" s="12" t="s">
@@ -8649,11 +9546,12 @@
       <c r="E209" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F209" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G209" s="5">
+      <c r="F209" s="5">
         <v>3</v>
+      </c>
+      <c r="G209" s="13">
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
       <c r="H209" s="13" t="b">
         <v>0</v>
@@ -8667,10 +9565,13 @@
       <c r="K209" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="210" spans="1:11">
+      <c r="O209" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15">
       <c r="A210" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>206</v>
       </c>
       <c r="B210" s="12" t="s">
@@ -8685,11 +9586,12 @@
       <c r="E210" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F210" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G210" s="5">
+      <c r="F210" s="5">
         <v>4</v>
+      </c>
+      <c r="G210" s="13">
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
       <c r="H210" s="13" t="b">
         <v>0</v>
@@ -8703,10 +9605,13 @@
       <c r="K210" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="211" spans="1:11">
+      <c r="O210" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15">
       <c r="A211" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>207</v>
       </c>
       <c r="B211" s="12" t="s">
@@ -8721,11 +9626,12 @@
       <c r="E211" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F211" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G211" s="5">
+      <c r="F211" s="5">
         <v>5</v>
+      </c>
+      <c r="G211" s="13">
+        <f t="shared" si="7"/>
+        <v>4</v>
       </c>
       <c r="H211" s="13" t="b">
         <v>0</v>
@@ -8739,10 +9645,13 @@
       <c r="K211" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="212" spans="1:11">
+      <c r="O211" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15">
       <c r="A212" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>208</v>
       </c>
       <c r="B212" s="12" t="s">
@@ -8757,11 +9666,12 @@
       <c r="E212" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F212" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G212" s="5">
-        <v>1</v>
+      <c r="F212" s="5">
+        <v>1</v>
+      </c>
+      <c r="G212" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="H212" s="13" t="b">
         <v>0</v>
@@ -8775,10 +9685,13 @@
       <c r="K212" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="213" spans="1:11">
+      <c r="O212" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15">
       <c r="A213" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>209</v>
       </c>
       <c r="B213" s="12" t="s">
@@ -8793,11 +9706,12 @@
       <c r="E213" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F213" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G213" s="5">
+      <c r="F213" s="5">
         <v>2</v>
+      </c>
+      <c r="G213" s="13">
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="H213" s="13" t="b">
         <v>0</v>
@@ -8811,10 +9725,13 @@
       <c r="K213" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="214" spans="1:11">
+      <c r="O213" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15">
       <c r="A214" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>210</v>
       </c>
       <c r="B214" s="12" t="s">
@@ -8829,11 +9746,12 @@
       <c r="E214" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F214" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G214" s="5">
+      <c r="F214" s="5">
         <v>3</v>
+      </c>
+      <c r="G214" s="13">
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
       <c r="H214" s="13" t="b">
         <v>0</v>
@@ -8847,10 +9765,13 @@
       <c r="K214" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="215" spans="1:11">
+      <c r="O214" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15">
       <c r="A215" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>211</v>
       </c>
       <c r="B215" s="12" t="s">
@@ -8865,11 +9786,12 @@
       <c r="E215" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F215" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G215" s="5">
+      <c r="F215" s="5">
         <v>4</v>
+      </c>
+      <c r="G215" s="13">
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
       <c r="H215" s="13" t="b">
         <v>0</v>
@@ -8883,10 +9805,13 @@
       <c r="K215" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="216" spans="1:11">
+      <c r="O215" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15">
       <c r="A216" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>212</v>
       </c>
       <c r="B216" s="12" t="s">
@@ -8901,11 +9826,12 @@
       <c r="E216" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F216" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G216" s="5">
+      <c r="F216" s="5">
         <v>5</v>
+      </c>
+      <c r="G216" s="13">
+        <f t="shared" si="7"/>
+        <v>4</v>
       </c>
       <c r="H216" s="13" t="b">
         <v>0</v>
@@ -8919,10 +9845,13 @@
       <c r="K216" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="217" spans="1:11">
+      <c r="O216" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15">
       <c r="A217" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>213</v>
       </c>
       <c r="B217" s="12" t="s">
@@ -8937,11 +9866,12 @@
       <c r="E217" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F217" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G217" s="5">
+      <c r="F217" s="5">
         <v>6</v>
+      </c>
+      <c r="G217" s="13">
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
       <c r="H217" s="13" t="b">
         <v>0</v>
@@ -8955,10 +9885,13 @@
       <c r="K217" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="218" spans="1:11">
+      <c r="O217" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15">
       <c r="A218" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>214</v>
       </c>
       <c r="B218" s="12" t="s">
@@ -8973,11 +9906,12 @@
       <c r="E218" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F218" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G218" s="5">
+      <c r="F218" s="5">
         <v>7</v>
+      </c>
+      <c r="G218" s="13">
+        <f t="shared" si="7"/>
+        <v>6</v>
       </c>
       <c r="H218" s="13" t="b">
         <v>0</v>
@@ -8991,10 +9925,13 @@
       <c r="K218" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="219" spans="1:11">
+      <c r="O218" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15">
       <c r="A219" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>215</v>
       </c>
       <c r="B219" s="12" t="s">
@@ -9009,11 +9946,12 @@
       <c r="E219" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F219" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="G219" s="5">
+      <c r="F219" s="5">
         <v>8</v>
+      </c>
+      <c r="G219" s="13">
+        <f t="shared" si="7"/>
+        <v>7</v>
       </c>
       <c r="H219" s="13" t="b">
         <v>0</v>
@@ -9027,10 +9965,13 @@
       <c r="K219" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="220" spans="1:11">
+      <c r="O219" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15">
       <c r="A220" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>216</v>
       </c>
       <c r="B220" s="12" t="s">
@@ -9045,11 +9986,12 @@
       <c r="E220" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F220" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G220" s="5">
-        <v>1</v>
+      <c r="F220" s="5">
+        <v>1</v>
+      </c>
+      <c r="G220" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="H220" s="13" t="b">
         <v>0</v>
@@ -9063,10 +10005,13 @@
       <c r="K220" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="221" spans="1:11">
+      <c r="O220" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15">
       <c r="A221" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>217</v>
       </c>
       <c r="B221" s="12" t="s">
@@ -9081,11 +10026,12 @@
       <c r="E221" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F221" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G221" s="5">
+      <c r="F221" s="5">
         <v>2</v>
+      </c>
+      <c r="G221" s="13">
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="H221" s="13" t="b">
         <v>0</v>
@@ -9099,10 +10045,13 @@
       <c r="K221" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="222" spans="1:11">
+      <c r="O221" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="222" spans="1:15">
       <c r="A222" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>218</v>
       </c>
       <c r="B222" s="12" t="s">
@@ -9117,11 +10066,12 @@
       <c r="E222" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F222" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G222" s="5">
+      <c r="F222" s="5">
         <v>3</v>
+      </c>
+      <c r="G222" s="13">
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
       <c r="H222" s="13" t="b">
         <v>0</v>
@@ -9135,10 +10085,13 @@
       <c r="K222" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="223" spans="1:11">
+      <c r="O222" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15">
       <c r="A223" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>219</v>
       </c>
       <c r="B223" s="12" t="s">
@@ -9153,11 +10106,12 @@
       <c r="E223" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F223" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G223" s="5">
+      <c r="F223" s="5">
         <v>4</v>
+      </c>
+      <c r="G223" s="13">
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
       <c r="H223" s="13" t="b">
         <v>0</v>
@@ -9171,10 +10125,13 @@
       <c r="K223" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="224" spans="1:11">
+      <c r="O223" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="224" spans="1:15">
       <c r="A224" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>220</v>
       </c>
       <c r="B224" s="12" t="s">
@@ -9189,11 +10146,12 @@
       <c r="E224" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F224" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G224" s="5">
+      <c r="F224" s="5">
         <v>5</v>
+      </c>
+      <c r="G224" s="13">
+        <f t="shared" si="7"/>
+        <v>4</v>
       </c>
       <c r="H224" s="13" t="b">
         <v>0</v>
@@ -9207,10 +10165,13 @@
       <c r="K224" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="225" spans="1:11">
+      <c r="O224" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="225" spans="1:15">
       <c r="A225" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>221</v>
       </c>
       <c r="B225" s="12" t="s">
@@ -9225,11 +10186,12 @@
       <c r="E225" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F225" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="G225" s="5">
+      <c r="F225" s="5">
         <v>6</v>
+      </c>
+      <c r="G225" s="13">
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
       <c r="H225" s="13" t="b">
         <v>0</v>
@@ -9243,10 +10205,13 @@
       <c r="K225" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="226" spans="1:11">
+      <c r="O225" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="226" spans="1:15">
       <c r="A226" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>222</v>
       </c>
       <c r="B226" s="12" t="s">
@@ -9261,11 +10226,12 @@
       <c r="E226" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F226" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G226" s="5">
-        <v>1</v>
+      <c r="F226" s="5">
+        <v>1</v>
+      </c>
+      <c r="G226" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="H226" s="13" t="b">
         <v>0</v>
@@ -9279,10 +10245,13 @@
       <c r="K226" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="227" spans="1:11">
+      <c r="O226" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="227" spans="1:15">
       <c r="A227" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>223</v>
       </c>
       <c r="B227" s="12" t="s">
@@ -9297,11 +10266,12 @@
       <c r="E227" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F227" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G227" s="5">
+      <c r="F227" s="5">
         <v>2</v>
+      </c>
+      <c r="G227" s="13">
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="H227" s="13" t="b">
         <v>0</v>
@@ -9315,10 +10285,13 @@
       <c r="K227" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="228" spans="1:11">
+      <c r="O227" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="228" spans="1:15">
       <c r="A228" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>224</v>
       </c>
       <c r="B228" s="12" t="s">
@@ -9333,11 +10306,12 @@
       <c r="E228" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F228" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G228" s="5">
+      <c r="F228" s="5">
         <v>3</v>
+      </c>
+      <c r="G228" s="13">
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
       <c r="H228" s="13" t="b">
         <v>0</v>
@@ -9351,10 +10325,13 @@
       <c r="K228" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="229" spans="1:11">
+      <c r="O228" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15">
       <c r="A229" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>225</v>
       </c>
       <c r="B229" s="12" t="s">
@@ -9369,11 +10346,12 @@
       <c r="E229" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F229" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G229" s="5">
+      <c r="F229" s="5">
         <v>4</v>
+      </c>
+      <c r="G229" s="13">
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
       <c r="H229" s="13" t="b">
         <v>0</v>
@@ -9387,10 +10365,13 @@
       <c r="K229" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="230" spans="1:11">
+      <c r="O229" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15">
       <c r="A230" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>226</v>
       </c>
       <c r="B230" s="12" t="s">
@@ -9405,11 +10386,12 @@
       <c r="E230" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F230" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G230" s="5">
+      <c r="F230" s="5">
         <v>5</v>
+      </c>
+      <c r="G230" s="13">
+        <f t="shared" si="7"/>
+        <v>4</v>
       </c>
       <c r="H230" s="13" t="b">
         <v>0</v>
@@ -9423,10 +10405,13 @@
       <c r="K230" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="231" spans="1:11">
+      <c r="O230" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15">
       <c r="A231" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>227</v>
       </c>
       <c r="B231" s="12" t="s">
@@ -9441,11 +10426,12 @@
       <c r="E231" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F231" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G231" s="5">
+      <c r="F231" s="5">
         <v>6</v>
+      </c>
+      <c r="G231" s="13">
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
       <c r="H231" s="13" t="b">
         <v>0</v>
@@ -9459,10 +10445,13 @@
       <c r="K231" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="232" spans="1:11">
+      <c r="O231" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15">
       <c r="A232" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>228</v>
       </c>
       <c r="B232" s="12" t="s">
@@ -9477,11 +10466,12 @@
       <c r="E232" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F232" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G232" s="5">
+      <c r="F232" s="5">
         <v>7</v>
+      </c>
+      <c r="G232" s="13">
+        <f t="shared" si="7"/>
+        <v>6</v>
       </c>
       <c r="H232" s="13" t="b">
         <v>0</v>
@@ -9495,10 +10485,13 @@
       <c r="K232" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="233" spans="1:11">
+      <c r="O232" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="233" spans="1:15">
       <c r="A233" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>229</v>
       </c>
       <c r="B233" s="12" t="s">
@@ -9513,11 +10506,12 @@
       <c r="E233" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F233" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G233" s="5">
+      <c r="F233" s="5">
         <v>8</v>
+      </c>
+      <c r="G233" s="13">
+        <f t="shared" si="7"/>
+        <v>7</v>
       </c>
       <c r="H233" s="13" t="b">
         <v>0</v>
@@ -9531,10 +10525,13 @@
       <c r="K233" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="234" spans="1:11">
+      <c r="O233" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15">
       <c r="A234" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>230</v>
       </c>
       <c r="B234" s="12" t="s">
@@ -9549,11 +10546,12 @@
       <c r="E234" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F234" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G234" s="5">
+      <c r="F234" s="5">
         <v>9</v>
+      </c>
+      <c r="G234" s="13">
+        <f t="shared" si="7"/>
+        <v>8</v>
       </c>
       <c r="H234" s="13" t="b">
         <v>0</v>
@@ -9567,10 +10565,13 @@
       <c r="K234" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="235" spans="1:11">
+      <c r="O234" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="235" spans="1:15">
       <c r="A235" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>231</v>
       </c>
       <c r="B235" s="12" t="s">
@@ -9585,11 +10586,12 @@
       <c r="E235" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F235" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G235" s="5">
+      <c r="F235" s="5">
         <v>10</v>
+      </c>
+      <c r="G235" s="13">
+        <f t="shared" si="7"/>
+        <v>9</v>
       </c>
       <c r="H235" s="13" t="b">
         <v>0</v>
@@ -9603,10 +10605,13 @@
       <c r="K235" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="236" spans="1:11">
+      <c r="O235" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="236" spans="1:15">
       <c r="A236" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>232</v>
       </c>
       <c r="B236" s="12" t="s">
@@ -9621,11 +10626,12 @@
       <c r="E236" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F236" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G236" s="5">
+      <c r="F236" s="5">
         <v>11</v>
+      </c>
+      <c r="G236" s="13">
+        <f t="shared" si="7"/>
+        <v>10</v>
       </c>
       <c r="H236" s="13" t="b">
         <v>0</v>
@@ -9639,10 +10645,13 @@
       <c r="K236" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="237" spans="1:11">
+      <c r="O236" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="237" spans="1:15">
       <c r="A237" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>233</v>
       </c>
       <c r="B237" s="12" t="s">
@@ -9657,11 +10666,12 @@
       <c r="E237" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F237" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G237" s="5">
+      <c r="F237" s="5">
         <v>12</v>
+      </c>
+      <c r="G237" s="13">
+        <f t="shared" si="7"/>
+        <v>11</v>
       </c>
       <c r="H237" s="13" t="b">
         <v>0</v>
@@ -9675,10 +10685,13 @@
       <c r="K237" s="13">
         <v>87</v>
       </c>
-    </row>
-    <row r="238" spans="1:11">
+      <c r="O237" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="238" spans="1:15">
       <c r="A238" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>234</v>
       </c>
       <c r="B238" s="12" t="s">
@@ -9693,11 +10706,12 @@
       <c r="E238" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F238" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G238" s="5">
+      <c r="F238" s="5">
         <v>13</v>
+      </c>
+      <c r="G238" s="13">
+        <f t="shared" si="7"/>
+        <v>12</v>
       </c>
       <c r="H238" s="13" t="b">
         <v>0</v>
@@ -9711,10 +10725,13 @@
       <c r="K238" s="13">
         <v>87</v>
       </c>
-    </row>
-    <row r="239" spans="1:11">
+      <c r="O238" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="239" spans="1:15">
       <c r="A239" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>235</v>
       </c>
       <c r="B239" s="12" t="s">
@@ -9729,11 +10746,12 @@
       <c r="E239" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F239" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="G239" s="5">
+      <c r="F239" s="5">
         <v>14</v>
+      </c>
+      <c r="G239" s="13">
+        <f t="shared" si="7"/>
+        <v>13</v>
       </c>
       <c r="H239" s="13" t="b">
         <v>0</v>
@@ -9747,10 +10765,13 @@
       <c r="K239" s="13">
         <v>198</v>
       </c>
-    </row>
-    <row r="240" spans="1:11">
+      <c r="O239" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="240" spans="1:15">
       <c r="A240" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>236</v>
       </c>
       <c r="B240" s="12" t="s">
@@ -9765,11 +10786,12 @@
       <c r="E240" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F240" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G240" s="5">
-        <v>1</v>
+      <c r="F240" s="5">
+        <v>1</v>
+      </c>
+      <c r="G240" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="H240" s="13" t="b">
         <v>0</v>
@@ -9783,10 +10805,13 @@
       <c r="K240" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="241" spans="1:11">
+      <c r="O240" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15">
       <c r="A241" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>237</v>
       </c>
       <c r="B241" s="12" t="s">
@@ -9801,11 +10826,12 @@
       <c r="E241" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F241" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G241" s="5">
+      <c r="F241" s="5">
         <v>2</v>
+      </c>
+      <c r="G241" s="13">
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="H241" s="13" t="b">
         <v>0</v>
@@ -9819,10 +10845,13 @@
       <c r="K241" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="242" spans="1:11">
+      <c r="O241" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="242" spans="1:15">
       <c r="A242" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>238</v>
       </c>
       <c r="B242" s="12" t="s">
@@ -9837,11 +10866,12 @@
       <c r="E242" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F242" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G242" s="5">
+      <c r="F242" s="5">
         <v>3</v>
+      </c>
+      <c r="G242" s="13">
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
       <c r="H242" s="13" t="b">
         <v>0</v>
@@ -9855,10 +10885,13 @@
       <c r="K242" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="243" spans="1:11">
+      <c r="O242" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="243" spans="1:15">
       <c r="A243" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>239</v>
       </c>
       <c r="B243" s="12" t="s">
@@ -9873,11 +10906,12 @@
       <c r="E243" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F243" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G243" s="5">
+      <c r="F243" s="5">
         <v>4</v>
+      </c>
+      <c r="G243" s="13">
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
       <c r="H243" s="13" t="b">
         <v>0</v>
@@ -9891,10 +10925,13 @@
       <c r="K243" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="244" spans="1:11">
+      <c r="O243" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="244" spans="1:15">
       <c r="A244" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>240</v>
       </c>
       <c r="B244" s="12" t="s">
@@ -9909,11 +10946,12 @@
       <c r="E244" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F244" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G244" s="5">
+      <c r="F244" s="5">
         <v>5</v>
+      </c>
+      <c r="G244" s="13">
+        <f t="shared" si="7"/>
+        <v>4</v>
       </c>
       <c r="H244" s="13" t="b">
         <v>0</v>
@@ -9927,10 +10965,13 @@
       <c r="K244" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="245" spans="1:11">
+      <c r="O244" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="245" spans="1:15">
       <c r="A245" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>241</v>
       </c>
       <c r="B245" s="12" t="s">
@@ -9945,11 +10986,12 @@
       <c r="E245" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F245" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G245" s="5">
+      <c r="F245" s="5">
         <v>6</v>
+      </c>
+      <c r="G245" s="13">
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
       <c r="H245" s="13" t="b">
         <v>0</v>
@@ -9963,10 +11005,13 @@
       <c r="K245" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="246" spans="1:11">
+      <c r="O245" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="246" spans="1:15">
       <c r="A246" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>242</v>
       </c>
       <c r="B246" s="12" t="s">
@@ -9981,11 +11026,12 @@
       <c r="E246" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F246" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G246" s="5">
+      <c r="F246" s="5">
         <v>7</v>
+      </c>
+      <c r="G246" s="13">
+        <f t="shared" si="7"/>
+        <v>6</v>
       </c>
       <c r="H246" s="13" t="b">
         <v>0</v>
@@ -9999,10 +11045,13 @@
       <c r="K246" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="247" spans="1:11">
+      <c r="O246" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="247" spans="1:15">
       <c r="A247" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>243</v>
       </c>
       <c r="B247" s="12" t="s">
@@ -10017,11 +11066,12 @@
       <c r="E247" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F247" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G247" s="5">
+      <c r="F247" s="5">
         <v>8</v>
+      </c>
+      <c r="G247" s="13">
+        <f t="shared" si="7"/>
+        <v>7</v>
       </c>
       <c r="H247" s="13" t="b">
         <v>0</v>
@@ -10035,10 +11085,13 @@
       <c r="K247" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="248" spans="1:11">
+      <c r="O247" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="248" spans="1:15">
       <c r="A248" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>244</v>
       </c>
       <c r="B248" s="12" t="s">
@@ -10053,11 +11106,12 @@
       <c r="E248" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F248" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G248" s="5">
+      <c r="F248" s="5">
         <v>9</v>
+      </c>
+      <c r="G248" s="13">
+        <f t="shared" si="7"/>
+        <v>8</v>
       </c>
       <c r="H248" s="13" t="b">
         <v>0</v>
@@ -10071,10 +11125,13 @@
       <c r="K248" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="249" spans="1:11">
+      <c r="O248" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="249" spans="1:15">
       <c r="A249" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>245</v>
       </c>
       <c r="B249" s="12" t="s">
@@ -10089,11 +11146,12 @@
       <c r="E249" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F249" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G249" s="5">
+      <c r="F249" s="5">
         <v>10</v>
+      </c>
+      <c r="G249" s="13">
+        <f t="shared" si="7"/>
+        <v>9</v>
       </c>
       <c r="H249" s="13" t="b">
         <v>0</v>
@@ -10107,10 +11165,13 @@
       <c r="K249" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="250" spans="1:11">
+      <c r="O249" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="250" spans="1:15">
       <c r="A250" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>246</v>
       </c>
       <c r="B250" s="12" t="s">
@@ -10125,11 +11186,12 @@
       <c r="E250" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F250" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G250" s="5">
+      <c r="F250" s="5">
         <v>11</v>
+      </c>
+      <c r="G250" s="13">
+        <f t="shared" si="7"/>
+        <v>10</v>
       </c>
       <c r="H250" s="13" t="b">
         <v>0</v>
@@ -10143,10 +11205,13 @@
       <c r="K250" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="251" spans="1:11">
+      <c r="O250" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="251" spans="1:15">
       <c r="A251" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>247</v>
       </c>
       <c r="B251" s="12" t="s">
@@ -10161,11 +11226,12 @@
       <c r="E251" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F251" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G251" s="5">
+      <c r="F251" s="5">
         <v>12</v>
+      </c>
+      <c r="G251" s="13">
+        <f t="shared" si="7"/>
+        <v>11</v>
       </c>
       <c r="H251" s="13" t="b">
         <v>0</v>
@@ -10179,10 +11245,13 @@
       <c r="K251" s="13">
         <v>87</v>
       </c>
-    </row>
-    <row r="252" spans="1:11">
+      <c r="O251" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="252" spans="1:15">
       <c r="A252" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>248</v>
       </c>
       <c r="B252" s="12" t="s">
@@ -10197,11 +11266,12 @@
       <c r="E252" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F252" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G252" s="5">
+      <c r="F252" s="5">
         <v>13</v>
+      </c>
+      <c r="G252" s="13">
+        <f t="shared" si="7"/>
+        <v>12</v>
       </c>
       <c r="H252" s="13" t="b">
         <v>0</v>
@@ -10215,10 +11285,13 @@
       <c r="K252" s="13">
         <v>87</v>
       </c>
-    </row>
-    <row r="253" spans="1:11">
+      <c r="O252" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="253" spans="1:15">
       <c r="A253" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>249</v>
       </c>
       <c r="B253" s="12" t="s">
@@ -10233,11 +11306,12 @@
       <c r="E253" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F253" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="G253" s="5">
+      <c r="F253" s="5">
         <v>14</v>
+      </c>
+      <c r="G253" s="13">
+        <f t="shared" si="7"/>
+        <v>13</v>
       </c>
       <c r="H253" s="13" t="b">
         <v>0</v>
@@ -10251,10 +11325,13 @@
       <c r="K253" s="13">
         <v>198</v>
       </c>
-    </row>
-    <row r="254" spans="1:11">
+      <c r="O253" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="254" spans="1:15">
       <c r="A254" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>250</v>
       </c>
       <c r="B254" s="12" t="s">
@@ -10269,11 +11346,12 @@
       <c r="E254" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F254" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G254" s="5">
-        <v>1</v>
+      <c r="F254" s="5">
+        <v>1</v>
+      </c>
+      <c r="G254" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="H254" s="13" t="b">
         <v>0</v>
@@ -10287,10 +11365,13 @@
       <c r="K254" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="255" spans="1:11">
+      <c r="O254" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="255" spans="1:15">
       <c r="A255" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>251</v>
       </c>
       <c r="B255" s="12" t="s">
@@ -10305,11 +11386,12 @@
       <c r="E255" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F255" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G255" s="5">
+      <c r="F255" s="5">
         <v>2</v>
+      </c>
+      <c r="G255" s="13">
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="H255" s="13" t="b">
         <v>0</v>
@@ -10323,10 +11405,13 @@
       <c r="K255" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="256" spans="1:11">
+      <c r="O255" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="256" spans="1:15">
       <c r="A256" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>252</v>
       </c>
       <c r="B256" s="12" t="s">
@@ -10341,11 +11426,12 @@
       <c r="E256" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F256" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="G256" s="5">
+      <c r="F256" s="5">
         <v>3</v>
+      </c>
+      <c r="G256" s="13">
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
       <c r="H256" s="13" t="b">
         <v>0</v>
@@ -10359,10 +11445,13 @@
       <c r="K256" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="257" spans="1:12">
+      <c r="O256" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="257" spans="1:15">
       <c r="A257" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>253</v>
       </c>
       <c r="B257" s="12" t="s">
@@ -10377,11 +11466,12 @@
       <c r="E257" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F257" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G257" s="5">
+      <c r="F257" s="5">
         <v>4</v>
+      </c>
+      <c r="G257" s="13">
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
       <c r="H257" s="13" t="b">
         <v>0</v>
@@ -10395,10 +11485,13 @@
       <c r="K257" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="258" spans="1:12">
+      <c r="O257" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="258" spans="1:15">
       <c r="A258" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>254</v>
       </c>
       <c r="B258" s="12" t="s">
@@ -10413,11 +11506,12 @@
       <c r="E258" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F258" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G258" s="5">
+      <c r="F258" s="5">
         <v>5</v>
+      </c>
+      <c r="G258" s="13">
+        <f t="shared" si="7"/>
+        <v>4</v>
       </c>
       <c r="H258" s="13" t="b">
         <v>0</v>
@@ -10431,10 +11525,13 @@
       <c r="K258" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="259" spans="1:12">
+      <c r="O258" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="259" spans="1:15">
       <c r="A259" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>255</v>
       </c>
       <c r="B259" s="12" t="s">
@@ -10449,11 +11546,12 @@
       <c r="E259" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F259" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G259" s="5">
+      <c r="F259" s="5">
         <v>6</v>
+      </c>
+      <c r="G259" s="13">
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
       <c r="H259" s="13" t="b">
         <v>0</v>
@@ -10467,10 +11565,13 @@
       <c r="K259" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="260" spans="1:12">
+      <c r="O259" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="260" spans="1:15">
       <c r="A260" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>256</v>
       </c>
       <c r="B260" s="12" t="s">
@@ -10485,11 +11586,12 @@
       <c r="E260" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F260" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G260" s="5">
+      <c r="F260" s="5">
         <v>7</v>
+      </c>
+      <c r="G260" s="13">
+        <f t="shared" si="7"/>
+        <v>6</v>
       </c>
       <c r="H260" s="13" t="b">
         <v>0</v>
@@ -10503,10 +11605,13 @@
       <c r="K260" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="261" spans="1:12">
+      <c r="O260" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="261" spans="1:15">
       <c r="A261" s="11">
-        <f t="shared" ref="A261:A267" si="4">ROW()-4</f>
+        <f t="shared" ref="A261:A267" si="8">ROW()-4</f>
         <v>257</v>
       </c>
       <c r="B261" s="12" t="s">
@@ -10521,11 +11626,12 @@
       <c r="E261" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F261" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G261" s="5">
+      <c r="F261" s="5">
         <v>8</v>
+      </c>
+      <c r="G261" s="13">
+        <f t="shared" ref="G261:G267" si="9">F261-1</f>
+        <v>7</v>
       </c>
       <c r="H261" s="13" t="b">
         <v>0</v>
@@ -10539,10 +11645,13 @@
       <c r="K261" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="262" spans="1:12">
+      <c r="O261" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="262" spans="1:15">
       <c r="A262" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>258</v>
       </c>
       <c r="B262" s="12" t="s">
@@ -10557,11 +11666,12 @@
       <c r="E262" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F262" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G262" s="5">
+      <c r="F262" s="5">
         <v>9</v>
+      </c>
+      <c r="G262" s="13">
+        <f t="shared" si="9"/>
+        <v>8</v>
       </c>
       <c r="H262" s="13" t="b">
         <v>1</v>
@@ -10575,10 +11685,13 @@
       <c r="K262" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="263" spans="1:12">
+      <c r="O262" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="263" spans="1:15">
       <c r="A263" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>259</v>
       </c>
       <c r="B263" s="12" t="s">
@@ -10593,11 +11706,12 @@
       <c r="E263" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F263" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G263" s="5">
+      <c r="F263" s="5">
         <v>10</v>
+      </c>
+      <c r="G263" s="13">
+        <f t="shared" si="9"/>
+        <v>9</v>
       </c>
       <c r="H263" s="13" t="b">
         <v>1</v>
@@ -10611,10 +11725,13 @@
       <c r="K263" s="13">
         <v>38</v>
       </c>
-    </row>
-    <row r="264" spans="1:12">
+      <c r="O263" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="264" spans="1:15">
       <c r="A264" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>260</v>
       </c>
       <c r="B264" s="12" t="s">
@@ -10629,11 +11746,12 @@
       <c r="E264" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F264" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="G264" s="5">
+      <c r="F264" s="5">
         <v>11</v>
+      </c>
+      <c r="G264" s="13">
+        <f t="shared" si="9"/>
+        <v>10</v>
       </c>
       <c r="H264" s="13" t="b">
         <v>1</v>
@@ -10647,10 +11765,13 @@
       <c r="K264" s="13">
         <v>87</v>
       </c>
-    </row>
-    <row r="265" spans="1:12">
+      <c r="O264" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="265" spans="1:15">
       <c r="A265" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>261</v>
       </c>
       <c r="B265" s="12" t="s">
@@ -10665,11 +11786,12 @@
       <c r="E265" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F265" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="G265" s="5">
+      <c r="F265" s="5">
         <v>12</v>
+      </c>
+      <c r="G265" s="13">
+        <f t="shared" si="9"/>
+        <v>11</v>
       </c>
       <c r="H265" s="13" t="b">
         <v>1</v>
@@ -10683,10 +11805,13 @@
       <c r="K265" s="13">
         <v>87</v>
       </c>
-    </row>
-    <row r="266" spans="1:12">
+      <c r="O265" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="266" spans="1:15">
       <c r="A266" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>262</v>
       </c>
       <c r="B266" s="12" t="s">
@@ -10701,11 +11826,12 @@
       <c r="E266" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F266" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="G266" s="5">
-        <v>1</v>
+      <c r="F266" s="5">
+        <v>1</v>
+      </c>
+      <c r="G266" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="H266" s="13" t="b">
         <v>1</v>
@@ -10719,10 +11845,13 @@
       <c r="K266" s="13">
         <v>13</v>
       </c>
-    </row>
-    <row r="267" spans="1:12">
+      <c r="O266" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="267" spans="1:15">
       <c r="A267" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>263</v>
       </c>
       <c r="B267" s="12" t="s">
@@ -10737,11 +11866,12 @@
       <c r="E267" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F267" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="G267" s="5">
-        <v>1</v>
+      <c r="F267" s="5">
+        <v>1</v>
+      </c>
+      <c r="G267" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="H267" s="13" t="b">
         <v>1</v>
@@ -10758,48 +11888,51 @@
       <c r="L267" s="5" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="268" spans="1:12">
+      <c r="O267" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="268" spans="1:15">
       <c r="A268" s="11"/>
       <c r="B268" s="12"/>
       <c r="C268" s="12"/>
       <c r="E268" s="12"/>
-      <c r="F268" s="13"/>
       <c r="H268" s="13"/>
       <c r="J268" s="15"/>
       <c r="K268" s="13"/>
-    </row>
-    <row r="269" spans="1:12">
+      <c r="O268" s="13"/>
+    </row>
+    <row r="269" spans="1:15">
       <c r="A269" s="11"/>
       <c r="B269" s="12"/>
       <c r="C269" s="12"/>
       <c r="E269" s="12"/>
-      <c r="F269" s="13"/>
       <c r="H269" s="13"/>
       <c r="J269" s="15"/>
       <c r="K269" s="13"/>
-    </row>
-    <row r="270" spans="1:12">
+      <c r="O269" s="13"/>
+    </row>
+    <row r="270" spans="1:15">
       <c r="A270" s="11"/>
       <c r="B270" s="12"/>
       <c r="C270" s="12"/>
       <c r="E270" s="12"/>
-      <c r="F270" s="13"/>
       <c r="H270" s="13"/>
       <c r="J270" s="15"/>
       <c r="K270" s="13"/>
-    </row>
-    <row r="271" spans="1:12">
+      <c r="O270" s="13"/>
+    </row>
+    <row r="271" spans="1:15">
       <c r="A271" s="11"/>
       <c r="B271" s="12"/>
       <c r="C271" s="12"/>
       <c r="E271" s="12"/>
-      <c r="F271" s="13"/>
       <c r="H271" s="13"/>
       <c r="J271" s="15"/>
       <c r="K271" s="13"/>
-    </row>
-    <row r="272" spans="1:12">
+      <c r="O271" s="13"/>
+    </row>
+    <row r="272" spans="1:15">
       <c r="A272" s="11"/>
       <c r="B272" s="12"/>
       <c r="C272" s="12"/>
@@ -11064,22 +12197,22 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B287" xr:uid="{EA80D64E-578A-4FE2-B978-0712AFDAAEE6}">
-      <formula1>$O$2:$O$3</formula1>
+      <formula1>$P$2:$P$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C287" xr:uid="{A88927D6-C705-42EA-93F9-56044FBF1090}">
-      <formula1>$P$2:$P$9</formula1>
+      <formula1>$Q$2:$Q$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F271" xr:uid="{B197848D-F103-4380-83AB-2CDAAF2AFD3C}">
-      <formula1>$S$2:$S$7</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O271" xr:uid="{B197848D-F103-4380-83AB-2CDAAF2AFD3C}">
+      <formula1>$T$2:$T$7</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H271" xr:uid="{4A1BC11C-DA03-43AB-9BCE-E2B3D7ABF0B6}">
-      <formula1>$O$8:$O$9</formula1>
+      <formula1>$P$8:$P$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E342" xr:uid="{269CC43C-2462-4F32-A11C-04284C405092}">
-      <formula1>$R$2:$R$43</formula1>
+      <formula1>$S$2:$S$43</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D267" xr:uid="{2F6AB2AA-CDCC-4A9C-BBFD-3B4002AE4F9B}">
-      <formula1>$Q$2:$Q$61</formula1>
+      <formula1>$R$2:$R$61</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/AddressableResource/Data/Excels/QuestData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/QuestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB36B37-507E-4E63-B961-06C042F84E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C224A0-EDE1-4BF9-8782-8136BD6D4329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -948,7 +948,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:U700"/>
+  <dimension ref="A1:S700"/>
   <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.625" style="3" customWidth="1"/>
@@ -970,11 +970,10 @@
     <col min="17" max="17" width="42.5" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="42.5" style="2" customWidth="1"/>
     <col min="19" max="19" width="11.75" style="15" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="10.625" style="15"/>
-    <col min="22" max="16384" width="10.625" style="2"/>
+    <col min="20" max="16384" width="10.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1027,9 +1026,8 @@
       <c r="S1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="2"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
@@ -1082,9 +1080,8 @@
       <c r="S2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="T2" s="2"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
@@ -1119,9 +1116,8 @@
       <c r="S3" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="T3" s="2"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
         <f>ROW()-4</f>
         <v>0</v>
@@ -1173,9 +1169,8 @@
       <c r="S4" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="T4" s="2"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <f t="shared" ref="A5:A163" si="0">ROW()-4</f>
         <v>1</v>
@@ -1228,9 +1223,8 @@
       <c r="S5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="T5" s="2"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1283,9 +1277,8 @@
       <c r="S6" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="T6" s="2"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1339,7 +1332,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1389,7 +1382,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1442,7 +1435,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1487,7 +1480,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1534,7 +1527,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1581,7 +1574,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1627,7 +1620,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1674,7 +1667,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1718,7 +1711,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <f t="shared" si="0"/>
         <v>12</v>

--- a/Assets/AddressableResource/Data/Excels/QuestData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/QuestData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CAA80B-E7AA-439E-BE35-3AFEF0571298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F2DFDC2-F038-47B3-B4F1-A3F5CB5E4D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1106,6 +1106,9 @@
       <c r="K4" s="12">
         <v>1</v>
       </c>
+      <c r="L4" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="M4" s="2"/>
       <c r="P4" s="2" t="s">
         <v>26</v>
@@ -1259,6 +1262,9 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
+      <c r="L7" s="2" t="s">
+        <v>105</v>
+      </c>
       <c r="M7" s="2"/>
       <c r="P7" s="2" t="s">
         <v>29</v>
@@ -1310,9 +1316,6 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="O8" s="15" t="b">
         <v>1</v>
       </c>
@@ -1634,9 +1637,6 @@
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="Q15" s="2" t="s">
         <v>45</v>
       </c>
@@ -1680,6 +1680,9 @@
       <c r="K16" s="12">
         <v>1</v>
       </c>
+      <c r="L16" s="2" t="s">
+        <v>103</v>
+      </c>
       <c r="Q16" s="2" t="s">
         <v>46</v>
       </c>
@@ -1767,9 +1770,6 @@
       <c r="K18" s="5">
         <v>5</v>
       </c>
-      <c r="L18" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="O18" s="15"/>
       <c r="Q18" s="2" t="s">
         <v>48</v>
@@ -1980,6 +1980,9 @@
       <c r="K23" s="12">
         <v>1</v>
       </c>
+      <c r="L23" s="2" t="s">
+        <v>106</v>
+      </c>
       <c r="M23" s="16"/>
       <c r="Q23" s="2" t="s">
         <v>53</v>
@@ -2108,7 +2111,9 @@
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="L26" s="13"/>
+      <c r="L26" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="M26" s="16"/>
       <c r="Q26" s="2" t="s">
         <v>56</v>
@@ -2151,9 +2156,6 @@
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="L27" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="M27" s="16"/>
       <c r="Q27" s="2" t="s">
         <v>57</v>
@@ -2451,9 +2453,6 @@
         <f t="shared" si="6"/>
         <v>26</v>
       </c>
-      <c r="L34" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="M34" s="12"/>
       <c r="Q34" s="2" t="s">
         <v>64</v>
@@ -2495,6 +2494,9 @@
       <c r="K35" s="12">
         <v>1</v>
       </c>
+      <c r="L35" s="2" t="s">
+        <v>107</v>
+      </c>
       <c r="M35" s="12"/>
       <c r="Q35" s="2" t="s">
         <v>65</v>
@@ -2578,7 +2580,9 @@
       <c r="K37" s="5">
         <v>3</v>
       </c>
-      <c r="L37" s="12"/>
+      <c r="L37" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="M37" s="12"/>
       <c r="Q37" s="2" t="s">
         <v>77</v>
@@ -2620,9 +2624,6 @@
       <c r="K38" s="12">
         <v>5</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="M38" s="12"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
@@ -2700,9 +2701,6 @@
       <c r="K40" s="12">
         <v>15</v>
       </c>
-      <c r="L40" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="M40" s="12"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
@@ -2858,7 +2856,9 @@
       <c r="K44" s="12">
         <v>1</v>
       </c>
-      <c r="L44" s="12"/>
+      <c r="L44" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="M44" s="12"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
@@ -2979,7 +2979,7 @@
         <v>4</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M47" s="12"/>
     </row>
@@ -3297,9 +3297,6 @@
         <f t="shared" si="10"/>
         <v>26</v>
       </c>
-      <c r="L55" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="M55" s="12"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
@@ -3378,7 +3375,9 @@
         <f>ROUNDUP(K56*1.5,0)</f>
         <v>2</v>
       </c>
-      <c r="L57" s="12"/>
+      <c r="L57" s="2" t="s">
+        <v>112</v>
+      </c>
       <c r="M57" s="12"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
@@ -3575,7 +3574,7 @@
         <v>200000</v>
       </c>
       <c r="K62" s="12">
-        <f t="shared" ref="K62:K84" si="14">ROUNDUP(K61*1.2,0)</f>
+        <f t="shared" ref="K62:K74" si="14">ROUNDUP(K61*1.2,0)</f>
         <v>12</v>
       </c>
       <c r="L62" s="12"/>
@@ -3741,9 +3740,6 @@
         <f t="shared" si="14"/>
         <v>27</v>
       </c>
-      <c r="L66" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="M66" s="12"/>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">
@@ -4109,7 +4105,7 @@
         <v>2600000</v>
       </c>
       <c r="K75" s="12">
-        <f t="shared" ref="K66:K84" si="19">ROUNDUP(K74*1.1,0)</f>
+        <f t="shared" ref="K75:K84" si="19">ROUNDUP(K74*1.1,0)</f>
         <v>135</v>
       </c>
     </row>
@@ -4225,7 +4221,7 @@
         <v>170000</v>
       </c>
       <c r="J78" s="18">
-        <f t="shared" ref="J70:J82" si="20">J79-300000</f>
+        <f t="shared" ref="J78:J82" si="20">J79-300000</f>
         <v>3200000</v>
       </c>
       <c r="K78" s="12">
@@ -8108,6 +8104,9 @@
       <c r="K178" s="12">
         <v>1</v>
       </c>
+      <c r="L178" s="2" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="10">
@@ -8223,7 +8222,7 @@
         <v>4</v>
       </c>
       <c r="L181" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
@@ -8527,9 +8526,6 @@
         <f t="shared" si="42"/>
         <v>26</v>
       </c>
-      <c r="L189" s="2" t="s">
-        <v>118</v>
-      </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="10">
@@ -8604,6 +8600,9 @@
       <c r="K191" s="12">
         <v>1</v>
       </c>
+      <c r="L191" s="2" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="10">
@@ -8642,7 +8641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" s="10">
         <f t="shared" si="39"/>
         <v>189</v>
@@ -8679,7 +8678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" s="10">
         <f t="shared" si="39"/>
         <v>190</v>
@@ -8715,11 +8714,8 @@
       <c r="K194" s="12">
         <v>2</v>
       </c>
-      <c r="L194" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" s="10">
         <f t="shared" si="39"/>
         <v>191</v>
@@ -8757,7 +8753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" s="10">
         <f t="shared" si="39"/>
         <v>192</v>
@@ -8795,7 +8791,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" s="10">
         <f t="shared" si="39"/>
         <v>193</v>
@@ -8833,7 +8829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" s="10">
         <f t="shared" si="39"/>
         <v>194</v>
@@ -8871,7 +8867,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" s="10">
         <f t="shared" si="39"/>
         <v>195</v>
@@ -8909,7 +8905,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" s="10">
         <f t="shared" si="39"/>
         <v>196</v>
@@ -8947,7 +8943,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" s="10">
         <f t="shared" si="39"/>
         <v>197</v>
@@ -8985,7 +8981,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202" s="10">
         <f t="shared" si="39"/>
         <v>198</v>
@@ -9023,7 +9019,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" s="10">
         <f t="shared" si="39"/>
         <v>199</v>
@@ -9061,7 +9057,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" s="10">
         <f t="shared" si="39"/>
         <v>200</v>
@@ -9099,7 +9095,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205" s="10">
         <f t="shared" si="39"/>
         <v>201</v>
@@ -9137,7 +9133,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" s="10">
         <f t="shared" si="39"/>
         <v>202</v>
@@ -9175,7 +9171,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207" s="10">
         <f t="shared" si="39"/>
         <v>203</v>
@@ -9213,7 +9209,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" s="10">
         <f t="shared" si="39"/>
         <v>204</v>
@@ -13101,6 +13097,9 @@
       <c r="K309" s="12">
         <v>1</v>
       </c>
+      <c r="L309" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" s="10">
@@ -13405,9 +13404,6 @@
         <f t="shared" si="70"/>
         <v>12</v>
       </c>
-      <c r="L317" s="2" t="s">
-        <v>104</v>
-      </c>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" s="10">
@@ -13597,6 +13593,9 @@
       <c r="K322" s="12">
         <v>1</v>
       </c>
+      <c r="L322" s="2" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A323" s="10">
@@ -13901,9 +13900,6 @@
         <f t="shared" si="73"/>
         <v>12</v>
       </c>
-      <c r="L330" s="2" t="s">
-        <v>109</v>
-      </c>
     </row>
     <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" s="10">
@@ -14093,6 +14089,9 @@
       <c r="K335" s="12">
         <v>1</v>
       </c>
+      <c r="L335" s="2" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" s="10">
@@ -14397,9 +14396,6 @@
         <f t="shared" si="76"/>
         <v>12</v>
       </c>
-      <c r="L343" s="2" t="s">
-        <v>113</v>
-      </c>
     </row>
     <row r="344" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A344" s="10">
@@ -15261,6 +15257,9 @@
       <c r="K365" s="12">
         <v>1</v>
       </c>
+      <c r="L365" s="2" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="366" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A366" s="10">
@@ -15376,7 +15375,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A369" s="10">
         <f t="shared" si="63"/>
         <v>365</v>
@@ -15414,7 +15413,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A370" s="10">
         <f t="shared" si="63"/>
         <v>366</v>
@@ -15452,7 +15451,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A371" s="10">
         <f t="shared" si="63"/>
         <v>367</v>
@@ -15490,7 +15489,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A372" s="10">
         <f t="shared" si="63"/>
         <v>368</v>
@@ -15528,7 +15527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A373" s="10">
         <f t="shared" si="63"/>
         <v>369</v>
@@ -15565,11 +15564,8 @@
         <f t="shared" si="82"/>
         <v>12</v>
       </c>
-      <c r="L373" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="374" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A374" s="10">
         <f t="shared" si="63"/>
         <v>370</v>
@@ -15607,7 +15603,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A375" s="10">
         <f t="shared" si="63"/>
         <v>371</v>
@@ -15645,7 +15641,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A376" s="10">
         <f t="shared" si="63"/>
         <v>372</v>
@@ -15683,7 +15679,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A377" s="10">
         <f t="shared" si="63"/>
         <v>373</v>
@@ -15721,7 +15717,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A378" s="10">
         <f t="shared" si="63"/>
         <v>374</v>
@@ -15758,7 +15754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A379" s="10">
         <f t="shared" si="63"/>
         <v>375</v>
@@ -15796,7 +15792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A380" s="10">
         <f t="shared" si="63"/>
         <v>376</v>
@@ -15834,7 +15830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A381" s="10">
         <f t="shared" si="63"/>
         <v>377</v>
@@ -15872,7 +15868,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A382" s="10">
         <f t="shared" si="63"/>
         <v>378</v>
@@ -15910,7 +15906,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A383" s="10">
         <f t="shared" si="63"/>
         <v>379</v>
@@ -15948,7 +15944,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A384" s="10">
         <f t="shared" si="63"/>
         <v>380</v>
